--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Apple Towing - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF7299E-D8D5-4E15-9104-E90F16CE0CDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017655B3-E745-4BAB-92E8-3F52B5650512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -40615,7 +40615,7 @@
         <v>12</v>
       </c>
       <c r="H1455" s="2">
-        <v>2.3148148148148147E-5</v>
+        <v>3.6458333333333334E-3</v>
       </c>
       <c r="I1455" s="1">
         <v>46055.755787037036</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Apple Towing - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017655B3-E745-4BAB-92E8-3F52B5650512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F6C848-D0F5-45B6-B84E-56C435A50637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7452" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7810" uniqueCount="167">
   <si>
     <t>Company Name</t>
   </si>
@@ -535,6 +535,12 @@
   <si>
     <t>Camera Event Management Orientation for Drivers</t>
   </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Jose Ramirez</t>
+  </si>
 </sst>
 </file>
 
@@ -43975,7 +43981,7 @@
         <v>10</v>
       </c>
       <c r="H1580" s="2">
-        <v>5.4745370370370373E-3</v>
+        <v>1.0289351851851852E-2</v>
       </c>
       <c r="I1580" s="1">
         <v>46083.711342592593</v>
@@ -44263,342 +44269,2130 @@
       </c>
     </row>
     <row r="1592" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1592" s="2"/>
-      <c r="I1592" s="1"/>
+      <c r="B1592" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1592">
+        <v>2111</v>
+      </c>
+      <c r="D1592" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1592" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1592" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1592" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1592" s="1">
+        <v>46118.717939814815</v>
+      </c>
+      <c r="J1592">
+        <v>1</v>
+      </c>
+      <c r="K1592" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1593" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1593" s="2"/>
-      <c r="I1593" s="1"/>
+      <c r="B1593" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1593">
+        <v>2114</v>
+      </c>
+      <c r="D1593" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1593" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1593" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1593" s="2">
+        <v>7.013888888888889E-3</v>
+      </c>
+      <c r="I1593" s="1">
+        <v>46118.718634259261</v>
+      </c>
+      <c r="J1593">
+        <v>1</v>
+      </c>
+      <c r="K1593" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1594" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1594" s="2"/>
-      <c r="I1594" s="1"/>
+      <c r="B1594" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1594">
+        <v>2613</v>
+      </c>
+      <c r="D1594" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1594" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1594" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1594" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1594" s="1">
+        <v>46118.719328703701</v>
+      </c>
+      <c r="J1594">
+        <v>1</v>
+      </c>
+      <c r="K1594" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1595" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I1595" s="1"/>
+      <c r="B1595" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1595">
+        <v>2506</v>
+      </c>
+      <c r="D1595" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1595" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1595" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1595" s="2">
+        <v>1.4085648148148147E-2</v>
+      </c>
+      <c r="I1595" s="1">
+        <v>46118.719328703701</v>
+      </c>
+      <c r="J1595">
+        <v>1</v>
+      </c>
+      <c r="K1595" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1596" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I1596" s="1"/>
+      <c r="B1596" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1596">
+        <v>2507</v>
+      </c>
+      <c r="D1596" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1596" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1596" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1596">
+        <v>0</v>
+      </c>
+      <c r="I1596" s="1">
+        <v>46118.720023148147</v>
+      </c>
+      <c r="J1596">
+        <v>1</v>
+      </c>
+      <c r="K1596" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1597" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1597" s="2"/>
-      <c r="I1597" s="1"/>
+      <c r="B1597" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1597">
+        <v>2505</v>
+      </c>
+      <c r="D1597" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1597" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1597" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1597" s="2">
+        <v>8.4375000000000006E-3</v>
+      </c>
+      <c r="I1597" s="1">
+        <v>46118.720717592594</v>
+      </c>
+      <c r="J1597">
+        <v>0</v>
+      </c>
+      <c r="K1597" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1598" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1598" s="2"/>
-      <c r="I1598" s="1"/>
+      <c r="B1598" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1598">
+        <v>2489</v>
+      </c>
+      <c r="D1598" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1598" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1598" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1598" s="2">
+        <v>8.2986111111111108E-3</v>
+      </c>
+      <c r="I1598" s="1">
+        <v>46118.721412037034</v>
+      </c>
+      <c r="J1598">
+        <v>1</v>
+      </c>
+      <c r="K1598" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1599" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1599" s="2"/>
-      <c r="I1599" s="1"/>
+      <c r="B1599" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1599">
+        <v>2082</v>
+      </c>
+      <c r="D1599" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1599" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1599" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1599" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1599" s="1">
+        <v>46118.721412037034</v>
+      </c>
+      <c r="J1599">
+        <v>1</v>
+      </c>
+      <c r="K1599" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1600" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1600" s="2"/>
-      <c r="I1600" s="1"/>
-    </row>
-    <row r="1601" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1601" s="2"/>
-      <c r="I1601" s="1"/>
-    </row>
-    <row r="1602" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1602" s="1"/>
-    </row>
-    <row r="1603" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1603" s="2"/>
-      <c r="I1603" s="1"/>
-    </row>
-    <row r="1604" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1604" s="2"/>
-      <c r="I1604" s="1"/>
-    </row>
-    <row r="1605" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1605" s="1"/>
-    </row>
-    <row r="1606" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1606" s="2"/>
-      <c r="I1606" s="1"/>
-    </row>
-    <row r="1607" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1607" s="2"/>
-      <c r="I1607" s="1"/>
-    </row>
-    <row r="1608" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1608" s="2"/>
-      <c r="I1608" s="1"/>
-    </row>
-    <row r="1609" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B1600" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1600">
+        <v>2615</v>
+      </c>
+      <c r="D1600" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1600" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1600" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1600" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1600" s="1">
+        <v>46118.72210648148</v>
+      </c>
+      <c r="J1600">
+        <v>1</v>
+      </c>
+      <c r="K1600" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1601" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1601" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1601">
+        <v>5036</v>
+      </c>
+      <c r="D1601" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1601" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1601" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1601" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1601" s="1">
+        <v>46118.72210648148</v>
+      </c>
+      <c r="J1601">
+        <v>1</v>
+      </c>
+      <c r="K1601" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1602" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1602" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1602">
+        <v>2504</v>
+      </c>
+      <c r="D1602" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1602" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1602" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1602" s="2">
+        <v>3.0787037037037037E-3</v>
+      </c>
+      <c r="I1602" s="1">
+        <v>46118.722800925927</v>
+      </c>
+      <c r="J1602">
+        <v>1</v>
+      </c>
+      <c r="K1602" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1603" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1603" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1603">
+        <v>2457</v>
+      </c>
+      <c r="D1603" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1603" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1603" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1603" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1603" s="1">
+        <v>46118.723495370374</v>
+      </c>
+      <c r="J1603">
+        <v>1</v>
+      </c>
+      <c r="K1603" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1604" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1604" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1604">
+        <v>2612</v>
+      </c>
+      <c r="D1604" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1604" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1604" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1604" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1604" s="1">
+        <v>46118.723495370374</v>
+      </c>
+      <c r="J1604">
+        <v>1</v>
+      </c>
+      <c r="K1604" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1605" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1605" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1605">
+        <v>5090</v>
+      </c>
+      <c r="D1605" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1605" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1605" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1605">
+        <v>0</v>
+      </c>
+      <c r="I1605" s="1">
+        <v>46118.724189814813</v>
+      </c>
+      <c r="J1605">
+        <v>1</v>
+      </c>
+      <c r="K1605" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1606" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1606" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1606">
+        <v>2634</v>
+      </c>
+      <c r="D1606" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1606" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1606" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1606" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1606" s="1">
+        <v>46118.72488425926</v>
+      </c>
+      <c r="J1606">
+        <v>1</v>
+      </c>
+      <c r="K1606" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1607" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1607" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1607">
+        <v>2636</v>
+      </c>
+      <c r="D1607" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1607" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1607" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1607" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1607" s="1">
+        <v>46118.72488425926</v>
+      </c>
+      <c r="J1607">
+        <v>1</v>
+      </c>
+      <c r="K1607" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1608" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1608" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1608">
+        <v>2487</v>
+      </c>
+      <c r="D1608" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1608" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1608" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1608" s="2">
+        <v>6.4814814814814813E-3</v>
+      </c>
+      <c r="I1608" s="1">
+        <v>46118.725578703707</v>
+      </c>
+      <c r="J1608">
+        <v>0</v>
+      </c>
+      <c r="K1608" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1609" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1609" s="1"/>
-    </row>
-    <row r="1610" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1610" s="2"/>
-      <c r="I1610" s="1"/>
-    </row>
-    <row r="1611" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1611" s="2"/>
-      <c r="I1611" s="1"/>
-    </row>
-    <row r="1612" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1612" s="1"/>
-    </row>
-    <row r="1613" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1609" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1610" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1610" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1610">
+        <v>2492</v>
+      </c>
+      <c r="D1610" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1610" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1610" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1610" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1610" s="1">
+        <v>46118.725578703707</v>
+      </c>
+      <c r="J1610">
+        <v>1</v>
+      </c>
+      <c r="K1610" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1611" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1611" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1611">
+        <v>5065</v>
+      </c>
+      <c r="D1611" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1611" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1611" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1611" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1611" s="1">
+        <v>46118.726273148146</v>
+      </c>
+      <c r="J1611">
+        <v>1</v>
+      </c>
+      <c r="K1611" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1612" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1612" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1612">
+        <v>2650</v>
+      </c>
+      <c r="D1612" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1612" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1612" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1612" s="2">
+        <v>1.1574074074074073E-5</v>
+      </c>
+      <c r="I1612" s="1">
+        <v>46118.726967592593</v>
+      </c>
+      <c r="J1612">
+        <v>1</v>
+      </c>
+      <c r="K1612" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1613" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1613" s="2"/>
       <c r="I1613" s="1"/>
-    </row>
-    <row r="1614" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1614" s="2"/>
-      <c r="I1614" s="1"/>
-    </row>
-    <row r="1615" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1615" s="2"/>
-      <c r="I1615" s="1"/>
-    </row>
-    <row r="1616" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1613" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1614" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1614" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1614">
+        <v>2632</v>
+      </c>
+      <c r="D1614" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1614" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1614" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1614" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1614" s="1">
+        <v>46118.726967592593</v>
+      </c>
+      <c r="J1614">
+        <v>1</v>
+      </c>
+      <c r="K1614" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1615" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1615" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1615">
+        <v>2494</v>
+      </c>
+      <c r="D1615" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1615" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1615" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1615" s="2">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="I1615" s="1">
+        <v>46118.727662037039</v>
+      </c>
+      <c r="J1615">
+        <v>0</v>
+      </c>
+      <c r="K1615" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1616" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1616" s="2"/>
       <c r="I1616" s="1"/>
-    </row>
-    <row r="1617" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1617" s="1"/>
-    </row>
-    <row r="1618" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1618" s="2"/>
-      <c r="I1618" s="1"/>
-    </row>
-    <row r="1619" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1619" s="1"/>
-    </row>
-    <row r="1620" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1620" s="2"/>
-      <c r="I1620" s="1"/>
-    </row>
-    <row r="1621" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1621" s="2"/>
-      <c r="I1621" s="1"/>
-    </row>
-    <row r="1622" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1622" s="2"/>
-      <c r="I1622" s="1"/>
-    </row>
-    <row r="1623" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1623" s="2"/>
-      <c r="I1623" s="1"/>
-    </row>
-    <row r="1624" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1616" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1617" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1617" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1617">
+        <v>2902</v>
+      </c>
+      <c r="D1617" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1617" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1617" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1617">
+        <v>0</v>
+      </c>
+      <c r="I1617" s="1">
+        <v>46118.728356481479</v>
+      </c>
+      <c r="J1617">
+        <v>1</v>
+      </c>
+      <c r="K1617" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1618" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1618" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1618">
+        <v>2633</v>
+      </c>
+      <c r="D1618" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1618" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1618" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1618" s="2">
+        <v>1.1284722222222222E-2</v>
+      </c>
+      <c r="I1618" s="1">
+        <v>46118.728356481479</v>
+      </c>
+      <c r="J1618">
+        <v>1</v>
+      </c>
+      <c r="K1618" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1619" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1619" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1619">
+        <v>2115</v>
+      </c>
+      <c r="D1619" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1619" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1619" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1619">
+        <v>0</v>
+      </c>
+      <c r="I1619" s="1">
+        <v>46118.729050925926</v>
+      </c>
+      <c r="J1619">
+        <v>1</v>
+      </c>
+      <c r="K1619" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1620" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1620" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1620">
+        <v>2081</v>
+      </c>
+      <c r="D1620" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1620" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1620" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1620" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1620" s="1">
+        <v>46118.729745370372</v>
+      </c>
+      <c r="J1620">
+        <v>1</v>
+      </c>
+      <c r="K1620" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1621" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1621" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1621">
+        <v>2458</v>
+      </c>
+      <c r="D1621" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1621" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1621" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1621" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1621" s="1">
+        <v>46118.729745370372</v>
+      </c>
+      <c r="J1621">
+        <v>1</v>
+      </c>
+      <c r="K1621" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1622" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1622" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1622">
+        <v>2635</v>
+      </c>
+      <c r="D1622" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1622" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1622" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1622" s="2">
+        <v>7.4074074074074077E-3</v>
+      </c>
+      <c r="I1622" s="1">
+        <v>46118.730439814812</v>
+      </c>
+      <c r="J1622">
+        <v>1</v>
+      </c>
+      <c r="K1622" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1623" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1623" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1623">
+        <v>3776</v>
+      </c>
+      <c r="D1623" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1623" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1623" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1623" s="2">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="I1623" s="1">
+        <v>46118.731134259258</v>
+      </c>
+      <c r="J1623">
+        <v>1</v>
+      </c>
+      <c r="K1623" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1624" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
-    </row>
-    <row r="1625" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1625" s="2"/>
-      <c r="I1625" s="1"/>
-    </row>
-    <row r="1626" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1626" s="1"/>
-    </row>
-    <row r="1627" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1624" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1625" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1625" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1625">
+        <v>2247</v>
+      </c>
+      <c r="D1625" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1625" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1625" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1625" s="2">
+        <v>9.1550925925925931E-3</v>
+      </c>
+      <c r="I1625" s="1">
+        <v>46118.731134259258</v>
+      </c>
+      <c r="J1625">
+        <v>0</v>
+      </c>
+      <c r="K1625" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1626" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1626" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1626">
+        <v>2651</v>
+      </c>
+      <c r="D1626" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1626" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1626" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1626" s="2">
+        <v>5.8692129629629629E-2</v>
+      </c>
+      <c r="I1626" s="1">
+        <v>46118.731828703705</v>
+      </c>
+      <c r="J1626">
+        <v>0</v>
+      </c>
+      <c r="K1626" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1627" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1627" s="2"/>
       <c r="I1627" s="1"/>
-    </row>
-    <row r="1628" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1628" s="1"/>
-    </row>
-    <row r="1629" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1629" s="2"/>
-      <c r="I1629" s="1"/>
-    </row>
-    <row r="1630" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1630" s="1"/>
-    </row>
-    <row r="1631" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1631" s="2"/>
-      <c r="I1631" s="1"/>
-    </row>
-    <row r="1632" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1627" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1628" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1628" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1628">
+        <v>2116</v>
+      </c>
+      <c r="D1628" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1628" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1628" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1628" s="2">
+        <v>6.4930555555555557E-3</v>
+      </c>
+      <c r="I1628" s="1">
+        <v>46118.731828703705</v>
+      </c>
+      <c r="J1628">
+        <v>1</v>
+      </c>
+      <c r="K1628" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1629" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1629" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1629">
+        <v>2053</v>
+      </c>
+      <c r="D1629" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1629" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1629" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1629" s="2">
+        <v>8.4953703703703701E-3</v>
+      </c>
+      <c r="I1629" s="1">
+        <v>46118.732523148145</v>
+      </c>
+      <c r="J1629">
+        <v>0</v>
+      </c>
+      <c r="K1629" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1630" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1630" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1630">
+        <v>2503</v>
+      </c>
+      <c r="D1630" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1630" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1630" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1630">
+        <v>0</v>
+      </c>
+      <c r="I1630" s="1">
+        <v>46118.732523148145</v>
+      </c>
+      <c r="J1630">
+        <v>1</v>
+      </c>
+      <c r="K1630" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1631" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1631" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1631">
+        <v>2493</v>
+      </c>
+      <c r="D1631" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1631" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1631" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1631" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1631" s="1">
+        <v>46118.753472222219</v>
+      </c>
+      <c r="J1631">
+        <v>1</v>
+      </c>
+      <c r="K1631" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1632" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1632" s="2"/>
       <c r="I1632" s="1"/>
-    </row>
-    <row r="1633" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1633" s="2"/>
-      <c r="I1633" s="1"/>
-    </row>
-    <row r="1634" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1634" s="2"/>
-      <c r="I1634" s="1"/>
-    </row>
-    <row r="1635" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1635" s="1"/>
-    </row>
-    <row r="1636" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1636" s="2"/>
-      <c r="I1636" s="1"/>
-    </row>
-    <row r="1637" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1637" s="2"/>
-      <c r="I1637" s="1"/>
-    </row>
-    <row r="1638" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1638" s="1"/>
-    </row>
-    <row r="1639" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1639" s="1"/>
-    </row>
-    <row r="1640" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1640" s="2"/>
-      <c r="I1640" s="1"/>
-    </row>
-    <row r="1641" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1641" s="2"/>
-      <c r="I1641" s="1"/>
-    </row>
-    <row r="1642" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1642" s="2"/>
-      <c r="I1642" s="1"/>
-    </row>
-    <row r="1643" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1643" s="2"/>
-      <c r="I1643" s="1"/>
-    </row>
-    <row r="1644" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1644" s="2"/>
-      <c r="I1644" s="1"/>
-    </row>
-    <row r="1645" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1645" s="2"/>
-      <c r="I1645" s="1"/>
-    </row>
-    <row r="1646" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1646" s="2"/>
-      <c r="I1646" s="1"/>
-    </row>
-    <row r="1647" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1632" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1633" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1633" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1633">
+        <v>5388</v>
+      </c>
+      <c r="D1633" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1633" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1633" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1633" s="2">
+        <v>8.4375000000000006E-3</v>
+      </c>
+      <c r="I1633" s="1">
+        <v>46118.754166666666</v>
+      </c>
+      <c r="J1633">
+        <v>0</v>
+      </c>
+      <c r="K1633" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1634" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1634" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1634">
+        <v>5038</v>
+      </c>
+      <c r="D1634" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1634" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1634" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1634" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1634" s="1">
+        <v>46118.754166666666</v>
+      </c>
+      <c r="J1634">
+        <v>1</v>
+      </c>
+      <c r="K1634" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1635" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1635" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1635">
+        <v>4961</v>
+      </c>
+      <c r="D1635" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1635" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1635" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1635">
+        <v>0</v>
+      </c>
+      <c r="I1635" s="1">
+        <v>46118.754861111112</v>
+      </c>
+      <c r="J1635">
+        <v>1</v>
+      </c>
+      <c r="K1635" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1636" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1636" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1636">
+        <v>2497</v>
+      </c>
+      <c r="D1636" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1636" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1636" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1636" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1636" s="1">
+        <v>46118.755555555559</v>
+      </c>
+      <c r="J1636">
+        <v>1</v>
+      </c>
+      <c r="K1636" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1637" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1637" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1637">
+        <v>4946</v>
+      </c>
+      <c r="D1637" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1637" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1637" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1637" s="2">
+        <v>7.0486111111111114E-3</v>
+      </c>
+      <c r="I1637" s="1">
+        <v>46118.755555555559</v>
+      </c>
+      <c r="J1637">
+        <v>1</v>
+      </c>
+      <c r="K1637" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1638" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1638" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1638">
+        <v>2118</v>
+      </c>
+      <c r="D1638" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1638" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1638" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1638">
+        <v>0</v>
+      </c>
+      <c r="I1638" s="1">
+        <v>46118.756249999999</v>
+      </c>
+      <c r="J1638">
+        <v>1</v>
+      </c>
+      <c r="K1638" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1639" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1639" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1639">
+        <v>2089</v>
+      </c>
+      <c r="D1639" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1639" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1639" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1639">
+        <v>0</v>
+      </c>
+      <c r="I1639" s="1">
+        <v>46118.756944444445</v>
+      </c>
+      <c r="J1639">
+        <v>1</v>
+      </c>
+      <c r="K1639" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1640" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1640" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1640">
+        <v>3206</v>
+      </c>
+      <c r="D1640" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1640" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1640" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1640" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1640" s="1">
+        <v>46118.757638888892</v>
+      </c>
+      <c r="J1640">
+        <v>1</v>
+      </c>
+      <c r="K1640" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1641" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1641" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1641">
+        <v>2905</v>
+      </c>
+      <c r="D1641" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1641" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1641" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1641" s="2">
+        <v>7.2106481481481483E-3</v>
+      </c>
+      <c r="I1641" s="1">
+        <v>46118.757638888892</v>
+      </c>
+      <c r="J1641">
+        <v>1</v>
+      </c>
+      <c r="K1641" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1642" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1642" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1642">
+        <v>2652</v>
+      </c>
+      <c r="D1642" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1642" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1642" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1642" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1642" s="1">
+        <v>46118.758333333331</v>
+      </c>
+      <c r="J1642">
+        <v>1</v>
+      </c>
+      <c r="K1642" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1643" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1643" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1643">
+        <v>2511</v>
+      </c>
+      <c r="D1643" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1643" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1643" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1643" s="2">
+        <v>1.0127314814814815E-2</v>
+      </c>
+      <c r="I1643" s="1">
+        <v>46118.758333333331</v>
+      </c>
+      <c r="J1643">
+        <v>1</v>
+      </c>
+      <c r="K1643" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1644" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1644" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1644">
+        <v>2499</v>
+      </c>
+      <c r="D1644" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1644" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1644" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1644" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1644" s="1">
+        <v>46118.759027777778</v>
+      </c>
+      <c r="J1644">
+        <v>1</v>
+      </c>
+      <c r="K1644" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1645" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1645" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1645">
+        <v>2510</v>
+      </c>
+      <c r="D1645" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1645" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1645" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1645" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1645" s="1">
+        <v>46118.759722222225</v>
+      </c>
+      <c r="J1645">
+        <v>1</v>
+      </c>
+      <c r="K1645" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1646" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1646" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1646">
+        <v>3239</v>
+      </c>
+      <c r="D1646" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1646" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1646" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1646" s="2">
+        <v>1.0972222222222222E-2</v>
+      </c>
+      <c r="I1646" s="1">
+        <v>46118.759722222225</v>
+      </c>
+      <c r="J1646">
+        <v>0</v>
+      </c>
+      <c r="K1646" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1647" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1647" s="2"/>
       <c r="I1647" s="1"/>
-    </row>
-    <row r="1648" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1648" s="2"/>
-      <c r="I1648" s="1"/>
-    </row>
-    <row r="1649" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1649" s="2"/>
-      <c r="I1649" s="1"/>
-    </row>
-    <row r="1650" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1650" s="2"/>
-      <c r="I1650" s="1"/>
-    </row>
-    <row r="1651" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1651" s="2"/>
-      <c r="I1651" s="1"/>
-    </row>
-    <row r="1652" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1652" s="2"/>
-      <c r="I1652" s="1"/>
-    </row>
-    <row r="1653" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1653" s="2"/>
-      <c r="I1653" s="1"/>
-    </row>
-    <row r="1654" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1647" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1648" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1648" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1648">
+        <v>2088</v>
+      </c>
+      <c r="D1648" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1648" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1648" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1648" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1648" s="1">
+        <v>46118.760416666664</v>
+      </c>
+      <c r="J1648">
+        <v>1</v>
+      </c>
+      <c r="K1648" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1649" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1649" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1649">
+        <v>2903</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1649" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1649" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1649" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1649" s="1">
+        <v>46118.761111111111</v>
+      </c>
+      <c r="J1649">
+        <v>1</v>
+      </c>
+      <c r="K1649" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1650" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1650" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1650">
+        <v>2508</v>
+      </c>
+      <c r="D1650" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1650" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1650" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1650" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1650" s="1">
+        <v>46118.761111111111</v>
+      </c>
+      <c r="J1650">
+        <v>1</v>
+      </c>
+      <c r="K1650" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1651" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1651" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1651">
+        <v>2648</v>
+      </c>
+      <c r="D1651" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1651" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1651" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1651" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1651" s="1">
+        <v>46118.761805555558</v>
+      </c>
+      <c r="J1651">
+        <v>1</v>
+      </c>
+      <c r="K1651" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1652" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1652" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1652">
+        <v>2459</v>
+      </c>
+      <c r="D1652" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1652" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1652" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1652" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1652" s="1">
+        <v>46118.762499999997</v>
+      </c>
+      <c r="J1652">
+        <v>1</v>
+      </c>
+      <c r="K1652" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1653" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1653" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1653">
+        <v>2483</v>
+      </c>
+      <c r="D1653" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1653" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1653" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1653" s="2">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="I1653" s="1">
+        <v>46118.762499999997</v>
+      </c>
+      <c r="J1653">
+        <v>1</v>
+      </c>
+      <c r="K1653" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1654" spans="2:11" x14ac:dyDescent="0.25">
       <c r="I1654" s="1"/>
-    </row>
-    <row r="1655" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1655" s="2"/>
-      <c r="I1655" s="1"/>
-    </row>
-    <row r="1656" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1656" s="2"/>
-      <c r="I1656" s="1"/>
-    </row>
-    <row r="1657" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1657" s="2"/>
-      <c r="I1657" s="1"/>
-    </row>
-    <row r="1658" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="I1658" s="1"/>
-    </row>
-    <row r="1659" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1659" s="2"/>
-      <c r="I1659" s="1"/>
-    </row>
-    <row r="1660" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1660" s="2"/>
-      <c r="I1660" s="1"/>
-    </row>
-    <row r="1661" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1661" s="2"/>
-      <c r="I1661" s="1"/>
-    </row>
-    <row r="1662" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1662" s="2"/>
-      <c r="I1662" s="1"/>
-    </row>
-    <row r="1663" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1663" s="2"/>
-      <c r="I1663" s="1"/>
-    </row>
-    <row r="1664" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1664" s="2"/>
-      <c r="I1664" s="1"/>
-    </row>
-    <row r="1665" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1665" s="2"/>
-      <c r="I1665" s="1"/>
-    </row>
-    <row r="1666" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1666" s="2"/>
-      <c r="I1666" s="1"/>
-    </row>
-    <row r="1667" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1667" s="2"/>
-      <c r="I1667" s="1"/>
-    </row>
-    <row r="1668" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1668" s="2"/>
-      <c r="I1668" s="1"/>
-    </row>
-    <row r="1669" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1669" s="2"/>
-      <c r="I1669" s="1"/>
-    </row>
-    <row r="1670" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1654" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1655" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1655" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1655">
+        <v>2113</v>
+      </c>
+      <c r="D1655" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1655" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1655" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1655" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1655" s="1">
+        <v>46118.763194444444</v>
+      </c>
+      <c r="J1655">
+        <v>1</v>
+      </c>
+      <c r="K1655" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1656" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1656" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1656">
+        <v>2490</v>
+      </c>
+      <c r="D1656" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1656" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1656" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1656" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1656" s="1">
+        <v>46118.763888888891</v>
+      </c>
+      <c r="J1656">
+        <v>1</v>
+      </c>
+      <c r="K1656" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1657" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1657" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1657">
+        <v>2638</v>
+      </c>
+      <c r="D1657" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1657" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1657" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1657" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1657" s="1">
+        <v>46118.763888888891</v>
+      </c>
+      <c r="J1657">
+        <v>1</v>
+      </c>
+      <c r="K1657" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1658" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1658" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1658">
+        <v>4919</v>
+      </c>
+      <c r="D1658" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1658" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1658" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1658">
+        <v>0</v>
+      </c>
+      <c r="I1658" s="1">
+        <v>46118.76458333333</v>
+      </c>
+      <c r="J1658">
+        <v>1</v>
+      </c>
+      <c r="K1658" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1659" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1659" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1659">
+        <v>2509</v>
+      </c>
+      <c r="D1659" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1659" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1659" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1659" s="2">
+        <v>7.3379629629629628E-3</v>
+      </c>
+      <c r="I1659" s="1">
+        <v>46118.765277777777</v>
+      </c>
+      <c r="J1659">
+        <v>0</v>
+      </c>
+      <c r="K1659" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1660" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1660" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1660">
+        <v>2901</v>
+      </c>
+      <c r="D1660" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1660" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1660" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1660" s="2">
+        <v>1.0636574074074074E-2</v>
+      </c>
+      <c r="I1660" s="1">
+        <v>46118.765277777777</v>
+      </c>
+      <c r="J1660">
+        <v>0</v>
+      </c>
+      <c r="K1660" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1661" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1661" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1661">
+        <v>3130</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1661" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1661" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1661" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1661" s="1">
+        <v>46118.765972222223</v>
+      </c>
+      <c r="J1661">
+        <v>1</v>
+      </c>
+      <c r="K1661" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1662" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1662" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1662">
+        <v>2653</v>
+      </c>
+      <c r="D1662" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1662" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1662" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1662" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1662" s="1">
+        <v>46118.765972222223</v>
+      </c>
+      <c r="J1662">
+        <v>1</v>
+      </c>
+      <c r="K1662" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1663" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1663" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1663">
+        <v>2485</v>
+      </c>
+      <c r="D1663" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1663" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1663" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1663" s="2">
+        <v>7.9976851851851858E-3</v>
+      </c>
+      <c r="I1663" s="1">
+        <v>46118.76666666667</v>
+      </c>
+      <c r="J1663">
+        <v>1</v>
+      </c>
+      <c r="K1663" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1664" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1664" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1664">
+        <v>2074</v>
+      </c>
+      <c r="D1664" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1664" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1664" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1664" s="2">
+        <v>6.8402777777777776E-3</v>
+      </c>
+      <c r="I1664" s="1">
+        <v>46118.767361111109</v>
+      </c>
+      <c r="J1664">
+        <v>1</v>
+      </c>
+      <c r="K1664" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1665" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1665" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1665">
+        <v>2486</v>
+      </c>
+      <c r="D1665" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1665" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1665" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1665" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1665" s="1">
+        <v>46118.767361111109</v>
+      </c>
+      <c r="J1665">
+        <v>1</v>
+      </c>
+      <c r="K1665" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1666" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1666" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1666">
+        <v>2065</v>
+      </c>
+      <c r="D1666" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1666" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1666" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1666" s="2">
+        <v>7.8009259259259256E-3</v>
+      </c>
+      <c r="I1666" s="1">
+        <v>46118.768055555556</v>
+      </c>
+      <c r="J1666">
+        <v>1</v>
+      </c>
+      <c r="K1666" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1667" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1667" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1667">
+        <v>2649</v>
+      </c>
+      <c r="D1667" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1667" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1667" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1667" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1667" s="1">
+        <v>46118.768055555556</v>
+      </c>
+      <c r="J1667">
+        <v>1</v>
+      </c>
+      <c r="K1667" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1668" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1668" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1668">
+        <v>2611</v>
+      </c>
+      <c r="D1668" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1668" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1668" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1668" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1668" s="1">
+        <v>46118.768750000003</v>
+      </c>
+      <c r="J1668">
+        <v>1</v>
+      </c>
+      <c r="K1668" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1669" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1669" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1669">
+        <v>2498</v>
+      </c>
+      <c r="D1669" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1669" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1669" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1669" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1669" s="1">
+        <v>46118.769444444442</v>
+      </c>
+      <c r="J1669">
+        <v>1</v>
+      </c>
+      <c r="K1669" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1670" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1670" s="2"/>
       <c r="I1670" s="1"/>
     </row>
-    <row r="1671" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1671" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1671" s="2"/>
       <c r="I1671" s="1"/>
     </row>
-    <row r="1672" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1672" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1672" s="2"/>
       <c r="I1672" s="1"/>
     </row>
-    <row r="1673" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1673" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1673" s="2"/>
       <c r="I1673" s="1"/>
     </row>
-    <row r="1674" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1674" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1674" s="2"/>
       <c r="I1674" s="1"/>
     </row>
-    <row r="1675" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1675" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1675" s="2"/>
       <c r="I1675" s="1"/>
     </row>
-    <row r="1676" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1676" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1676" s="2"/>
       <c r="I1676" s="1"/>
     </row>
-    <row r="1677" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1677" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1677" s="2"/>
       <c r="I1677" s="1"/>
     </row>
-    <row r="1678" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1678" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1678" s="2"/>
       <c r="I1678" s="1"/>
     </row>
-    <row r="1679" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1679" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1679" s="2"/>
       <c r="I1679" s="1"/>
     </row>
-    <row r="1680" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1680" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1680" s="2"/>
       <c r="I1680" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Apple Towing - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F6C848-D0F5-45B6-B84E-56C435A50637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F39C2A-744E-4D8A-9548-5690E9E0F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -44291,7 +44291,7 @@
         <v>46118.717939814815</v>
       </c>
       <c r="J1592">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1592" t="s">
         <v>11</v>
@@ -44349,7 +44349,7 @@
         <v>46118.719328703701</v>
       </c>
       <c r="J1594">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1594" t="s">
         <v>11</v>
@@ -44407,7 +44407,7 @@
         <v>46118.720023148147</v>
       </c>
       <c r="J1596">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1596" t="s">
         <v>11</v>
@@ -44494,7 +44494,7 @@
         <v>46118.721412037034</v>
       </c>
       <c r="J1599">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1599" t="s">
         <v>11</v>
@@ -44523,7 +44523,7 @@
         <v>46118.72210648148</v>
       </c>
       <c r="J1600">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1600" t="s">
         <v>11</v>
@@ -44552,7 +44552,7 @@
         <v>46118.72210648148</v>
       </c>
       <c r="J1601">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1601" t="s">
         <v>11</v>
@@ -44601,48 +44601,26 @@
         <v>165</v>
       </c>
       <c r="G1603" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1603" s="2">
-        <v>0</v>
+        <v>4.0509259259259258E-4</v>
       </c>
       <c r="I1603" s="1">
         <v>46118.723495370374</v>
       </c>
       <c r="J1603">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1603" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1604" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1604" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1604">
-        <v>2612</v>
-      </c>
-      <c r="D1604" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1604" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1604" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1604" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1604" s="1">
-        <v>46118.723495370374</v>
-      </c>
-      <c r="J1604">
-        <v>1</v>
-      </c>
+      <c r="H1604" s="2"/>
+      <c r="I1604" s="1"/>
       <c r="K1604" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1605" spans="2:11" x14ac:dyDescent="0.25">
@@ -44650,10 +44628,10 @@
         <v>29</v>
       </c>
       <c r="C1605">
-        <v>5090</v>
+        <v>2612</v>
       </c>
       <c r="D1605" t="s">
-        <v>162</v>
+        <v>42</v>
       </c>
       <c r="F1605" t="s">
         <v>165</v>
@@ -44665,10 +44643,10 @@
         <v>0</v>
       </c>
       <c r="I1605" s="1">
-        <v>46118.724189814813</v>
+        <v>46118.723495370374</v>
       </c>
       <c r="J1605">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1605" t="s">
         <v>11</v>
@@ -44679,25 +44657,25 @@
         <v>29</v>
       </c>
       <c r="C1606">
-        <v>2634</v>
+        <v>5090</v>
       </c>
       <c r="D1606" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
       <c r="F1606" t="s">
         <v>165</v>
       </c>
       <c r="G1606" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1606" s="2">
-        <v>0</v>
+        <v>4.1666666666666666E-3</v>
       </c>
       <c r="I1606" s="1">
-        <v>46118.72488425926</v>
+        <v>46118.724189814813</v>
       </c>
       <c r="J1606">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1606" t="s">
         <v>11</v>
@@ -44708,10 +44686,10 @@
         <v>29</v>
       </c>
       <c r="C1607">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="D1607" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="F1607" t="s">
         <v>165</v>
@@ -44726,7 +44704,7 @@
         <v>46118.72488425926</v>
       </c>
       <c r="J1607">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1607" t="s">
         <v>11</v>
@@ -44737,63 +44715,64 @@
         <v>29</v>
       </c>
       <c r="C1608">
-        <v>2487</v>
+        <v>2636</v>
       </c>
       <c r="D1608" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="F1608" t="s">
         <v>165</v>
       </c>
       <c r="G1608" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1608" s="2">
+        <v>9.0740740740740747E-3</v>
+      </c>
+      <c r="I1608" s="1">
+        <v>46118.72488425926</v>
+      </c>
+      <c r="J1608">
+        <v>1</v>
+      </c>
+      <c r="K1608" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1609" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1609" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1609">
+        <v>2487</v>
+      </c>
+      <c r="D1609" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1609" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1609" t="s">
         <v>12</v>
       </c>
-      <c r="H1608" s="2">
+      <c r="H1609" s="2">
         <v>6.4814814814814813E-3</v>
       </c>
-      <c r="I1608" s="1">
+      <c r="I1609" s="1">
         <v>46118.725578703707</v>
       </c>
-      <c r="J1608">
-        <v>0</v>
-      </c>
-      <c r="K1608" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1609" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I1609" s="1"/>
+      <c r="J1609">
+        <v>0</v>
+      </c>
       <c r="K1609" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1610" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1610" s="2"/>
+      <c r="I1610" s="1"/>
+      <c r="K1610" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1610" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1610" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1610">
-        <v>2492</v>
-      </c>
-      <c r="D1610" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1610" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1610" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1610" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1610" s="1">
-        <v>46118.725578703707</v>
-      </c>
-      <c r="J1610">
-        <v>1</v>
-      </c>
-      <c r="K1610" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1611" spans="2:11" x14ac:dyDescent="0.25">
@@ -44801,10 +44780,10 @@
         <v>29</v>
       </c>
       <c r="C1611">
-        <v>5065</v>
+        <v>2492</v>
       </c>
       <c r="D1611" t="s">
-        <v>163</v>
+        <v>46</v>
       </c>
       <c r="F1611" t="s">
         <v>165</v>
@@ -44816,10 +44795,10 @@
         <v>0</v>
       </c>
       <c r="I1611" s="1">
-        <v>46118.726273148146</v>
+        <v>46118.725578703707</v>
       </c>
       <c r="J1611">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1611" t="s">
         <v>11</v>
@@ -44830,64 +44809,64 @@
         <v>29</v>
       </c>
       <c r="C1612">
-        <v>2650</v>
+        <v>5065</v>
       </c>
       <c r="D1612" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="F1612" t="s">
         <v>165</v>
       </c>
       <c r="G1612" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1612" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1612" s="1">
+        <v>46118.726273148146</v>
+      </c>
+      <c r="J1612">
+        <v>2</v>
+      </c>
+      <c r="K1612" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1613" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1613" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1613">
+        <v>2650</v>
+      </c>
+      <c r="D1613" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1613" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1613" t="s">
         <v>12</v>
       </c>
-      <c r="H1612" s="2">
+      <c r="H1613" s="2">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="I1612" s="1">
+      <c r="I1613" s="1">
         <v>46118.726967592593</v>
       </c>
-      <c r="J1612">
+      <c r="J1613">
         <v>1</v>
       </c>
-      <c r="K1612" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1613" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1613" s="2"/>
-      <c r="I1613" s="1"/>
       <c r="K1613" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1614" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1614" s="2"/>
+      <c r="I1614" s="1"/>
+      <c r="K1614" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1614" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1614" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1614">
-        <v>2632</v>
-      </c>
-      <c r="D1614" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1614" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1614" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1614" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1614" s="1">
-        <v>46118.726967592593</v>
-      </c>
-      <c r="J1614">
-        <v>1</v>
-      </c>
-      <c r="K1614" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1615" spans="2:11" x14ac:dyDescent="0.25">
@@ -44895,64 +44874,63 @@
         <v>29</v>
       </c>
       <c r="C1615">
-        <v>2494</v>
+        <v>2632</v>
       </c>
       <c r="D1615" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F1615" t="s">
         <v>165</v>
       </c>
       <c r="G1615" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1615" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1615" s="1">
+        <v>46118.726967592593</v>
+      </c>
+      <c r="J1615">
+        <v>2</v>
+      </c>
+      <c r="K1615" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1616" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1616" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1616">
+        <v>2494</v>
+      </c>
+      <c r="D1616" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1616" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1616" t="s">
         <v>12</v>
       </c>
-      <c r="H1615" s="2">
+      <c r="H1616" s="2">
         <v>1.0416666666666667E-4</v>
       </c>
-      <c r="I1615" s="1">
+      <c r="I1616" s="1">
         <v>46118.727662037039</v>
       </c>
-      <c r="J1615">
-        <v>0</v>
-      </c>
-      <c r="K1615" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1616" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1616" s="2"/>
-      <c r="I1616" s="1"/>
+      <c r="J1616">
+        <v>0</v>
+      </c>
       <c r="K1616" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1617" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I1617" s="1"/>
+      <c r="K1617" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1617" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1617" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1617">
-        <v>2902</v>
-      </c>
-      <c r="D1617" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1617" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1617" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1617">
-        <v>0</v>
-      </c>
-      <c r="I1617" s="1">
-        <v>46118.728356481479</v>
-      </c>
-      <c r="J1617">
-        <v>1</v>
-      </c>
-      <c r="K1617" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1618" spans="2:11" x14ac:dyDescent="0.25">
@@ -44960,25 +44938,25 @@
         <v>29</v>
       </c>
       <c r="C1618">
-        <v>2633</v>
+        <v>2902</v>
       </c>
       <c r="D1618" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="F1618" t="s">
         <v>165</v>
       </c>
       <c r="G1618" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1618" s="2">
-        <v>1.1284722222222222E-2</v>
+        <v>0</v>
       </c>
       <c r="I1618" s="1">
         <v>46118.728356481479</v>
       </c>
       <c r="J1618">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1618" t="s">
         <v>11</v>
@@ -44989,22 +44967,22 @@
         <v>29</v>
       </c>
       <c r="C1619">
-        <v>2115</v>
+        <v>2633</v>
       </c>
       <c r="D1619" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F1619" t="s">
         <v>165</v>
       </c>
       <c r="G1619" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1619">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1619" s="2">
+        <v>1.1284722222222222E-2</v>
       </c>
       <c r="I1619" s="1">
-        <v>46118.729050925926</v>
+        <v>46118.728356481479</v>
       </c>
       <c r="J1619">
         <v>1</v>
@@ -45018,10 +44996,10 @@
         <v>29</v>
       </c>
       <c r="C1620">
-        <v>2081</v>
+        <v>2115</v>
       </c>
       <c r="D1620" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1620" t="s">
         <v>165</v>
@@ -45033,10 +45011,10 @@
         <v>0</v>
       </c>
       <c r="I1620" s="1">
-        <v>46118.729745370372</v>
+        <v>46118.729050925926</v>
       </c>
       <c r="J1620">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1620" t="s">
         <v>11</v>
@@ -45047,10 +45025,10 @@
         <v>29</v>
       </c>
       <c r="C1621">
-        <v>2458</v>
+        <v>2081</v>
       </c>
       <c r="D1621" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="F1621" t="s">
         <v>165</v>
@@ -45065,7 +45043,7 @@
         <v>46118.729745370372</v>
       </c>
       <c r="J1621">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1621" t="s">
         <v>11</v>
@@ -45076,25 +45054,25 @@
         <v>29</v>
       </c>
       <c r="C1622">
-        <v>2635</v>
+        <v>2458</v>
       </c>
       <c r="D1622" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F1622" t="s">
         <v>165</v>
       </c>
       <c r="G1622" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1622" s="2">
-        <v>7.4074074074074077E-3</v>
+        <v>0</v>
       </c>
       <c r="I1622" s="1">
-        <v>46118.730439814812</v>
+        <v>46118.729745370372</v>
       </c>
       <c r="J1622">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1622" t="s">
         <v>11</v>
@@ -45105,22 +45083,22 @@
         <v>29</v>
       </c>
       <c r="C1623">
-        <v>3776</v>
+        <v>2635</v>
       </c>
       <c r="D1623" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="F1623" t="s">
         <v>165</v>
       </c>
       <c r="G1623" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1623" s="2">
-        <v>1.1574074074074075E-4</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="I1623" s="1">
-        <v>46118.731134259258</v>
+        <v>46118.730439814812</v>
       </c>
       <c r="J1623">
         <v>1</v>
@@ -45130,10 +45108,32 @@
       </c>
     </row>
     <row r="1624" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1624" s="2"/>
-      <c r="I1624" s="1"/>
+      <c r="B1624" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1624">
+        <v>3776</v>
+      </c>
+      <c r="D1624" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1624" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1624" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1624" s="2">
+        <v>8.6342592592592599E-3</v>
+      </c>
+      <c r="I1624" s="1">
+        <v>46118.731134259258</v>
+      </c>
+      <c r="J1624">
+        <v>1</v>
+      </c>
       <c r="K1624" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1625" spans="2:11" x14ac:dyDescent="0.25">
@@ -45282,7 +45282,7 @@
         <v>46118.732523148145</v>
       </c>
       <c r="J1630">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1630" t="s">
         <v>11</v>
@@ -45367,16 +45367,16 @@
         <v>165</v>
       </c>
       <c r="G1634" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1634" s="2">
-        <v>0</v>
+        <v>7.951388888888888E-3</v>
       </c>
       <c r="I1634" s="1">
         <v>46118.754166666666</v>
       </c>
       <c r="J1634">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1634" t="s">
         <v>11</v>
@@ -45405,7 +45405,7 @@
         <v>46118.754861111112</v>
       </c>
       <c r="J1635">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1635" t="s">
         <v>11</v>
@@ -45434,7 +45434,7 @@
         <v>46118.755555555559</v>
       </c>
       <c r="J1636">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1636" t="s">
         <v>11</v>
@@ -45492,7 +45492,7 @@
         <v>46118.756249999999</v>
       </c>
       <c r="J1638">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1638" t="s">
         <v>11</v>
@@ -45521,7 +45521,7 @@
         <v>46118.756944444445</v>
       </c>
       <c r="J1639">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1639" t="s">
         <v>11</v>
@@ -45550,7 +45550,7 @@
         <v>46118.757638888892</v>
       </c>
       <c r="J1640">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1640" t="s">
         <v>11</v>
@@ -45608,7 +45608,7 @@
         <v>46118.758333333331</v>
       </c>
       <c r="J1642">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1642" t="s">
         <v>11</v>
@@ -45666,7 +45666,7 @@
         <v>46118.759027777778</v>
       </c>
       <c r="J1644">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1644" t="s">
         <v>11</v>
@@ -45695,7 +45695,7 @@
         <v>46118.759722222225</v>
       </c>
       <c r="J1645">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1645" t="s">
         <v>11</v>
@@ -45760,7 +45760,7 @@
         <v>46118.760416666664</v>
       </c>
       <c r="J1648">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1648" t="s">
         <v>11</v>
@@ -45789,7 +45789,7 @@
         <v>46118.761111111111</v>
       </c>
       <c r="J1649">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1649" t="s">
         <v>11</v>
@@ -45809,16 +45809,16 @@
         <v>165</v>
       </c>
       <c r="G1650" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1650" s="2">
-        <v>0</v>
+        <v>8.611111111111111E-3</v>
       </c>
       <c r="I1650" s="1">
         <v>46118.761111111111</v>
       </c>
       <c r="J1650">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1650" t="s">
         <v>11</v>
@@ -45838,16 +45838,16 @@
         <v>165</v>
       </c>
       <c r="G1651" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1651" s="2">
-        <v>0</v>
+        <v>7.6157407407407406E-3</v>
       </c>
       <c r="I1651" s="1">
         <v>46118.761805555558</v>
       </c>
       <c r="J1651">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1651" t="s">
         <v>11</v>
@@ -45876,7 +45876,7 @@
         <v>46118.762499999997</v>
       </c>
       <c r="J1652">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1652" t="s">
         <v>11</v>
@@ -45940,7 +45940,7 @@
         <v>46118.763194444444</v>
       </c>
       <c r="J1655">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1655" t="s">
         <v>11</v>
@@ -45960,16 +45960,16 @@
         <v>165</v>
       </c>
       <c r="G1656" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1656" s="2">
-        <v>0</v>
+        <v>8.0902777777777778E-3</v>
       </c>
       <c r="I1656" s="1">
         <v>46118.763888888891</v>
       </c>
       <c r="J1656">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1656" t="s">
         <v>11</v>
@@ -45998,7 +45998,7 @@
         <v>46118.763888888891</v>
       </c>
       <c r="J1657">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1657" t="s">
         <v>11</v>
@@ -46027,7 +46027,7 @@
         <v>46118.76458333333</v>
       </c>
       <c r="J1658">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1658" t="s">
         <v>11</v>
@@ -46114,7 +46114,7 @@
         <v>46118.765972222223</v>
       </c>
       <c r="J1661">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1661" t="s">
         <v>11</v>
@@ -46143,7 +46143,7 @@
         <v>46118.765972222223</v>
       </c>
       <c r="J1662">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1662" t="s">
         <v>11</v>
@@ -46230,7 +46230,7 @@
         <v>46118.767361111109</v>
       </c>
       <c r="J1665">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1665" t="s">
         <v>11</v>
@@ -46279,16 +46279,16 @@
         <v>165</v>
       </c>
       <c r="G1667" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1667" s="2">
-        <v>0</v>
+        <v>7.3495370370370372E-3</v>
       </c>
       <c r="I1667" s="1">
         <v>46118.768055555556</v>
       </c>
       <c r="J1667">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1667" t="s">
         <v>11</v>
@@ -46317,7 +46317,7 @@
         <v>46118.768750000003</v>
       </c>
       <c r="J1668">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1668" t="s">
         <v>11</v>
@@ -46346,7 +46346,7 @@
         <v>46118.769444444442</v>
       </c>
       <c r="J1669">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1669" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Apple Towing - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F39C2A-744E-4D8A-9548-5690E9E0F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC2268C-84F4-40AE-B66D-B3EA127E6241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7810" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7813" uniqueCount="167">
   <si>
     <t>Company Name</t>
   </si>
@@ -42718,10 +42718,10 @@
         <v>28</v>
       </c>
       <c r="G1532" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1532" s="2">
-        <v>0</v>
+        <v>5.185185185185185E-3</v>
       </c>
       <c r="I1532" s="1">
         <v>46083.71539351852</v>
@@ -44291,7 +44291,7 @@
         <v>46118.717939814815</v>
       </c>
       <c r="J1592">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1592" t="s">
         <v>11</v>
@@ -44349,7 +44349,7 @@
         <v>46118.719328703701</v>
       </c>
       <c r="J1594">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1594" t="s">
         <v>11</v>
@@ -44407,7 +44407,7 @@
         <v>46118.720023148147</v>
       </c>
       <c r="J1596">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1596" t="s">
         <v>11</v>
@@ -44485,48 +44485,26 @@
         <v>165</v>
       </c>
       <c r="G1599" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1599" s="2">
-        <v>0</v>
+        <v>7.0486111111111114E-3</v>
       </c>
       <c r="I1599" s="1">
         <v>46118.721412037034</v>
       </c>
       <c r="J1599">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1599" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1600" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1600" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1600">
-        <v>2615</v>
-      </c>
-      <c r="D1600" t="s">
-        <v>110</v>
-      </c>
-      <c r="F1600" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1600" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1600" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1600" s="1">
-        <v>46118.72210648148</v>
-      </c>
-      <c r="J1600">
-        <v>2</v>
-      </c>
+      <c r="H1600" s="2"/>
+      <c r="I1600" s="1"/>
       <c r="K1600" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1601" spans="2:11" x14ac:dyDescent="0.25">
@@ -44534,10 +44512,10 @@
         <v>29</v>
       </c>
       <c r="C1601">
-        <v>5036</v>
+        <v>2615</v>
       </c>
       <c r="D1601" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="F1601" t="s">
         <v>165</v>
@@ -44552,7 +44530,7 @@
         <v>46118.72210648148</v>
       </c>
       <c r="J1601">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1601" t="s">
         <v>11</v>
@@ -44563,25 +44541,25 @@
         <v>29</v>
       </c>
       <c r="C1602">
-        <v>2504</v>
+        <v>5036</v>
       </c>
       <c r="D1602" t="s">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c r="F1602" t="s">
         <v>165</v>
       </c>
       <c r="G1602" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1602" s="2">
-        <v>3.0787037037037037E-3</v>
+        <v>0</v>
       </c>
       <c r="I1602" s="1">
-        <v>46118.722800925927</v>
+        <v>46118.72210648148</v>
       </c>
       <c r="J1602">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1602" t="s">
         <v>11</v>
@@ -44592,64 +44570,63 @@
         <v>29</v>
       </c>
       <c r="C1603">
-        <v>2457</v>
+        <v>2504</v>
       </c>
       <c r="D1603" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="F1603" t="s">
         <v>165</v>
       </c>
       <c r="G1603" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1603" s="2">
+        <v>3.0787037037037037E-3</v>
+      </c>
+      <c r="I1603" s="1">
+        <v>46118.722800925927</v>
+      </c>
+      <c r="J1603">
+        <v>1</v>
+      </c>
+      <c r="K1603" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1604" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1604" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1604">
+        <v>2457</v>
+      </c>
+      <c r="D1604" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1604" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1604" t="s">
         <v>12</v>
       </c>
-      <c r="H1603" s="2">
+      <c r="H1604" s="2">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="I1603" s="1">
+      <c r="I1604" s="1">
         <v>46118.723495370374</v>
       </c>
-      <c r="J1603">
+      <c r="J1604">
         <v>2</v>
       </c>
-      <c r="K1603" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1604" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1604" s="2"/>
-      <c r="I1604" s="1"/>
       <c r="K1604" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1605" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I1605" s="1"/>
+      <c r="K1605" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1605" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1605" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1605">
-        <v>2612</v>
-      </c>
-      <c r="D1605" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1605" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1605" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1605">
-        <v>0</v>
-      </c>
-      <c r="I1605" s="1">
-        <v>46118.723495370374</v>
-      </c>
-      <c r="J1605">
-        <v>2</v>
-      </c>
-      <c r="K1605" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1606" spans="2:11" x14ac:dyDescent="0.25">
@@ -44657,57 +44634,35 @@
         <v>29</v>
       </c>
       <c r="C1606">
-        <v>5090</v>
+        <v>2612</v>
       </c>
       <c r="D1606" t="s">
-        <v>162</v>
+        <v>42</v>
       </c>
       <c r="F1606" t="s">
         <v>165</v>
       </c>
       <c r="G1606" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1606" s="2">
-        <v>4.1666666666666666E-3</v>
+        <v>1.3888888888888889E-4</v>
       </c>
       <c r="I1606" s="1">
-        <v>46118.724189814813</v>
+        <v>46118.723495370374</v>
       </c>
       <c r="J1606">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1606" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1607" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1607" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1607">
-        <v>2634</v>
-      </c>
-      <c r="D1607" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1607" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1607" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1607" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1607" s="1">
-        <v>46118.72488425926</v>
-      </c>
-      <c r="J1607">
-        <v>2</v>
-      </c>
+      <c r="H1607" s="2"/>
+      <c r="I1607" s="1"/>
       <c r="K1607" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1608" spans="2:11" x14ac:dyDescent="0.25">
@@ -44715,10 +44670,10 @@
         <v>29</v>
       </c>
       <c r="C1608">
-        <v>2636</v>
+        <v>5090</v>
       </c>
       <c r="D1608" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="F1608" t="s">
         <v>165</v>
@@ -44727,13 +44682,13 @@
         <v>10</v>
       </c>
       <c r="H1608" s="2">
-        <v>9.0740740740740747E-3</v>
+        <v>4.1666666666666666E-3</v>
       </c>
       <c r="I1608" s="1">
-        <v>46118.72488425926</v>
+        <v>46118.724189814813</v>
       </c>
       <c r="J1608">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1608" t="s">
         <v>11</v>
@@ -44744,35 +44699,57 @@
         <v>29</v>
       </c>
       <c r="C1609">
-        <v>2487</v>
+        <v>2634</v>
       </c>
       <c r="D1609" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F1609" t="s">
         <v>165</v>
       </c>
       <c r="G1609" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H1609" s="2">
-        <v>6.4814814814814813E-3</v>
+        <v>0</v>
       </c>
       <c r="I1609" s="1">
-        <v>46118.725578703707</v>
+        <v>46118.72488425926</v>
       </c>
       <c r="J1609">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1609" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1610" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1610" s="2"/>
-      <c r="I1610" s="1"/>
+      <c r="B1610" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1610">
+        <v>2636</v>
+      </c>
+      <c r="D1610" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1610" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1610" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1610" s="2">
+        <v>9.0740740740740747E-3</v>
+      </c>
+      <c r="I1610" s="1">
+        <v>46118.72488425926</v>
+      </c>
+      <c r="J1610">
+        <v>1</v>
+      </c>
       <c r="K1610" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1611" spans="2:11" x14ac:dyDescent="0.25">
@@ -44780,57 +44757,35 @@
         <v>29</v>
       </c>
       <c r="C1611">
-        <v>2492</v>
+        <v>2487</v>
       </c>
       <c r="D1611" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F1611" t="s">
         <v>165</v>
       </c>
       <c r="G1611" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1611" s="2">
-        <v>0</v>
+        <v>6.4814814814814813E-3</v>
       </c>
       <c r="I1611" s="1">
         <v>46118.725578703707</v>
       </c>
       <c r="J1611">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1611" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1612" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1612" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1612">
-        <v>5065</v>
-      </c>
-      <c r="D1612" t="s">
-        <v>163</v>
-      </c>
-      <c r="F1612" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1612" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1612" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1612" s="1">
-        <v>46118.726273148146</v>
-      </c>
-      <c r="J1612">
-        <v>2</v>
-      </c>
+      <c r="H1612" s="2"/>
+      <c r="I1612" s="1"/>
       <c r="K1612" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1613" spans="2:11" x14ac:dyDescent="0.25">
@@ -44838,35 +44793,57 @@
         <v>29</v>
       </c>
       <c r="C1613">
-        <v>2650</v>
+        <v>2492</v>
       </c>
       <c r="D1613" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="F1613" t="s">
         <v>165</v>
       </c>
       <c r="G1613" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1613" s="2">
-        <v>1.1574074074074073E-5</v>
+        <v>7.7083333333333335E-3</v>
       </c>
       <c r="I1613" s="1">
-        <v>46118.726967592593</v>
+        <v>46118.725578703707</v>
       </c>
       <c r="J1613">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1613" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1614" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1614" s="2"/>
-      <c r="I1614" s="1"/>
+      <c r="B1614" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1614">
+        <v>5065</v>
+      </c>
+      <c r="D1614" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1614" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1614" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1614" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1614" s="1">
+        <v>46118.726273148146</v>
+      </c>
+      <c r="J1614">
+        <v>3</v>
+      </c>
       <c r="K1614" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1615" spans="2:11" x14ac:dyDescent="0.25">
@@ -44874,63 +44851,64 @@
         <v>29</v>
       </c>
       <c r="C1615">
-        <v>2632</v>
+        <v>2650</v>
       </c>
       <c r="D1615" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="F1615" t="s">
         <v>165</v>
       </c>
       <c r="G1615" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1615" s="2">
-        <v>0</v>
+        <v>1.1574074074074073E-5</v>
       </c>
       <c r="I1615" s="1">
         <v>46118.726967592593</v>
       </c>
       <c r="J1615">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1615" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1616" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1616" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1616">
-        <v>2494</v>
-      </c>
-      <c r="D1616" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1616" t="s">
+      <c r="H1616" s="2"/>
+      <c r="I1616" s="1"/>
+      <c r="K1616" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1617" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1617" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1617">
+        <v>2632</v>
+      </c>
+      <c r="D1617" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1617" t="s">
         <v>165</v>
       </c>
-      <c r="G1616" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1616" s="2">
-        <v>1.0416666666666667E-4</v>
-      </c>
-      <c r="I1616" s="1">
-        <v>46118.727662037039</v>
-      </c>
-      <c r="J1616">
-        <v>0</v>
-      </c>
-      <c r="K1616" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1617" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I1617" s="1"/>
+      <c r="G1617" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1617">
+        <v>0</v>
+      </c>
+      <c r="I1617" s="1">
+        <v>46118.726967592593</v>
+      </c>
+      <c r="J1617">
+        <v>3</v>
+      </c>
       <c r="K1617" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1618" spans="2:11" x14ac:dyDescent="0.25">
@@ -44938,57 +44916,35 @@
         <v>29</v>
       </c>
       <c r="C1618">
-        <v>2902</v>
+        <v>2494</v>
       </c>
       <c r="D1618" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="F1618" t="s">
         <v>165</v>
       </c>
       <c r="G1618" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1618" s="2">
-        <v>0</v>
+        <v>1.0416666666666667E-4</v>
       </c>
       <c r="I1618" s="1">
-        <v>46118.728356481479</v>
+        <v>46118.727662037039</v>
       </c>
       <c r="J1618">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1618" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1619" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1619" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1619">
-        <v>2633</v>
-      </c>
-      <c r="D1619" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1619" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1619" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1619" s="2">
-        <v>1.1284722222222222E-2</v>
-      </c>
-      <c r="I1619" s="1">
-        <v>46118.728356481479</v>
-      </c>
-      <c r="J1619">
-        <v>1</v>
-      </c>
+      <c r="H1619" s="2"/>
+      <c r="I1619" s="1"/>
       <c r="K1619" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1620" spans="2:11" x14ac:dyDescent="0.25">
@@ -44996,10 +44952,10 @@
         <v>29</v>
       </c>
       <c r="C1620">
-        <v>2115</v>
+        <v>2902</v>
       </c>
       <c r="D1620" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="F1620" t="s">
         <v>165</v>
@@ -45011,10 +44967,10 @@
         <v>0</v>
       </c>
       <c r="I1620" s="1">
-        <v>46118.729050925926</v>
+        <v>46118.728356481479</v>
       </c>
       <c r="J1620">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1620" t="s">
         <v>11</v>
@@ -45025,25 +44981,25 @@
         <v>29</v>
       </c>
       <c r="C1621">
-        <v>2081</v>
+        <v>2633</v>
       </c>
       <c r="D1621" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F1621" t="s">
         <v>165</v>
       </c>
       <c r="G1621" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1621" s="2">
-        <v>0</v>
+        <v>1.1284722222222222E-2</v>
       </c>
       <c r="I1621" s="1">
-        <v>46118.729745370372</v>
+        <v>46118.728356481479</v>
       </c>
       <c r="J1621">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1621" t="s">
         <v>11</v>
@@ -45054,10 +45010,10 @@
         <v>29</v>
       </c>
       <c r="C1622">
-        <v>2458</v>
+        <v>2115</v>
       </c>
       <c r="D1622" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="F1622" t="s">
         <v>165</v>
@@ -45069,10 +45025,10 @@
         <v>0</v>
       </c>
       <c r="I1622" s="1">
-        <v>46118.729745370372</v>
+        <v>46118.729050925926</v>
       </c>
       <c r="J1622">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1622" t="s">
         <v>11</v>
@@ -45083,25 +45039,25 @@
         <v>29</v>
       </c>
       <c r="C1623">
-        <v>2635</v>
+        <v>2081</v>
       </c>
       <c r="D1623" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F1623" t="s">
         <v>165</v>
       </c>
       <c r="G1623" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1623" s="2">
-        <v>7.4074074074074077E-3</v>
+        <v>0</v>
       </c>
       <c r="I1623" s="1">
-        <v>46118.730439814812</v>
+        <v>46118.729745370372</v>
       </c>
       <c r="J1623">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1623" t="s">
         <v>11</v>
@@ -45112,25 +45068,25 @@
         <v>29</v>
       </c>
       <c r="C1624">
-        <v>3776</v>
+        <v>2458</v>
       </c>
       <c r="D1624" t="s">
-        <v>146</v>
+        <v>99</v>
       </c>
       <c r="F1624" t="s">
         <v>165</v>
       </c>
       <c r="G1624" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1624" s="2">
-        <v>8.6342592592592599E-3</v>
+        <v>0</v>
       </c>
       <c r="I1624" s="1">
-        <v>46118.731134259258</v>
+        <v>46118.729745370372</v>
       </c>
       <c r="J1624">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1624" t="s">
         <v>11</v>
@@ -45141,10 +45097,10 @@
         <v>29</v>
       </c>
       <c r="C1625">
-        <v>2247</v>
+        <v>2635</v>
       </c>
       <c r="D1625" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="F1625" t="s">
         <v>165</v>
@@ -45153,13 +45109,13 @@
         <v>10</v>
       </c>
       <c r="H1625" s="2">
-        <v>9.1550925925925931E-3</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="I1625" s="1">
-        <v>46118.731134259258</v>
+        <v>46118.730439814812</v>
       </c>
       <c r="J1625">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1625" t="s">
         <v>11</v>
@@ -45170,35 +45126,57 @@
         <v>29</v>
       </c>
       <c r="C1626">
-        <v>2651</v>
+        <v>3776</v>
       </c>
       <c r="D1626" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="F1626" t="s">
         <v>165</v>
       </c>
       <c r="G1626" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1626" s="2">
-        <v>5.8692129629629629E-2</v>
+        <v>8.6342592592592599E-3</v>
       </c>
       <c r="I1626" s="1">
-        <v>46118.731828703705</v>
+        <v>46118.731134259258</v>
       </c>
       <c r="J1626">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1626" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1627" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1627" s="2"/>
-      <c r="I1627" s="1"/>
+      <c r="B1627" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1627">
+        <v>2247</v>
+      </c>
+      <c r="D1627" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1627" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1627" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1627" s="2">
+        <v>9.1550925925925931E-3</v>
+      </c>
+      <c r="I1627" s="1">
+        <v>46118.731134259258</v>
+      </c>
+      <c r="J1627">
+        <v>0</v>
+      </c>
       <c r="K1627" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1628" spans="2:11" x14ac:dyDescent="0.25">
@@ -45206,57 +45184,35 @@
         <v>29</v>
       </c>
       <c r="C1628">
-        <v>2116</v>
+        <v>2651</v>
       </c>
       <c r="D1628" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="F1628" t="s">
         <v>165</v>
       </c>
       <c r="G1628" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1628" s="2">
-        <v>6.4930555555555557E-3</v>
+        <v>5.8692129629629629E-2</v>
       </c>
       <c r="I1628" s="1">
         <v>46118.731828703705</v>
       </c>
       <c r="J1628">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1628" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1629" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1629" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1629">
-        <v>2053</v>
-      </c>
-      <c r="D1629" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1629" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1629" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1629" s="2">
-        <v>8.4953703703703701E-3</v>
-      </c>
-      <c r="I1629" s="1">
-        <v>46118.732523148145</v>
-      </c>
-      <c r="J1629">
-        <v>0</v>
-      </c>
+      <c r="H1629" s="2"/>
+      <c r="I1629" s="1"/>
       <c r="K1629" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1630" spans="2:11" x14ac:dyDescent="0.25">
@@ -45264,25 +45220,25 @@
         <v>29</v>
       </c>
       <c r="C1630">
-        <v>2503</v>
+        <v>2116</v>
       </c>
       <c r="D1630" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F1630" t="s">
         <v>165</v>
       </c>
       <c r="G1630" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1630">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1630" s="2">
+        <v>6.4930555555555557E-3</v>
       </c>
       <c r="I1630" s="1">
-        <v>46118.732523148145</v>
+        <v>46118.731828703705</v>
       </c>
       <c r="J1630">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1630" t="s">
         <v>11</v>
@@ -45293,35 +45249,57 @@
         <v>29</v>
       </c>
       <c r="C1631">
-        <v>2493</v>
+        <v>2053</v>
       </c>
       <c r="D1631" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F1631" t="s">
         <v>165</v>
       </c>
       <c r="G1631" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1631" s="2">
-        <v>0</v>
+        <v>8.4953703703703701E-3</v>
       </c>
       <c r="I1631" s="1">
-        <v>46118.753472222219</v>
+        <v>46118.732523148145</v>
       </c>
       <c r="J1631">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1631" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1632" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1632" s="2"/>
-      <c r="I1632" s="1"/>
+      <c r="B1632" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1632">
+        <v>2503</v>
+      </c>
+      <c r="D1632" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1632" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1632" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1632" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1632" s="1">
+        <v>46118.732523148145</v>
+      </c>
+      <c r="J1632">
+        <v>3</v>
+      </c>
       <c r="K1632" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1633" spans="2:11" x14ac:dyDescent="0.25">
@@ -45329,57 +45307,35 @@
         <v>29</v>
       </c>
       <c r="C1633">
-        <v>5388</v>
+        <v>2493</v>
       </c>
       <c r="D1633" t="s">
-        <v>166</v>
+        <v>61</v>
       </c>
       <c r="F1633" t="s">
         <v>165</v>
       </c>
       <c r="G1633" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H1633" s="2">
-        <v>8.4375000000000006E-3</v>
+        <v>0</v>
       </c>
       <c r="I1633" s="1">
-        <v>46118.754166666666</v>
+        <v>46118.753472222219</v>
       </c>
       <c r="J1633">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1633" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1634" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1634" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1634">
-        <v>5038</v>
-      </c>
-      <c r="D1634" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1634" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1634" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1634" s="2">
-        <v>7.951388888888888E-3</v>
-      </c>
-      <c r="I1634" s="1">
-        <v>46118.754166666666</v>
-      </c>
-      <c r="J1634">
-        <v>2</v>
-      </c>
+      <c r="H1634" s="2"/>
+      <c r="I1634" s="1"/>
       <c r="K1634" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1635" spans="2:11" x14ac:dyDescent="0.25">
@@ -45387,25 +45343,25 @@
         <v>29</v>
       </c>
       <c r="C1635">
-        <v>4961</v>
+        <v>5388</v>
       </c>
       <c r="D1635" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F1635" t="s">
         <v>165</v>
       </c>
       <c r="G1635" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1635">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1635" s="2">
+        <v>8.4375000000000006E-3</v>
       </c>
       <c r="I1635" s="1">
-        <v>46118.754861111112</v>
+        <v>46118.754166666666</v>
       </c>
       <c r="J1635">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1635" t="s">
         <v>11</v>
@@ -45416,22 +45372,22 @@
         <v>29</v>
       </c>
       <c r="C1636">
-        <v>2497</v>
+        <v>5038</v>
       </c>
       <c r="D1636" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="F1636" t="s">
         <v>165</v>
       </c>
       <c r="G1636" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1636" s="2">
-        <v>0</v>
+        <v>7.951388888888888E-3</v>
       </c>
       <c r="I1636" s="1">
-        <v>46118.755555555559</v>
+        <v>46118.754166666666</v>
       </c>
       <c r="J1636">
         <v>2</v>
@@ -45445,25 +45401,25 @@
         <v>29</v>
       </c>
       <c r="C1637">
-        <v>4946</v>
+        <v>4961</v>
       </c>
       <c r="D1637" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F1637" t="s">
         <v>165</v>
       </c>
       <c r="G1637" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1637" s="2">
-        <v>7.0486111111111114E-3</v>
+        <v>0</v>
       </c>
       <c r="I1637" s="1">
-        <v>46118.755555555559</v>
+        <v>46118.754861111112</v>
       </c>
       <c r="J1637">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1637" t="s">
         <v>11</v>
@@ -45474,10 +45430,10 @@
         <v>29</v>
       </c>
       <c r="C1638">
-        <v>2118</v>
+        <v>2497</v>
       </c>
       <c r="D1638" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F1638" t="s">
         <v>165</v>
@@ -45489,10 +45445,10 @@
         <v>0</v>
       </c>
       <c r="I1638" s="1">
-        <v>46118.756249999999</v>
+        <v>46118.755555555559</v>
       </c>
       <c r="J1638">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1638" t="s">
         <v>11</v>
@@ -45503,25 +45459,25 @@
         <v>29</v>
       </c>
       <c r="C1639">
-        <v>2089</v>
+        <v>4946</v>
       </c>
       <c r="D1639" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="F1639" t="s">
         <v>165</v>
       </c>
       <c r="G1639" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1639">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1639" s="2">
+        <v>7.0486111111111114E-3</v>
       </c>
       <c r="I1639" s="1">
-        <v>46118.756944444445</v>
+        <v>46118.755555555559</v>
       </c>
       <c r="J1639">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1639" t="s">
         <v>11</v>
@@ -45532,10 +45488,10 @@
         <v>29</v>
       </c>
       <c r="C1640">
-        <v>3206</v>
+        <v>2118</v>
       </c>
       <c r="D1640" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="F1640" t="s">
         <v>165</v>
@@ -45547,10 +45503,10 @@
         <v>0</v>
       </c>
       <c r="I1640" s="1">
-        <v>46118.757638888892</v>
+        <v>46118.756249999999</v>
       </c>
       <c r="J1640">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1640" t="s">
         <v>11</v>
@@ -45561,10 +45517,10 @@
         <v>29</v>
       </c>
       <c r="C1641">
-        <v>2905</v>
+        <v>2089</v>
       </c>
       <c r="D1641" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F1641" t="s">
         <v>165</v>
@@ -45573,13 +45529,13 @@
         <v>10</v>
       </c>
       <c r="H1641" s="2">
-        <v>7.2106481481481483E-3</v>
+        <v>8.3333333333333332E-3</v>
       </c>
       <c r="I1641" s="1">
-        <v>46118.757638888892</v>
+        <v>46118.756944444445</v>
       </c>
       <c r="J1641">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1641" t="s">
         <v>11</v>
@@ -45590,10 +45546,10 @@
         <v>29</v>
       </c>
       <c r="C1642">
-        <v>2652</v>
+        <v>3206</v>
       </c>
       <c r="D1642" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="F1642" t="s">
         <v>165</v>
@@ -45605,10 +45561,10 @@
         <v>0</v>
       </c>
       <c r="I1642" s="1">
-        <v>46118.758333333331</v>
+        <v>46118.757638888892</v>
       </c>
       <c r="J1642">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1642" t="s">
         <v>11</v>
@@ -45619,10 +45575,10 @@
         <v>29</v>
       </c>
       <c r="C1643">
-        <v>2511</v>
+        <v>2905</v>
       </c>
       <c r="D1643" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F1643" t="s">
         <v>165</v>
@@ -45631,10 +45587,10 @@
         <v>10</v>
       </c>
       <c r="H1643" s="2">
-        <v>1.0127314814814815E-2</v>
+        <v>7.2106481481481483E-3</v>
       </c>
       <c r="I1643" s="1">
-        <v>46118.758333333331</v>
+        <v>46118.757638888892</v>
       </c>
       <c r="J1643">
         <v>1</v>
@@ -45648,10 +45604,10 @@
         <v>29</v>
       </c>
       <c r="C1644">
-        <v>2499</v>
+        <v>2652</v>
       </c>
       <c r="D1644" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="F1644" t="s">
         <v>165</v>
@@ -45663,10 +45619,10 @@
         <v>0</v>
       </c>
       <c r="I1644" s="1">
-        <v>46118.759027777778</v>
+        <v>46118.758333333331</v>
       </c>
       <c r="J1644">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1644" t="s">
         <v>11</v>
@@ -45677,25 +45633,25 @@
         <v>29</v>
       </c>
       <c r="C1645">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="D1645" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="F1645" t="s">
         <v>165</v>
       </c>
       <c r="G1645" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1645" s="2">
-        <v>0</v>
+        <v>1.0127314814814815E-2</v>
       </c>
       <c r="I1645" s="1">
-        <v>46118.759722222225</v>
+        <v>46118.758333333331</v>
       </c>
       <c r="J1645">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1645" t="s">
         <v>11</v>
@@ -45706,35 +45662,57 @@
         <v>29</v>
       </c>
       <c r="C1646">
-        <v>3239</v>
+        <v>2499</v>
       </c>
       <c r="D1646" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="F1646" t="s">
         <v>165</v>
       </c>
       <c r="G1646" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H1646" s="2">
-        <v>1.0972222222222222E-2</v>
+        <v>0</v>
       </c>
       <c r="I1646" s="1">
+        <v>46118.759027777778</v>
+      </c>
+      <c r="J1646">
+        <v>3</v>
+      </c>
+      <c r="K1646" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1647" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1647" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1647">
+        <v>2510</v>
+      </c>
+      <c r="D1647" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1647" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1647" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1647" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1647" s="1">
         <v>46118.759722222225</v>
       </c>
-      <c r="J1646">
-        <v>0</v>
-      </c>
-      <c r="K1646" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1647" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1647" s="2"/>
-      <c r="I1647" s="1"/>
+      <c r="J1647">
+        <v>3</v>
+      </c>
       <c r="K1647" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1648" spans="2:11" x14ac:dyDescent="0.25">
@@ -45742,57 +45720,35 @@
         <v>29</v>
       </c>
       <c r="C1648">
-        <v>2088</v>
+        <v>3239</v>
       </c>
       <c r="D1648" t="s">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="F1648" t="s">
         <v>165</v>
       </c>
       <c r="G1648" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1648" s="2">
-        <v>0</v>
+        <v>1.0972222222222222E-2</v>
       </c>
       <c r="I1648" s="1">
-        <v>46118.760416666664</v>
+        <v>46118.759722222225</v>
       </c>
       <c r="J1648">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1648" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1649" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1649" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1649">
-        <v>2903</v>
-      </c>
-      <c r="D1649" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1649" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1649" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1649" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1649" s="1">
-        <v>46118.761111111111</v>
-      </c>
-      <c r="J1649">
-        <v>2</v>
-      </c>
+      <c r="H1649" s="2"/>
+      <c r="I1649" s="1"/>
       <c r="K1649" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1650" spans="2:11" x14ac:dyDescent="0.25">
@@ -45800,25 +45756,25 @@
         <v>29</v>
       </c>
       <c r="C1650">
-        <v>2508</v>
+        <v>2088</v>
       </c>
       <c r="D1650" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F1650" t="s">
         <v>165</v>
       </c>
       <c r="G1650" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1650" s="2">
-        <v>8.611111111111111E-3</v>
+        <v>0</v>
       </c>
       <c r="I1650" s="1">
-        <v>46118.761111111111</v>
+        <v>46118.760416666664</v>
       </c>
       <c r="J1650">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1650" t="s">
         <v>11</v>
@@ -45829,25 +45785,25 @@
         <v>29</v>
       </c>
       <c r="C1651">
-        <v>2648</v>
+        <v>2903</v>
       </c>
       <c r="D1651" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="F1651" t="s">
         <v>165</v>
       </c>
       <c r="G1651" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1651" s="2">
-        <v>7.6157407407407406E-3</v>
+        <v>0</v>
       </c>
       <c r="I1651" s="1">
-        <v>46118.761805555558</v>
+        <v>46118.761111111111</v>
       </c>
       <c r="J1651">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1651" t="s">
         <v>11</v>
@@ -45858,22 +45814,22 @@
         <v>29</v>
       </c>
       <c r="C1652">
-        <v>2459</v>
+        <v>2508</v>
       </c>
       <c r="D1652" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F1652" t="s">
         <v>165</v>
       </c>
       <c r="G1652" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1652" s="2">
-        <v>0</v>
+        <v>8.611111111111111E-3</v>
       </c>
       <c r="I1652" s="1">
-        <v>46118.762499999997</v>
+        <v>46118.761111111111</v>
       </c>
       <c r="J1652">
         <v>2</v>
@@ -45887,34 +45843,57 @@
         <v>29</v>
       </c>
       <c r="C1653">
-        <v>2483</v>
+        <v>2648</v>
       </c>
       <c r="D1653" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="F1653" t="s">
         <v>165</v>
       </c>
       <c r="G1653" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1653" s="2">
-        <v>1.0416666666666667E-4</v>
+        <v>7.6157407407407406E-3</v>
       </c>
       <c r="I1653" s="1">
+        <v>46118.761805555558</v>
+      </c>
+      <c r="J1653">
+        <v>2</v>
+      </c>
+      <c r="K1653" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1654" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1654" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1654">
+        <v>2459</v>
+      </c>
+      <c r="D1654" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1654" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1654" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1654">
+        <v>0</v>
+      </c>
+      <c r="I1654" s="1">
         <v>46118.762499999997</v>
       </c>
-      <c r="J1653">
-        <v>1</v>
-      </c>
-      <c r="K1653" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1654" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I1654" s="1"/>
+      <c r="J1654">
+        <v>3</v>
+      </c>
       <c r="K1654" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1655" spans="2:11" x14ac:dyDescent="0.25">
@@ -45922,57 +45901,35 @@
         <v>29</v>
       </c>
       <c r="C1655">
-        <v>2113</v>
+        <v>2483</v>
       </c>
       <c r="D1655" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F1655" t="s">
         <v>165</v>
       </c>
       <c r="G1655" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1655" s="2">
-        <v>0</v>
+        <v>1.0416666666666667E-4</v>
       </c>
       <c r="I1655" s="1">
-        <v>46118.763194444444</v>
+        <v>46118.762499999997</v>
       </c>
       <c r="J1655">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1655" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1656" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1656" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1656">
-        <v>2490</v>
-      </c>
-      <c r="D1656" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1656" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1656" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1656" s="2">
-        <v>8.0902777777777778E-3</v>
-      </c>
-      <c r="I1656" s="1">
-        <v>46118.763888888891</v>
-      </c>
-      <c r="J1656">
-        <v>2</v>
-      </c>
+      <c r="H1656" s="2"/>
+      <c r="I1656" s="1"/>
       <c r="K1656" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1657" spans="2:11" x14ac:dyDescent="0.25">
@@ -45980,10 +45937,10 @@
         <v>29</v>
       </c>
       <c r="C1657">
-        <v>2638</v>
+        <v>2113</v>
       </c>
       <c r="D1657" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F1657" t="s">
         <v>165</v>
@@ -45995,10 +45952,10 @@
         <v>0</v>
       </c>
       <c r="I1657" s="1">
-        <v>46118.763888888891</v>
+        <v>46118.763194444444</v>
       </c>
       <c r="J1657">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1657" t="s">
         <v>11</v>
@@ -46009,22 +45966,22 @@
         <v>29</v>
       </c>
       <c r="C1658">
-        <v>4919</v>
+        <v>2490</v>
       </c>
       <c r="D1658" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="F1658" t="s">
         <v>165</v>
       </c>
       <c r="G1658" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1658">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1658" s="2">
+        <v>8.0902777777777778E-3</v>
       </c>
       <c r="I1658" s="1">
-        <v>46118.76458333333</v>
+        <v>46118.763888888891</v>
       </c>
       <c r="J1658">
         <v>2</v>
@@ -46038,25 +45995,25 @@
         <v>29</v>
       </c>
       <c r="C1659">
-        <v>2509</v>
+        <v>2638</v>
       </c>
       <c r="D1659" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F1659" t="s">
         <v>165</v>
       </c>
       <c r="G1659" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1659" s="2">
-        <v>7.3379629629629628E-3</v>
+        <v>0</v>
       </c>
       <c r="I1659" s="1">
-        <v>46118.765277777777</v>
+        <v>46118.763888888891</v>
       </c>
       <c r="J1659">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1659" t="s">
         <v>11</v>
@@ -46067,57 +46024,35 @@
         <v>29</v>
       </c>
       <c r="C1660">
-        <v>2901</v>
+        <v>4919</v>
       </c>
       <c r="D1660" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="F1660" t="s">
         <v>165</v>
       </c>
       <c r="G1660" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H1660" s="2">
-        <v>1.0636574074074074E-2</v>
+        <v>0</v>
       </c>
       <c r="I1660" s="1">
-        <v>46118.765277777777</v>
+        <v>46118.76458333333</v>
       </c>
       <c r="J1660">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K1660" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1661" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1661" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1661">
-        <v>3130</v>
-      </c>
-      <c r="D1661" t="s">
-        <v>135</v>
-      </c>
-      <c r="F1661" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1661" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1661" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1661" s="1">
-        <v>46118.765972222223</v>
-      </c>
-      <c r="J1661">
-        <v>2</v>
-      </c>
+      <c r="H1661" s="2"/>
+      <c r="I1661" s="1"/>
       <c r="K1661" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1662" spans="2:11" x14ac:dyDescent="0.25">
@@ -46125,25 +46060,25 @@
         <v>29</v>
       </c>
       <c r="C1662">
-        <v>2653</v>
+        <v>2509</v>
       </c>
       <c r="D1662" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="F1662" t="s">
         <v>165</v>
       </c>
       <c r="G1662" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1662" s="2">
-        <v>0</v>
+        <v>7.3379629629629628E-3</v>
       </c>
       <c r="I1662" s="1">
-        <v>46118.765972222223</v>
+        <v>46118.765277777777</v>
       </c>
       <c r="J1662">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1662" t="s">
         <v>11</v>
@@ -46154,10 +46089,10 @@
         <v>29</v>
       </c>
       <c r="C1663">
-        <v>2485</v>
+        <v>2901</v>
       </c>
       <c r="D1663" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="F1663" t="s">
         <v>165</v>
@@ -46166,13 +46101,13 @@
         <v>10</v>
       </c>
       <c r="H1663" s="2">
-        <v>7.9976851851851858E-3</v>
+        <v>1.0636574074074074E-2</v>
       </c>
       <c r="I1663" s="1">
-        <v>46118.76666666667</v>
+        <v>46118.765277777777</v>
       </c>
       <c r="J1663">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1663" t="s">
         <v>11</v>
@@ -46183,25 +46118,25 @@
         <v>29</v>
       </c>
       <c r="C1664">
-        <v>2074</v>
+        <v>3130</v>
       </c>
       <c r="D1664" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="F1664" t="s">
         <v>165</v>
       </c>
       <c r="G1664" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1664" s="2">
-        <v>6.8402777777777776E-3</v>
+        <v>0</v>
       </c>
       <c r="I1664" s="1">
-        <v>46118.767361111109</v>
+        <v>46118.765972222223</v>
       </c>
       <c r="J1664">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1664" t="s">
         <v>11</v>
@@ -46212,10 +46147,10 @@
         <v>29</v>
       </c>
       <c r="C1665">
-        <v>2486</v>
+        <v>2653</v>
       </c>
       <c r="D1665" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="F1665" t="s">
         <v>165</v>
@@ -46227,10 +46162,10 @@
         <v>0</v>
       </c>
       <c r="I1665" s="1">
-        <v>46118.767361111109</v>
+        <v>46118.765972222223</v>
       </c>
       <c r="J1665">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1665" t="s">
         <v>11</v>
@@ -46241,10 +46176,10 @@
         <v>29</v>
       </c>
       <c r="C1666">
-        <v>2065</v>
+        <v>2485</v>
       </c>
       <c r="D1666" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="F1666" t="s">
         <v>165</v>
@@ -46253,10 +46188,10 @@
         <v>10</v>
       </c>
       <c r="H1666" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>7.9976851851851858E-3</v>
       </c>
       <c r="I1666" s="1">
-        <v>46118.768055555556</v>
+        <v>46118.76666666667</v>
       </c>
       <c r="J1666">
         <v>1</v>
@@ -46270,10 +46205,10 @@
         <v>29</v>
       </c>
       <c r="C1667">
-        <v>2649</v>
+        <v>2074</v>
       </c>
       <c r="D1667" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="F1667" t="s">
         <v>165</v>
@@ -46282,13 +46217,13 @@
         <v>10</v>
       </c>
       <c r="H1667" s="2">
-        <v>7.3495370370370372E-3</v>
+        <v>6.8402777777777776E-3</v>
       </c>
       <c r="I1667" s="1">
-        <v>46118.768055555556</v>
+        <v>46118.767361111109</v>
       </c>
       <c r="J1667">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1667" t="s">
         <v>11</v>
@@ -46299,10 +46234,10 @@
         <v>29</v>
       </c>
       <c r="C1668">
-        <v>2611</v>
+        <v>2486</v>
       </c>
       <c r="D1668" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F1668" t="s">
         <v>165</v>
@@ -46314,10 +46249,10 @@
         <v>0</v>
       </c>
       <c r="I1668" s="1">
-        <v>46118.768750000003</v>
+        <v>46118.767361111109</v>
       </c>
       <c r="J1668">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1668" t="s">
         <v>11</v>
@@ -46328,41 +46263,116 @@
         <v>29</v>
       </c>
       <c r="C1669">
-        <v>2498</v>
+        <v>2065</v>
       </c>
       <c r="D1669" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F1669" t="s">
         <v>165</v>
       </c>
       <c r="G1669" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1669" s="2">
-        <v>0</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I1669" s="1">
+        <v>46118.768055555556</v>
+      </c>
+      <c r="J1669">
+        <v>1</v>
+      </c>
+      <c r="K1669" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1670" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1670" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1670">
+        <v>2649</v>
+      </c>
+      <c r="D1670" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1670" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1670" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1670" s="2">
+        <v>7.3495370370370372E-3</v>
+      </c>
+      <c r="I1670" s="1">
+        <v>46118.768055555556</v>
+      </c>
+      <c r="J1670">
+        <v>2</v>
+      </c>
+      <c r="K1670" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1671" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1671" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1671">
+        <v>2611</v>
+      </c>
+      <c r="D1671" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1671" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1671" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1671" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1671" s="1">
+        <v>46118.768750000003</v>
+      </c>
+      <c r="J1671">
+        <v>3</v>
+      </c>
+      <c r="K1671" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1672" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1672" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1672">
+        <v>2498</v>
+      </c>
+      <c r="D1672" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1672" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1672" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1672" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1672" s="1">
         <v>46118.769444444442</v>
       </c>
-      <c r="J1669">
-        <v>2</v>
-      </c>
-      <c r="K1669" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1670" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1670" s="2"/>
-      <c r="I1670" s="1"/>
-    </row>
-    <row r="1671" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1671" s="2"/>
-      <c r="I1671" s="1"/>
-    </row>
-    <row r="1672" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1672" s="2"/>
-      <c r="I1672" s="1"/>
+      <c r="J1672">
+        <v>3</v>
+      </c>
+      <c r="K1672" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1673" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1673" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Apple Towing - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC2268C-84F4-40AE-B66D-B3EA127E6241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C72150C-73BC-4900-9962-5E4D46CE886E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7813" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8167" uniqueCount="169">
   <si>
     <t>Company Name</t>
   </si>
@@ -541,6 +541,12 @@
   <si>
     <t>Jose Ramirez</t>
   </si>
+  <si>
+    <t>LaMarcus Tucker</t>
+  </si>
+  <si>
+    <t>William Cage</t>
+  </si>
 </sst>
 </file>
 
@@ -44291,7 +44297,7 @@
         <v>46118.717939814815</v>
       </c>
       <c r="J1592">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1592" t="s">
         <v>11</v>
@@ -44349,7 +44355,7 @@
         <v>46118.719328703701</v>
       </c>
       <c r="J1594">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1594" t="s">
         <v>11</v>
@@ -44407,7 +44413,7 @@
         <v>46118.720023148147</v>
       </c>
       <c r="J1596">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1596" t="s">
         <v>11</v>
@@ -44530,7 +44536,7 @@
         <v>46118.72210648148</v>
       </c>
       <c r="J1601">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1601" t="s">
         <v>11</v>
@@ -44550,48 +44556,26 @@
         <v>165</v>
       </c>
       <c r="G1602" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H1602" s="2">
-        <v>0</v>
+        <v>6.9444444444444444E-5</v>
       </c>
       <c r="I1602" s="1">
         <v>46118.72210648148</v>
       </c>
       <c r="J1602">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1602" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1603" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1603" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1603">
-        <v>2504</v>
-      </c>
-      <c r="D1603" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1603" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1603" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1603" s="2">
-        <v>3.0787037037037037E-3</v>
-      </c>
-      <c r="I1603" s="1">
-        <v>46118.722800925927</v>
-      </c>
-      <c r="J1603">
-        <v>1</v>
-      </c>
+      <c r="H1603" s="2"/>
+      <c r="I1603" s="1"/>
       <c r="K1603" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1604" spans="2:11" x14ac:dyDescent="0.25">
@@ -44599,99 +44583,100 @@
         <v>29</v>
       </c>
       <c r="C1604">
-        <v>2457</v>
+        <v>2504</v>
       </c>
       <c r="D1604" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="F1604" t="s">
         <v>165</v>
       </c>
       <c r="G1604" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1604" s="2">
+        <v>3.0787037037037037E-3</v>
+      </c>
+      <c r="I1604" s="1">
+        <v>46118.722800925927</v>
+      </c>
+      <c r="J1604">
+        <v>1</v>
+      </c>
+      <c r="K1604" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1605" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1605" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1605">
+        <v>2457</v>
+      </c>
+      <c r="D1605" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1605" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1605" t="s">
         <v>12</v>
       </c>
-      <c r="H1604" s="2">
+      <c r="H1605" s="2">
         <v>4.0509259259259258E-4</v>
       </c>
-      <c r="I1604" s="1">
+      <c r="I1605" s="1">
         <v>46118.723495370374</v>
       </c>
-      <c r="J1604">
+      <c r="J1605">
         <v>2</v>
       </c>
-      <c r="K1604" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1605" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I1605" s="1"/>
       <c r="K1605" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1606" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1606" s="2"/>
+      <c r="I1606" s="1"/>
+      <c r="K1606" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="1606" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1606" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1606">
+    <row r="1607" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1607" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1607">
         <v>2612</v>
       </c>
-      <c r="D1606" t="s">
+      <c r="D1607" t="s">
         <v>42</v>
       </c>
-      <c r="F1606" t="s">
+      <c r="F1607" t="s">
         <v>165</v>
       </c>
-      <c r="G1606" t="s">
+      <c r="G1607" t="s">
         <v>12</v>
       </c>
-      <c r="H1606" s="2">
+      <c r="H1607" s="2">
         <v>1.3888888888888889E-4</v>
       </c>
-      <c r="I1606" s="1">
+      <c r="I1607" s="1">
         <v>46118.723495370374</v>
       </c>
-      <c r="J1606">
+      <c r="J1607">
         <v>3</v>
       </c>
-      <c r="K1606" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1607" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1607" s="2"/>
-      <c r="I1607" s="1"/>
       <c r="K1607" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1608" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1608" s="2"/>
+      <c r="I1608" s="1"/>
+      <c r="K1608" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1608" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1608" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1608">
-        <v>5090</v>
-      </c>
-      <c r="D1608" t="s">
-        <v>162</v>
-      </c>
-      <c r="F1608" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1608" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1608" s="2">
-        <v>4.1666666666666666E-3</v>
-      </c>
-      <c r="I1608" s="1">
-        <v>46118.724189814813</v>
-      </c>
-      <c r="J1608">
-        <v>2</v>
-      </c>
-      <c r="K1608" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1609" spans="2:11" x14ac:dyDescent="0.25">
@@ -44699,25 +44684,25 @@
         <v>29</v>
       </c>
       <c r="C1609">
-        <v>2634</v>
+        <v>5090</v>
       </c>
       <c r="D1609" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
       <c r="F1609" t="s">
         <v>165</v>
       </c>
       <c r="G1609" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1609" s="2">
-        <v>0</v>
+        <v>4.1666666666666666E-3</v>
       </c>
       <c r="I1609" s="1">
-        <v>46118.72488425926</v>
+        <v>46118.724189814813</v>
       </c>
       <c r="J1609">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1609" t="s">
         <v>11</v>
@@ -44728,25 +44713,25 @@
         <v>29</v>
       </c>
       <c r="C1610">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="D1610" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="F1610" t="s">
         <v>165</v>
       </c>
       <c r="G1610" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1610" s="2">
-        <v>9.0740740740740747E-3</v>
+        <v>0</v>
       </c>
       <c r="I1610" s="1">
         <v>46118.72488425926</v>
       </c>
       <c r="J1610">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1610" t="s">
         <v>11</v>
@@ -44757,64 +44742,64 @@
         <v>29</v>
       </c>
       <c r="C1611">
-        <v>2487</v>
+        <v>2636</v>
       </c>
       <c r="D1611" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="F1611" t="s">
         <v>165</v>
       </c>
       <c r="G1611" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1611" s="2">
+        <v>9.0740740740740747E-3</v>
+      </c>
+      <c r="I1611" s="1">
+        <v>46118.72488425926</v>
+      </c>
+      <c r="J1611">
+        <v>1</v>
+      </c>
+      <c r="K1611" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1612" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1612" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1612">
+        <v>2487</v>
+      </c>
+      <c r="D1612" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1612" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1612" t="s">
         <v>12</v>
       </c>
-      <c r="H1611" s="2">
+      <c r="H1612" s="2">
         <v>6.4814814814814813E-3</v>
       </c>
-      <c r="I1611" s="1">
+      <c r="I1612" s="1">
         <v>46118.725578703707</v>
       </c>
-      <c r="J1611">
-        <v>0</v>
-      </c>
-      <c r="K1611" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1612" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1612" s="2"/>
-      <c r="I1612" s="1"/>
+      <c r="J1612">
+        <v>0</v>
+      </c>
       <c r="K1612" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1613" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1613" s="2"/>
+      <c r="I1613" s="1"/>
+      <c r="K1613" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1613" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1613" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1613">
-        <v>2492</v>
-      </c>
-      <c r="D1613" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1613" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1613" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1613" s="2">
-        <v>7.7083333333333335E-3</v>
-      </c>
-      <c r="I1613" s="1">
-        <v>46118.725578703707</v>
-      </c>
-      <c r="J1613">
-        <v>3</v>
-      </c>
-      <c r="K1613" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1614" spans="2:11" x14ac:dyDescent="0.25">
@@ -44822,22 +44807,22 @@
         <v>29</v>
       </c>
       <c r="C1614">
-        <v>5065</v>
+        <v>2492</v>
       </c>
       <c r="D1614" t="s">
-        <v>163</v>
+        <v>46</v>
       </c>
       <c r="F1614" t="s">
         <v>165</v>
       </c>
       <c r="G1614" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1614" s="2">
-        <v>0</v>
+        <v>7.7083333333333335E-3</v>
       </c>
       <c r="I1614" s="1">
-        <v>46118.726273148146</v>
+        <v>46118.725578703707</v>
       </c>
       <c r="J1614">
         <v>3</v>
@@ -44851,64 +44836,63 @@
         <v>29</v>
       </c>
       <c r="C1615">
-        <v>2650</v>
+        <v>5065</v>
       </c>
       <c r="D1615" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="F1615" t="s">
         <v>165</v>
       </c>
       <c r="G1615" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1615" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1615" s="1">
+        <v>46118.726273148146</v>
+      </c>
+      <c r="J1615">
+        <v>4</v>
+      </c>
+      <c r="K1615" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1616" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1616" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1616">
+        <v>2650</v>
+      </c>
+      <c r="D1616" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1616" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1616" t="s">
         <v>12</v>
       </c>
-      <c r="H1615" s="2">
+      <c r="H1616" s="2">
         <v>1.1574074074074073E-5</v>
       </c>
-      <c r="I1615" s="1">
+      <c r="I1616" s="1">
         <v>46118.726967592593</v>
       </c>
-      <c r="J1615">
+      <c r="J1616">
         <v>1</v>
       </c>
-      <c r="K1615" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1616" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1616" s="2"/>
-      <c r="I1616" s="1"/>
       <c r="K1616" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1617" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="I1617" s="1"/>
+      <c r="K1617" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1617" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1617" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1617">
-        <v>2632</v>
-      </c>
-      <c r="D1617" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1617" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1617" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1617">
-        <v>0</v>
-      </c>
-      <c r="I1617" s="1">
-        <v>46118.726967592593</v>
-      </c>
-      <c r="J1617">
-        <v>3</v>
-      </c>
-      <c r="K1617" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1618" spans="2:11" x14ac:dyDescent="0.25">
@@ -44916,64 +44900,64 @@
         <v>29</v>
       </c>
       <c r="C1618">
-        <v>2494</v>
+        <v>2632</v>
       </c>
       <c r="D1618" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F1618" t="s">
         <v>165</v>
       </c>
       <c r="G1618" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1618" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1618" s="1">
+        <v>46118.726967592593</v>
+      </c>
+      <c r="J1618">
+        <v>4</v>
+      </c>
+      <c r="K1618" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1619" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1619" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1619">
+        <v>2494</v>
+      </c>
+      <c r="D1619" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1619" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1619" t="s">
         <v>12</v>
       </c>
-      <c r="H1618" s="2">
+      <c r="H1619" s="2">
         <v>1.0416666666666667E-4</v>
       </c>
-      <c r="I1618" s="1">
+      <c r="I1619" s="1">
         <v>46118.727662037039</v>
       </c>
-      <c r="J1618">
-        <v>0</v>
-      </c>
-      <c r="K1618" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1619" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1619" s="2"/>
-      <c r="I1619" s="1"/>
+      <c r="J1619">
+        <v>0</v>
+      </c>
       <c r="K1619" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1620" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1620" s="2"/>
+      <c r="I1620" s="1"/>
+      <c r="K1620" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1620" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1620" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1620">
-        <v>2902</v>
-      </c>
-      <c r="D1620" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1620" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1620" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1620" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1620" s="1">
-        <v>46118.728356481479</v>
-      </c>
-      <c r="J1620">
-        <v>3</v>
-      </c>
-      <c r="K1620" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1621" spans="2:11" x14ac:dyDescent="0.25">
@@ -44981,25 +44965,25 @@
         <v>29</v>
       </c>
       <c r="C1621">
-        <v>2633</v>
+        <v>2902</v>
       </c>
       <c r="D1621" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="F1621" t="s">
         <v>165</v>
       </c>
       <c r="G1621" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1621" s="2">
-        <v>1.1284722222222222E-2</v>
+        <v>0</v>
       </c>
       <c r="I1621" s="1">
         <v>46118.728356481479</v>
       </c>
       <c r="J1621">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1621" t="s">
         <v>11</v>
@@ -45010,25 +44994,25 @@
         <v>29</v>
       </c>
       <c r="C1622">
-        <v>2115</v>
+        <v>2633</v>
       </c>
       <c r="D1622" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F1622" t="s">
         <v>165</v>
       </c>
       <c r="G1622" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1622" s="2">
-        <v>0</v>
+        <v>1.1284722222222222E-2</v>
       </c>
       <c r="I1622" s="1">
-        <v>46118.729050925926</v>
+        <v>46118.728356481479</v>
       </c>
       <c r="J1622">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1622" t="s">
         <v>11</v>
@@ -45039,10 +45023,10 @@
         <v>29</v>
       </c>
       <c r="C1623">
-        <v>2081</v>
+        <v>2115</v>
       </c>
       <c r="D1623" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F1623" t="s">
         <v>165</v>
@@ -45054,10 +45038,10 @@
         <v>0</v>
       </c>
       <c r="I1623" s="1">
-        <v>46118.729745370372</v>
+        <v>46118.729050925926</v>
       </c>
       <c r="J1623">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1623" t="s">
         <v>11</v>
@@ -45068,10 +45052,10 @@
         <v>29</v>
       </c>
       <c r="C1624">
-        <v>2458</v>
+        <v>2081</v>
       </c>
       <c r="D1624" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="F1624" t="s">
         <v>165</v>
@@ -45086,7 +45070,7 @@
         <v>46118.729745370372</v>
       </c>
       <c r="J1624">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1624" t="s">
         <v>11</v>
@@ -45097,25 +45081,25 @@
         <v>29</v>
       </c>
       <c r="C1625">
-        <v>2635</v>
+        <v>2458</v>
       </c>
       <c r="D1625" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="F1625" t="s">
         <v>165</v>
       </c>
       <c r="G1625" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1625" s="2">
-        <v>7.4074074074074077E-3</v>
+        <v>0</v>
       </c>
       <c r="I1625" s="1">
-        <v>46118.730439814812</v>
+        <v>46118.729745370372</v>
       </c>
       <c r="J1625">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1625" t="s">
         <v>11</v>
@@ -45126,10 +45110,10 @@
         <v>29</v>
       </c>
       <c r="C1626">
-        <v>3776</v>
+        <v>2635</v>
       </c>
       <c r="D1626" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="F1626" t="s">
         <v>165</v>
@@ -45138,10 +45122,10 @@
         <v>10</v>
       </c>
       <c r="H1626" s="2">
-        <v>8.6342592592592599E-3</v>
+        <v>7.4074074074074077E-3</v>
       </c>
       <c r="I1626" s="1">
-        <v>46118.731134259258</v>
+        <v>46118.730439814812</v>
       </c>
       <c r="J1626">
         <v>1</v>
@@ -45155,10 +45139,10 @@
         <v>29</v>
       </c>
       <c r="C1627">
-        <v>2247</v>
+        <v>3776</v>
       </c>
       <c r="D1627" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="F1627" t="s">
         <v>165</v>
@@ -45167,13 +45151,13 @@
         <v>10</v>
       </c>
       <c r="H1627" s="2">
-        <v>9.1550925925925931E-3</v>
+        <v>8.6342592592592599E-3</v>
       </c>
       <c r="I1627" s="1">
         <v>46118.731134259258</v>
       </c>
       <c r="J1627">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1627" t="s">
         <v>11</v>
@@ -45184,64 +45168,64 @@
         <v>29</v>
       </c>
       <c r="C1628">
-        <v>2651</v>
+        <v>2247</v>
       </c>
       <c r="D1628" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="F1628" t="s">
         <v>165</v>
       </c>
       <c r="G1628" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1628" s="2">
+        <v>9.1550925925925931E-3</v>
+      </c>
+      <c r="I1628" s="1">
+        <v>46118.731134259258</v>
+      </c>
+      <c r="J1628">
+        <v>0</v>
+      </c>
+      <c r="K1628" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1629" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1629" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1629">
+        <v>2651</v>
+      </c>
+      <c r="D1629" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1629" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1629" t="s">
         <v>12</v>
       </c>
-      <c r="H1628" s="2">
+      <c r="H1629" s="2">
         <v>5.8692129629629629E-2</v>
       </c>
-      <c r="I1628" s="1">
+      <c r="I1629" s="1">
         <v>46118.731828703705</v>
       </c>
-      <c r="J1628">
-        <v>0</v>
-      </c>
-      <c r="K1628" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1629" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1629" s="2"/>
-      <c r="I1629" s="1"/>
+      <c r="J1629">
+        <v>0</v>
+      </c>
       <c r="K1629" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1630" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1630" s="2"/>
+      <c r="I1630" s="1"/>
+      <c r="K1630" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1630" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1630" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1630">
-        <v>2116</v>
-      </c>
-      <c r="D1630" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1630" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1630" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1630" s="2">
-        <v>6.4930555555555557E-3</v>
-      </c>
-      <c r="I1630" s="1">
-        <v>46118.731828703705</v>
-      </c>
-      <c r="J1630">
-        <v>1</v>
-      </c>
-      <c r="K1630" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1631" spans="2:11" x14ac:dyDescent="0.25">
@@ -45249,10 +45233,10 @@
         <v>29</v>
       </c>
       <c r="C1631">
-        <v>2053</v>
+        <v>2116</v>
       </c>
       <c r="D1631" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F1631" t="s">
         <v>165</v>
@@ -45261,13 +45245,13 @@
         <v>10</v>
       </c>
       <c r="H1631" s="2">
-        <v>8.4953703703703701E-3</v>
+        <v>6.4930555555555557E-3</v>
       </c>
       <c r="I1631" s="1">
-        <v>46118.732523148145</v>
+        <v>46118.731828703705</v>
       </c>
       <c r="J1631">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1631" t="s">
         <v>11</v>
@@ -45278,25 +45262,25 @@
         <v>29</v>
       </c>
       <c r="C1632">
-        <v>2503</v>
+        <v>2053</v>
       </c>
       <c r="D1632" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F1632" t="s">
         <v>165</v>
       </c>
       <c r="G1632" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1632" s="2">
-        <v>0</v>
+        <v>8.4953703703703701E-3</v>
       </c>
       <c r="I1632" s="1">
         <v>46118.732523148145</v>
       </c>
       <c r="J1632">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1632" t="s">
         <v>11</v>
@@ -45307,64 +45291,64 @@
         <v>29</v>
       </c>
       <c r="C1633">
-        <v>2493</v>
+        <v>2503</v>
       </c>
       <c r="D1633" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F1633" t="s">
         <v>165</v>
       </c>
       <c r="G1633" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1633" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1633" s="1">
+        <v>46118.732523148145</v>
+      </c>
+      <c r="J1633">
+        <v>4</v>
+      </c>
+      <c r="K1633" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1634" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1634" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1634">
+        <v>2493</v>
+      </c>
+      <c r="D1634" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1634" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1634" t="s">
         <v>12</v>
       </c>
-      <c r="H1633" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1633" s="1">
+      <c r="H1634" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1634" s="1">
         <v>46118.753472222219</v>
       </c>
-      <c r="J1633">
+      <c r="J1634">
         <v>1</v>
       </c>
-      <c r="K1633" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1634" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1634" s="2"/>
-      <c r="I1634" s="1"/>
       <c r="K1634" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1635" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1635" s="2"/>
+      <c r="I1635" s="1"/>
+      <c r="K1635" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1635" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1635" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1635">
-        <v>5388</v>
-      </c>
-      <c r="D1635" t="s">
-        <v>166</v>
-      </c>
-      <c r="F1635" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1635" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1635" s="2">
-        <v>8.4375000000000006E-3</v>
-      </c>
-      <c r="I1635" s="1">
-        <v>46118.754166666666</v>
-      </c>
-      <c r="J1635">
-        <v>0</v>
-      </c>
-      <c r="K1635" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1636" spans="2:11" x14ac:dyDescent="0.25">
@@ -45372,10 +45356,10 @@
         <v>29</v>
       </c>
       <c r="C1636">
-        <v>5038</v>
+        <v>5388</v>
       </c>
       <c r="D1636" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F1636" t="s">
         <v>165</v>
@@ -45384,13 +45368,13 @@
         <v>10</v>
       </c>
       <c r="H1636" s="2">
-        <v>7.951388888888888E-3</v>
+        <v>8.4375000000000006E-3</v>
       </c>
       <c r="I1636" s="1">
         <v>46118.754166666666</v>
       </c>
       <c r="J1636">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K1636" t="s">
         <v>11</v>
@@ -45401,25 +45385,25 @@
         <v>29</v>
       </c>
       <c r="C1637">
-        <v>4961</v>
+        <v>5038</v>
       </c>
       <c r="D1637" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F1637" t="s">
         <v>165</v>
       </c>
       <c r="G1637" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1637" s="2">
-        <v>0</v>
+        <v>7.951388888888888E-3</v>
       </c>
       <c r="I1637" s="1">
-        <v>46118.754861111112</v>
+        <v>46118.754166666666</v>
       </c>
       <c r="J1637">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1637" t="s">
         <v>11</v>
@@ -45430,10 +45414,10 @@
         <v>29</v>
       </c>
       <c r="C1638">
-        <v>2497</v>
+        <v>4961</v>
       </c>
       <c r="D1638" t="s">
-        <v>65</v>
+        <v>159</v>
       </c>
       <c r="F1638" t="s">
         <v>165</v>
@@ -45445,10 +45429,10 @@
         <v>0</v>
       </c>
       <c r="I1638" s="1">
-        <v>46118.755555555559</v>
+        <v>46118.754861111112</v>
       </c>
       <c r="J1638">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1638" t="s">
         <v>11</v>
@@ -45459,25 +45443,25 @@
         <v>29</v>
       </c>
       <c r="C1639">
-        <v>4946</v>
+        <v>2497</v>
       </c>
       <c r="D1639" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="F1639" t="s">
         <v>165</v>
       </c>
       <c r="G1639" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1639" s="2">
-        <v>7.0486111111111114E-3</v>
+        <v>0</v>
       </c>
       <c r="I1639" s="1">
         <v>46118.755555555559</v>
       </c>
       <c r="J1639">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1639" t="s">
         <v>11</v>
@@ -45488,25 +45472,25 @@
         <v>29</v>
       </c>
       <c r="C1640">
-        <v>2118</v>
+        <v>4946</v>
       </c>
       <c r="D1640" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="F1640" t="s">
         <v>165</v>
       </c>
       <c r="G1640" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1640" s="2">
-        <v>0</v>
+        <v>7.0486111111111114E-3</v>
       </c>
       <c r="I1640" s="1">
-        <v>46118.756249999999</v>
+        <v>46118.755555555559</v>
       </c>
       <c r="J1640">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1640" t="s">
         <v>11</v>
@@ -45517,25 +45501,25 @@
         <v>29</v>
       </c>
       <c r="C1641">
-        <v>2089</v>
+        <v>2118</v>
       </c>
       <c r="D1641" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F1641" t="s">
         <v>165</v>
       </c>
       <c r="G1641" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1641" s="2">
-        <v>8.3333333333333332E-3</v>
+        <v>0</v>
       </c>
       <c r="I1641" s="1">
-        <v>46118.756944444445</v>
+        <v>46118.756249999999</v>
       </c>
       <c r="J1641">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1641" t="s">
         <v>11</v>
@@ -45546,22 +45530,22 @@
         <v>29</v>
       </c>
       <c r="C1642">
-        <v>3206</v>
+        <v>2089</v>
       </c>
       <c r="D1642" t="s">
-        <v>134</v>
+        <v>68</v>
       </c>
       <c r="F1642" t="s">
         <v>165</v>
       </c>
       <c r="G1642" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1642" s="2">
-        <v>0</v>
+        <v>8.3333333333333332E-3</v>
       </c>
       <c r="I1642" s="1">
-        <v>46118.757638888892</v>
+        <v>46118.756944444445</v>
       </c>
       <c r="J1642">
         <v>3</v>
@@ -45575,25 +45559,25 @@
         <v>29</v>
       </c>
       <c r="C1643">
-        <v>2905</v>
+        <v>3206</v>
       </c>
       <c r="D1643" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="F1643" t="s">
         <v>165</v>
       </c>
       <c r="G1643" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1643" s="2">
-        <v>7.2106481481481483E-3</v>
+        <v>0</v>
       </c>
       <c r="I1643" s="1">
         <v>46118.757638888892</v>
       </c>
       <c r="J1643">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1643" t="s">
         <v>11</v>
@@ -45604,25 +45588,25 @@
         <v>29</v>
       </c>
       <c r="C1644">
-        <v>2652</v>
+        <v>2905</v>
       </c>
       <c r="D1644" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="F1644" t="s">
         <v>165</v>
       </c>
       <c r="G1644" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1644" s="2">
-        <v>0</v>
+        <v>7.2106481481481483E-3</v>
       </c>
       <c r="I1644" s="1">
-        <v>46118.758333333331</v>
+        <v>46118.757638888892</v>
       </c>
       <c r="J1644">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1644" t="s">
         <v>11</v>
@@ -45633,25 +45617,25 @@
         <v>29</v>
       </c>
       <c r="C1645">
-        <v>2511</v>
+        <v>2652</v>
       </c>
       <c r="D1645" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="F1645" t="s">
         <v>165</v>
       </c>
       <c r="G1645" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1645" s="2">
-        <v>1.0127314814814815E-2</v>
+        <v>0</v>
       </c>
       <c r="I1645" s="1">
         <v>46118.758333333331</v>
       </c>
       <c r="J1645">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1645" t="s">
         <v>11</v>
@@ -45662,25 +45646,25 @@
         <v>29</v>
       </c>
       <c r="C1646">
-        <v>2499</v>
+        <v>2511</v>
       </c>
       <c r="D1646" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="F1646" t="s">
         <v>165</v>
       </c>
       <c r="G1646" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1646" s="2">
-        <v>0</v>
+        <v>1.0127314814814815E-2</v>
       </c>
       <c r="I1646" s="1">
-        <v>46118.759027777778</v>
+        <v>46118.758333333331</v>
       </c>
       <c r="J1646">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1646" t="s">
         <v>11</v>
@@ -45691,10 +45675,10 @@
         <v>29</v>
       </c>
       <c r="C1647">
-        <v>2510</v>
+        <v>2499</v>
       </c>
       <c r="D1647" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="F1647" t="s">
         <v>165</v>
@@ -45706,10 +45690,10 @@
         <v>0</v>
       </c>
       <c r="I1647" s="1">
-        <v>46118.759722222225</v>
+        <v>46118.759027777778</v>
       </c>
       <c r="J1647">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1647" t="s">
         <v>11</v>
@@ -45720,64 +45704,64 @@
         <v>29</v>
       </c>
       <c r="C1648">
-        <v>3239</v>
+        <v>2510</v>
       </c>
       <c r="D1648" t="s">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="F1648" t="s">
         <v>165</v>
       </c>
       <c r="G1648" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1648" s="2">
-        <v>1.0972222222222222E-2</v>
+        <v>7.7314814814814815E-3</v>
       </c>
       <c r="I1648" s="1">
         <v>46118.759722222225</v>
       </c>
       <c r="J1648">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K1648" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1649" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1649" s="2"/>
-      <c r="I1649" s="1"/>
+      <c r="B1649" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1649">
+        <v>3239</v>
+      </c>
+      <c r="D1649" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1649" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1649" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1649" s="2">
+        <v>1.0972222222222222E-2</v>
+      </c>
+      <c r="I1649" s="1">
+        <v>46118.759722222225</v>
+      </c>
+      <c r="J1649">
+        <v>0</v>
+      </c>
       <c r="K1649" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1650" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1650" s="2"/>
+      <c r="I1650" s="1"/>
+      <c r="K1650" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1650" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1650" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1650">
-        <v>2088</v>
-      </c>
-      <c r="D1650" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1650" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1650" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1650" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1650" s="1">
-        <v>46118.760416666664</v>
-      </c>
-      <c r="J1650">
-        <v>3</v>
-      </c>
-      <c r="K1650" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1651" spans="2:11" x14ac:dyDescent="0.25">
@@ -45785,10 +45769,10 @@
         <v>29</v>
       </c>
       <c r="C1651">
-        <v>2903</v>
+        <v>2088</v>
       </c>
       <c r="D1651" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F1651" t="s">
         <v>165</v>
@@ -45800,10 +45784,10 @@
         <v>0</v>
       </c>
       <c r="I1651" s="1">
-        <v>46118.761111111111</v>
+        <v>46118.760416666664</v>
       </c>
       <c r="J1651">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1651" t="s">
         <v>11</v>
@@ -45814,25 +45798,25 @@
         <v>29</v>
       </c>
       <c r="C1652">
-        <v>2508</v>
+        <v>2903</v>
       </c>
       <c r="D1652" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F1652" t="s">
         <v>165</v>
       </c>
       <c r="G1652" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1652" s="2">
-        <v>8.611111111111111E-3</v>
+        <v>0</v>
       </c>
       <c r="I1652" s="1">
         <v>46118.761111111111</v>
       </c>
       <c r="J1652">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1652" t="s">
         <v>11</v>
@@ -45843,10 +45827,10 @@
         <v>29</v>
       </c>
       <c r="C1653">
-        <v>2648</v>
+        <v>2508</v>
       </c>
       <c r="D1653" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="F1653" t="s">
         <v>165</v>
@@ -45855,10 +45839,10 @@
         <v>10</v>
       </c>
       <c r="H1653" s="2">
-        <v>7.6157407407407406E-3</v>
+        <v>8.611111111111111E-3</v>
       </c>
       <c r="I1653" s="1">
-        <v>46118.761805555558</v>
+        <v>46118.761111111111</v>
       </c>
       <c r="J1653">
         <v>2</v>
@@ -45872,25 +45856,25 @@
         <v>29</v>
       </c>
       <c r="C1654">
-        <v>2459</v>
+        <v>2648</v>
       </c>
       <c r="D1654" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F1654" t="s">
         <v>165</v>
       </c>
       <c r="G1654" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1654">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="H1654" s="2">
+        <v>7.6157407407407406E-3</v>
       </c>
       <c r="I1654" s="1">
-        <v>46118.762499999997</v>
+        <v>46118.761805555558</v>
       </c>
       <c r="J1654">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1654" t="s">
         <v>11</v>
@@ -45901,64 +45885,64 @@
         <v>29</v>
       </c>
       <c r="C1655">
-        <v>2483</v>
+        <v>2459</v>
       </c>
       <c r="D1655" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F1655" t="s">
         <v>165</v>
       </c>
       <c r="G1655" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H1655" s="2">
-        <v>1.0416666666666667E-4</v>
+        <v>0</v>
       </c>
       <c r="I1655" s="1">
         <v>46118.762499999997</v>
       </c>
       <c r="J1655">
+        <v>4</v>
+      </c>
+      <c r="K1655" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1656" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1656" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1656">
+        <v>2483</v>
+      </c>
+      <c r="D1656" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1656" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1656" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1656" s="2">
+        <v>1.0416666666666667E-4</v>
+      </c>
+      <c r="I1656" s="1">
+        <v>46118.762499999997</v>
+      </c>
+      <c r="J1656">
         <v>1</v>
       </c>
-      <c r="K1655" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1656" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1656" s="2"/>
-      <c r="I1656" s="1"/>
       <c r="K1656" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1657" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1657" s="2"/>
+      <c r="I1657" s="1"/>
+      <c r="K1657" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1657" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1657" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1657">
-        <v>2113</v>
-      </c>
-      <c r="D1657" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1657" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1657" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1657" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1657" s="1">
-        <v>46118.763194444444</v>
-      </c>
-      <c r="J1657">
-        <v>3</v>
-      </c>
-      <c r="K1657" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1658" spans="2:11" x14ac:dyDescent="0.25">
@@ -45966,25 +45950,25 @@
         <v>29</v>
       </c>
       <c r="C1658">
-        <v>2490</v>
+        <v>2113</v>
       </c>
       <c r="D1658" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="F1658" t="s">
         <v>165</v>
       </c>
       <c r="G1658" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1658" s="2">
-        <v>8.0902777777777778E-3</v>
+        <v>0</v>
       </c>
       <c r="I1658" s="1">
-        <v>46118.763888888891</v>
+        <v>46118.763194444444</v>
       </c>
       <c r="J1658">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1658" t="s">
         <v>11</v>
@@ -45995,25 +45979,25 @@
         <v>29</v>
       </c>
       <c r="C1659">
-        <v>2638</v>
+        <v>2490</v>
       </c>
       <c r="D1659" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="F1659" t="s">
         <v>165</v>
       </c>
       <c r="G1659" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1659" s="2">
-        <v>0</v>
+        <v>8.0902777777777778E-3</v>
       </c>
       <c r="I1659" s="1">
         <v>46118.763888888891</v>
       </c>
       <c r="J1659">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1659" t="s">
         <v>11</v>
@@ -46024,64 +46008,64 @@
         <v>29</v>
       </c>
       <c r="C1660">
-        <v>4919</v>
+        <v>2638</v>
       </c>
       <c r="D1660" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="F1660" t="s">
         <v>165</v>
       </c>
       <c r="G1660" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1660" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1660" s="1">
+        <v>46118.763888888891</v>
+      </c>
+      <c r="J1660">
+        <v>4</v>
+      </c>
+      <c r="K1660" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1661" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1661" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1661">
+        <v>4919</v>
+      </c>
+      <c r="D1661" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1661" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1661" t="s">
         <v>15</v>
       </c>
-      <c r="H1660" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1660" s="1">
+      <c r="H1661" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1661" s="1">
         <v>46118.76458333333</v>
       </c>
-      <c r="J1660">
+      <c r="J1661">
         <v>3</v>
       </c>
-      <c r="K1660" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1661" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1661" s="2"/>
-      <c r="I1661" s="1"/>
       <c r="K1661" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1662" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H1662" s="2"/>
+      <c r="I1662" s="1"/>
+      <c r="K1662" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="1662" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1662" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1662">
-        <v>2509</v>
-      </c>
-      <c r="D1662" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1662" t="s">
-        <v>165</v>
-      </c>
-      <c r="G1662" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1662" s="2">
-        <v>7.3379629629629628E-3</v>
-      </c>
-      <c r="I1662" s="1">
-        <v>46118.765277777777</v>
-      </c>
-      <c r="J1662">
-        <v>0</v>
-      </c>
-      <c r="K1662" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1663" spans="2:11" x14ac:dyDescent="0.25">
@@ -46089,10 +46073,10 @@
         <v>29</v>
       </c>
       <c r="C1663">
-        <v>2901</v>
+        <v>2509</v>
       </c>
       <c r="D1663" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F1663" t="s">
         <v>165</v>
@@ -46101,7 +46085,7 @@
         <v>10</v>
       </c>
       <c r="H1663" s="2">
-        <v>1.0636574074074074E-2</v>
+        <v>7.3379629629629628E-3</v>
       </c>
       <c r="I1663" s="1">
         <v>46118.765277777777</v>
@@ -46118,25 +46102,25 @@
         <v>29</v>
       </c>
       <c r="C1664">
-        <v>3130</v>
+        <v>2901</v>
       </c>
       <c r="D1664" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="F1664" t="s">
         <v>165</v>
       </c>
       <c r="G1664" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1664" s="2">
-        <v>0</v>
+        <v>1.0636574074074074E-2</v>
       </c>
       <c r="I1664" s="1">
-        <v>46118.765972222223</v>
+        <v>46118.765277777777</v>
       </c>
       <c r="J1664">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1664" t="s">
         <v>11</v>
@@ -46147,10 +46131,10 @@
         <v>29</v>
       </c>
       <c r="C1665">
-        <v>2653</v>
+        <v>3130</v>
       </c>
       <c r="D1665" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="F1665" t="s">
         <v>165</v>
@@ -46165,7 +46149,7 @@
         <v>46118.765972222223</v>
       </c>
       <c r="J1665">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1665" t="s">
         <v>11</v>
@@ -46176,25 +46160,25 @@
         <v>29</v>
       </c>
       <c r="C1666">
-        <v>2485</v>
+        <v>2653</v>
       </c>
       <c r="D1666" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="F1666" t="s">
         <v>165</v>
       </c>
       <c r="G1666" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1666" s="2">
-        <v>7.9976851851851858E-3</v>
+        <v>0</v>
       </c>
       <c r="I1666" s="1">
-        <v>46118.76666666667</v>
+        <v>46118.765972222223</v>
       </c>
       <c r="J1666">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1666" t="s">
         <v>11</v>
@@ -46205,10 +46189,10 @@
         <v>29</v>
       </c>
       <c r="C1667">
-        <v>2074</v>
+        <v>2485</v>
       </c>
       <c r="D1667" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="F1667" t="s">
         <v>165</v>
@@ -46217,10 +46201,10 @@
         <v>10</v>
       </c>
       <c r="H1667" s="2">
-        <v>6.8402777777777776E-3</v>
+        <v>7.9976851851851858E-3</v>
       </c>
       <c r="I1667" s="1">
-        <v>46118.767361111109</v>
+        <v>46118.76666666667</v>
       </c>
       <c r="J1667">
         <v>1</v>
@@ -46234,25 +46218,25 @@
         <v>29</v>
       </c>
       <c r="C1668">
-        <v>2486</v>
+        <v>2074</v>
       </c>
       <c r="D1668" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F1668" t="s">
         <v>165</v>
       </c>
       <c r="G1668" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1668" s="2">
-        <v>0</v>
+        <v>6.8402777777777776E-3</v>
       </c>
       <c r="I1668" s="1">
         <v>46118.767361111109</v>
       </c>
       <c r="J1668">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1668" t="s">
         <v>11</v>
@@ -46263,25 +46247,25 @@
         <v>29</v>
       </c>
       <c r="C1669">
-        <v>2065</v>
+        <v>2486</v>
       </c>
       <c r="D1669" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F1669" t="s">
         <v>165</v>
       </c>
       <c r="G1669" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1669" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>0</v>
       </c>
       <c r="I1669" s="1">
-        <v>46118.768055555556</v>
+        <v>46118.767361111109</v>
       </c>
       <c r="J1669">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1669" t="s">
         <v>11</v>
@@ -46292,10 +46276,10 @@
         <v>29</v>
       </c>
       <c r="C1670">
-        <v>2649</v>
+        <v>2065</v>
       </c>
       <c r="D1670" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F1670" t="s">
         <v>165</v>
@@ -46304,13 +46288,13 @@
         <v>10</v>
       </c>
       <c r="H1670" s="2">
-        <v>7.3495370370370372E-3</v>
+        <v>7.8009259259259256E-3</v>
       </c>
       <c r="I1670" s="1">
         <v>46118.768055555556</v>
       </c>
       <c r="J1670">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1670" t="s">
         <v>11</v>
@@ -46321,25 +46305,25 @@
         <v>29</v>
       </c>
       <c r="C1671">
-        <v>2611</v>
+        <v>2649</v>
       </c>
       <c r="D1671" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="F1671" t="s">
         <v>165</v>
       </c>
       <c r="G1671" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1671" s="2">
-        <v>0</v>
+        <v>7.3495370370370372E-3</v>
       </c>
       <c r="I1671" s="1">
-        <v>46118.768750000003</v>
+        <v>46118.768055555556</v>
       </c>
       <c r="J1671">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1671" t="s">
         <v>11</v>
@@ -46350,10 +46334,10 @@
         <v>29</v>
       </c>
       <c r="C1672">
-        <v>2498</v>
+        <v>2611</v>
       </c>
       <c r="D1672" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F1672" t="s">
         <v>165</v>
@@ -46365,364 +46349,2148 @@
         <v>0</v>
       </c>
       <c r="I1672" s="1">
+        <v>46118.768750000003</v>
+      </c>
+      <c r="J1672">
+        <v>4</v>
+      </c>
+      <c r="K1672" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1673" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1673" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1673">
+        <v>2498</v>
+      </c>
+      <c r="D1673" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1673" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1673" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1673" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1673" s="1">
         <v>46118.769444444442</v>
       </c>
-      <c r="J1672">
-        <v>3</v>
-      </c>
-      <c r="K1672" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1673" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1673" s="2"/>
-      <c r="I1673" s="1"/>
+      <c r="J1673">
+        <v>4</v>
+      </c>
+      <c r="K1673" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1674" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1674" s="2"/>
-      <c r="I1674" s="1"/>
+      <c r="B1674" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1674">
+        <v>2111</v>
+      </c>
+      <c r="D1674" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1674" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1674" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1674" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1674" s="1">
+        <v>46146.631365740737</v>
+      </c>
+      <c r="J1674">
+        <v>0</v>
+      </c>
+      <c r="K1674" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1675" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1675" s="2"/>
-      <c r="I1675" s="1"/>
+      <c r="B1675" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1675">
+        <v>2114</v>
+      </c>
+      <c r="D1675" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1675" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1675" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1675" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1675" s="1">
+        <v>46146.632060185184</v>
+      </c>
+      <c r="J1675">
+        <v>0</v>
+      </c>
+      <c r="K1675" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1676" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1676" s="2"/>
-      <c r="I1676" s="1"/>
+      <c r="B1676" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1676">
+        <v>2613</v>
+      </c>
+      <c r="D1676" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1676" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1676" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1676" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1676" s="1">
+        <v>46146.632060185184</v>
+      </c>
+      <c r="J1676">
+        <v>0</v>
+      </c>
+      <c r="K1676" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1677" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1677" s="2"/>
-      <c r="I1677" s="1"/>
+      <c r="B1677" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1677">
+        <v>2506</v>
+      </c>
+      <c r="D1677" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1677" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1677" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1677" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1677" s="1">
+        <v>46146.632754629631</v>
+      </c>
+      <c r="J1677">
+        <v>0</v>
+      </c>
+      <c r="K1677" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1678" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1678" s="2"/>
-      <c r="I1678" s="1"/>
+      <c r="B1678" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1678">
+        <v>2507</v>
+      </c>
+      <c r="D1678" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1678" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1678" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1678" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1678" s="1">
+        <v>46146.633449074077</v>
+      </c>
+      <c r="J1678">
+        <v>0</v>
+      </c>
+      <c r="K1678" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1679" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1679" s="2"/>
-      <c r="I1679" s="1"/>
+      <c r="B1679" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1679">
+        <v>2505</v>
+      </c>
+      <c r="D1679" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1679" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1679" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1679" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1679" s="1">
+        <v>46146.633449074077</v>
+      </c>
+      <c r="J1679">
+        <v>0</v>
+      </c>
+      <c r="K1679" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="1680" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1680" s="2"/>
-      <c r="I1680" s="1"/>
-    </row>
-    <row r="1681" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1681" s="2"/>
-      <c r="I1681" s="1"/>
-    </row>
-    <row r="1682" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1682" s="2"/>
-      <c r="I1682" s="1"/>
-    </row>
-    <row r="1683" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1683" s="2"/>
-      <c r="I1683" s="1"/>
-    </row>
-    <row r="1684" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1684" s="2"/>
-      <c r="I1684" s="1"/>
-    </row>
-    <row r="1685" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B1680" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1680">
+        <v>2489</v>
+      </c>
+      <c r="D1680" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1680" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1680" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1680" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1680" s="1">
+        <v>46146.634143518517</v>
+      </c>
+      <c r="J1680">
+        <v>0</v>
+      </c>
+      <c r="K1680" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1681" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1681" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1681">
+        <v>2082</v>
+      </c>
+      <c r="D1681" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1681" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1681" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1681" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1681" s="1">
+        <v>46146.634837962964</v>
+      </c>
+      <c r="J1681">
+        <v>0</v>
+      </c>
+      <c r="K1681" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1682" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1682" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1682">
+        <v>2615</v>
+      </c>
+      <c r="D1682" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1682" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1682" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1682" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1682" s="1">
+        <v>46146.634837962964</v>
+      </c>
+      <c r="J1682">
+        <v>0</v>
+      </c>
+      <c r="K1682" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1683" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1683" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1683">
+        <v>2504</v>
+      </c>
+      <c r="D1683" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1683" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1683" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1683" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1683" s="1">
+        <v>46146.63553240741</v>
+      </c>
+      <c r="J1683">
+        <v>0</v>
+      </c>
+      <c r="K1683" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1684" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1684" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1684">
+        <v>2457</v>
+      </c>
+      <c r="D1684" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1684" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1684" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1684" s="2">
+        <v>2.685185185185185E-3</v>
+      </c>
+      <c r="I1684" s="1">
+        <v>46146.63553240741</v>
+      </c>
+      <c r="J1684">
+        <v>0</v>
+      </c>
+      <c r="K1684" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1685" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1685" s="2"/>
       <c r="I1685" s="1"/>
-    </row>
-    <row r="1686" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1686" s="2"/>
-      <c r="I1686" s="1"/>
-    </row>
-    <row r="1687" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1687" s="2"/>
-      <c r="I1687" s="1"/>
-    </row>
-    <row r="1688" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1688" s="2"/>
-      <c r="I1688" s="1"/>
-    </row>
-    <row r="1689" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1689" s="2"/>
-      <c r="I1689" s="1"/>
-    </row>
-    <row r="1690" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1690" s="2"/>
-      <c r="I1690" s="1"/>
-    </row>
-    <row r="1691" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1691" s="2"/>
-      <c r="I1691" s="1"/>
-    </row>
-    <row r="1692" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1692" s="2"/>
-      <c r="I1692" s="1"/>
-    </row>
-    <row r="1693" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1693" s="2"/>
-      <c r="I1693" s="1"/>
-    </row>
-    <row r="1694" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1694" s="2"/>
-      <c r="I1694" s="1"/>
-    </row>
-    <row r="1695" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1695" s="2"/>
-      <c r="I1695" s="1"/>
-    </row>
-    <row r="1696" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1685" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1686" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1686" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1686">
+        <v>2612</v>
+      </c>
+      <c r="D1686" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1686" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1686" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1686" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1686" s="1">
+        <v>46146.63622685185</v>
+      </c>
+      <c r="J1686">
+        <v>0</v>
+      </c>
+      <c r="K1686" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1687" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1687" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1687">
+        <v>5090</v>
+      </c>
+      <c r="D1687" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1687" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1687" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1687" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1687" s="1">
+        <v>46146.636921296296</v>
+      </c>
+      <c r="J1687">
+        <v>0</v>
+      </c>
+      <c r="K1687" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1688" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1688" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1688">
+        <v>2634</v>
+      </c>
+      <c r="D1688" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1688" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1688" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1688" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1688" s="1">
+        <v>46146.636921296296</v>
+      </c>
+      <c r="J1688">
+        <v>0</v>
+      </c>
+      <c r="K1688" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1689" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1689" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1689">
+        <v>2636</v>
+      </c>
+      <c r="D1689" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1689" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1689" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1689" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1689" s="1">
+        <v>46146.637615740743</v>
+      </c>
+      <c r="J1689">
+        <v>0</v>
+      </c>
+      <c r="K1689" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1690" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1690" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1690">
+        <v>2487</v>
+      </c>
+      <c r="D1690" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1690" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1690" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1690" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1690" s="1">
+        <v>46146.638310185182</v>
+      </c>
+      <c r="J1690">
+        <v>0</v>
+      </c>
+      <c r="K1690" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1691" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1691" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1691">
+        <v>2492</v>
+      </c>
+      <c r="D1691" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1691" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1691" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1691" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1691" s="1">
+        <v>46146.639004629629</v>
+      </c>
+      <c r="J1691">
+        <v>0</v>
+      </c>
+      <c r="K1691" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1692" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1692" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1692">
+        <v>5065</v>
+      </c>
+      <c r="D1692" t="s">
+        <v>163</v>
+      </c>
+      <c r="F1692" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1692" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1692" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1692" s="1">
+        <v>46146.639004629629</v>
+      </c>
+      <c r="J1692">
+        <v>0</v>
+      </c>
+      <c r="K1692" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1693" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1693" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1693">
+        <v>2650</v>
+      </c>
+      <c r="D1693" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1693" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1693" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1693" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1693" s="1">
+        <v>46146.639699074076</v>
+      </c>
+      <c r="J1693">
+        <v>0</v>
+      </c>
+      <c r="K1693" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1694" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1694" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1694">
+        <v>2632</v>
+      </c>
+      <c r="D1694" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1694" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1694" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1694" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1694" s="1">
+        <v>46146.639699074076</v>
+      </c>
+      <c r="J1694">
+        <v>0</v>
+      </c>
+      <c r="K1694" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1695" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1695" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1695">
+        <v>2494</v>
+      </c>
+      <c r="D1695" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1695" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1695" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1695" s="2">
+        <v>2.199074074074074E-4</v>
+      </c>
+      <c r="I1695" s="1">
+        <v>46146.640393518515</v>
+      </c>
+      <c r="J1695">
+        <v>0</v>
+      </c>
+      <c r="K1695" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1696" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
-    </row>
-    <row r="1697" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1697" s="2"/>
-      <c r="I1697" s="1"/>
-    </row>
-    <row r="1698" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1698" s="2"/>
-      <c r="I1698" s="1"/>
-    </row>
-    <row r="1699" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1699" s="2"/>
-      <c r="I1699" s="1"/>
-    </row>
-    <row r="1700" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1700" s="2"/>
-      <c r="I1700" s="1"/>
-    </row>
-    <row r="1701" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1701" s="2"/>
-      <c r="I1701" s="1"/>
-    </row>
-    <row r="1702" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1702" s="2"/>
-      <c r="I1702" s="1"/>
-    </row>
-    <row r="1703" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1703" s="2"/>
-      <c r="I1703" s="1"/>
-    </row>
-    <row r="1704" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1696" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1697" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1697" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1697">
+        <v>2902</v>
+      </c>
+      <c r="D1697" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1697" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1697" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1697" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1697" s="1">
+        <v>46146.641087962962</v>
+      </c>
+      <c r="J1697">
+        <v>0</v>
+      </c>
+      <c r="K1697" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1698" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1698" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1698">
+        <v>2633</v>
+      </c>
+      <c r="D1698" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1698" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1698" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1698" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1698" s="1">
+        <v>46146.641087962962</v>
+      </c>
+      <c r="J1698">
+        <v>0</v>
+      </c>
+      <c r="K1698" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1699" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1699" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1699">
+        <v>2115</v>
+      </c>
+      <c r="D1699" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1699" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1699" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1699" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1699" s="1">
+        <v>46146.641782407409</v>
+      </c>
+      <c r="J1699">
+        <v>0</v>
+      </c>
+      <c r="K1699" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1700" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1700" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1700">
+        <v>2458</v>
+      </c>
+      <c r="D1700" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1700" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1700" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1700" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1700" s="1">
+        <v>46146.642476851855</v>
+      </c>
+      <c r="J1700">
+        <v>0</v>
+      </c>
+      <c r="K1700" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1701" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1701" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1701">
+        <v>2635</v>
+      </c>
+      <c r="D1701" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1701" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1701" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1701" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1701" s="1">
+        <v>46146.642476851855</v>
+      </c>
+      <c r="J1701">
+        <v>0</v>
+      </c>
+      <c r="K1701" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1702" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1702" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1702">
+        <v>3776</v>
+      </c>
+      <c r="D1702" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1702" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1702" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1702" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1702" s="1">
+        <v>46146.643171296295</v>
+      </c>
+      <c r="J1702">
+        <v>0</v>
+      </c>
+      <c r="K1702" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1703" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1703" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1703">
+        <v>2247</v>
+      </c>
+      <c r="D1703" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1703" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1703" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1703" s="2">
+        <v>3.0671296296296297E-3</v>
+      </c>
+      <c r="I1703" s="1">
+        <v>46146.643865740742</v>
+      </c>
+      <c r="J1703">
+        <v>0</v>
+      </c>
+      <c r="K1703" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1704" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1704" s="2"/>
       <c r="I1704" s="1"/>
-    </row>
-    <row r="1705" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1705" s="2"/>
-      <c r="I1705" s="1"/>
-    </row>
-    <row r="1706" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1706" s="2"/>
-      <c r="I1706" s="1"/>
-    </row>
-    <row r="1707" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1707" s="2"/>
-      <c r="I1707" s="1"/>
-    </row>
-    <row r="1708" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1708" s="2"/>
-      <c r="I1708" s="1"/>
-    </row>
-    <row r="1709" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1709" s="2"/>
-      <c r="I1709" s="1"/>
-    </row>
-    <row r="1710" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1710" s="2"/>
-      <c r="I1710" s="1"/>
-    </row>
-    <row r="1711" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1711" s="2"/>
-      <c r="I1711" s="1"/>
-    </row>
-    <row r="1712" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1712" s="2"/>
-      <c r="I1712" s="1"/>
-    </row>
-    <row r="1713" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1713" s="2"/>
-      <c r="I1713" s="1"/>
-    </row>
-    <row r="1714" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1714" s="2"/>
-      <c r="I1714" s="1"/>
-    </row>
-    <row r="1715" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1715" s="2"/>
-      <c r="I1715" s="1"/>
-    </row>
-    <row r="1716" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1716" s="2"/>
-      <c r="I1716" s="1"/>
-    </row>
-    <row r="1717" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1717" s="2"/>
-      <c r="I1717" s="1"/>
-    </row>
-    <row r="1718" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1718" s="2"/>
-      <c r="I1718" s="1"/>
-    </row>
-    <row r="1719" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1719" s="2"/>
-      <c r="I1719" s="1"/>
-    </row>
-    <row r="1720" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1720" s="2"/>
-      <c r="I1720" s="1"/>
-    </row>
-    <row r="1721" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1721" s="2"/>
-      <c r="I1721" s="1"/>
-    </row>
-    <row r="1722" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1722" s="2"/>
-      <c r="I1722" s="1"/>
-    </row>
-    <row r="1723" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1723" s="2"/>
-      <c r="I1723" s="1"/>
-    </row>
-    <row r="1724" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1724" s="2"/>
-      <c r="I1724" s="1"/>
-    </row>
-    <row r="1725" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1725" s="2"/>
-      <c r="I1725" s="1"/>
-    </row>
-    <row r="1726" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1726" s="2"/>
-      <c r="I1726" s="1"/>
-    </row>
-    <row r="1727" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1727" s="2"/>
-      <c r="I1727" s="1"/>
-    </row>
-    <row r="1728" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1728" s="2"/>
-      <c r="I1728" s="1"/>
-    </row>
-    <row r="1729" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1729" s="2"/>
-      <c r="I1729" s="1"/>
-    </row>
-    <row r="1730" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1730" s="2"/>
-      <c r="I1730" s="1"/>
-    </row>
-    <row r="1731" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1731" s="2"/>
-      <c r="I1731" s="1"/>
-    </row>
-    <row r="1732" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1732" s="2"/>
-      <c r="I1732" s="1"/>
-    </row>
-    <row r="1733" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1733" s="2"/>
-      <c r="I1733" s="1"/>
-    </row>
-    <row r="1734" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1734" s="2"/>
-      <c r="I1734" s="1"/>
-    </row>
-    <row r="1735" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1735" s="2"/>
-      <c r="I1735" s="1"/>
-    </row>
-    <row r="1736" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1736" s="2"/>
-      <c r="I1736" s="1"/>
-    </row>
-    <row r="1737" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1737" s="2"/>
-      <c r="I1737" s="1"/>
-    </row>
-    <row r="1738" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1738" s="2"/>
-      <c r="I1738" s="1"/>
-    </row>
-    <row r="1739" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1739" s="2"/>
-      <c r="I1739" s="1"/>
-    </row>
-    <row r="1740" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1740" s="2"/>
-      <c r="I1740" s="1"/>
-    </row>
-    <row r="1741" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1741" s="2"/>
-      <c r="I1741" s="1"/>
-    </row>
-    <row r="1742" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1742" s="2"/>
-      <c r="I1742" s="1"/>
-    </row>
-    <row r="1743" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1743" s="2"/>
-      <c r="I1743" s="1"/>
-    </row>
-    <row r="1744" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1744" s="2"/>
-      <c r="I1744" s="1"/>
-    </row>
-    <row r="1745" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1745" s="2"/>
-      <c r="I1745" s="1"/>
-    </row>
-    <row r="1746" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H1746" s="2"/>
-      <c r="I1746" s="1"/>
-    </row>
-    <row r="1747" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K1704" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1705" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1705" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1705">
+        <v>2651</v>
+      </c>
+      <c r="D1705" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1705" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1705" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1705" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1705" s="1">
+        <v>46146.644560185188</v>
+      </c>
+      <c r="J1705">
+        <v>0</v>
+      </c>
+      <c r="K1705" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1706" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1706" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1706">
+        <v>2116</v>
+      </c>
+      <c r="D1706" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1706" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1706" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1706" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1706" s="1">
+        <v>46146.644560185188</v>
+      </c>
+      <c r="J1706">
+        <v>0</v>
+      </c>
+      <c r="K1706" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1707" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1707" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1707">
+        <v>2053</v>
+      </c>
+      <c r="D1707" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1707" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1707" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1707" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1707" s="1">
+        <v>46146.645254629628</v>
+      </c>
+      <c r="J1707">
+        <v>0</v>
+      </c>
+      <c r="K1707" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1708" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1708" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1708">
+        <v>2503</v>
+      </c>
+      <c r="D1708" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1708" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1708" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1708" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1708" s="1">
+        <v>46146.645949074074</v>
+      </c>
+      <c r="J1708">
+        <v>0</v>
+      </c>
+      <c r="K1708" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1709" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1709" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1709">
+        <v>2493</v>
+      </c>
+      <c r="D1709" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1709" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1709" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1709" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1709" s="1">
+        <v>46146.645949074074</v>
+      </c>
+      <c r="J1709">
+        <v>0</v>
+      </c>
+      <c r="K1709" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1710" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1710" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1710">
+        <v>5388</v>
+      </c>
+      <c r="D1710" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1710" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1710" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1710" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1710" s="1">
+        <v>46146.646643518521</v>
+      </c>
+      <c r="J1710">
+        <v>0</v>
+      </c>
+      <c r="K1710" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1711" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1711" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1711">
+        <v>5038</v>
+      </c>
+      <c r="D1711" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1711" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1711" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1711" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1711" s="1">
+        <v>46146.647337962961</v>
+      </c>
+      <c r="J1711">
+        <v>0</v>
+      </c>
+      <c r="K1711" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1712" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1712" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1712">
+        <v>4961</v>
+      </c>
+      <c r="D1712" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1712" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1712" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1712" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1712" s="1">
+        <v>46146.647337962961</v>
+      </c>
+      <c r="J1712">
+        <v>0</v>
+      </c>
+      <c r="K1712" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1713" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1713" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1713">
+        <v>2497</v>
+      </c>
+      <c r="D1713" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1713" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1713" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1713" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1713" s="1">
+        <v>46146.648032407407</v>
+      </c>
+      <c r="J1713">
+        <v>0</v>
+      </c>
+      <c r="K1713" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1714" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1714" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1714">
+        <v>4946</v>
+      </c>
+      <c r="D1714" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1714" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1714" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1714" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1714" s="1">
+        <v>46146.648726851854</v>
+      </c>
+      <c r="J1714">
+        <v>0</v>
+      </c>
+      <c r="K1714" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1715" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1715" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1715">
+        <v>5531</v>
+      </c>
+      <c r="D1715" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1715" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1715" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1715" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1715" s="1">
+        <v>46146.648726851854</v>
+      </c>
+      <c r="J1715">
+        <v>0</v>
+      </c>
+      <c r="K1715" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1716" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1716" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1716">
+        <v>2118</v>
+      </c>
+      <c r="D1716" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1716" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1716" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1716" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1716" s="1">
+        <v>46146.649421296293</v>
+      </c>
+      <c r="J1716">
+        <v>0</v>
+      </c>
+      <c r="K1716" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1717" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1717" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1717">
+        <v>2089</v>
+      </c>
+      <c r="D1717" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1717" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1717" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1717" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1717" s="1">
+        <v>46146.65011574074</v>
+      </c>
+      <c r="J1717">
+        <v>0</v>
+      </c>
+      <c r="K1717" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1718" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1718" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1718">
+        <v>3206</v>
+      </c>
+      <c r="D1718" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1718" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1718" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1718" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1718" s="1">
+        <v>46146.626620370371</v>
+      </c>
+      <c r="J1718">
+        <v>0</v>
+      </c>
+      <c r="K1718" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1719" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1719" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1719">
+        <v>2905</v>
+      </c>
+      <c r="D1719" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1719" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1719" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1719" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1719" s="1">
+        <v>46146.627314814818</v>
+      </c>
+      <c r="J1719">
+        <v>0</v>
+      </c>
+      <c r="K1719" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1720" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1720" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1720">
+        <v>2652</v>
+      </c>
+      <c r="D1720" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1720" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1720" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1720" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1720" s="1">
+        <v>46146.628009259257</v>
+      </c>
+      <c r="J1720">
+        <v>0</v>
+      </c>
+      <c r="K1720" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1721" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1721" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1721">
+        <v>2511</v>
+      </c>
+      <c r="D1721" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1721" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1721" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1721" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1721" s="1">
+        <v>46146.628009259257</v>
+      </c>
+      <c r="J1721">
+        <v>0</v>
+      </c>
+      <c r="K1721" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1722" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1722" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1722">
+        <v>2499</v>
+      </c>
+      <c r="D1722" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1722" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1722" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1722" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1722" s="1">
+        <v>46146.628703703704</v>
+      </c>
+      <c r="J1722">
+        <v>0</v>
+      </c>
+      <c r="K1722" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1723" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1723" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1723">
+        <v>2510</v>
+      </c>
+      <c r="D1723" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1723" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1723" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1723" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1723" s="1">
+        <v>46146.62939814815</v>
+      </c>
+      <c r="J1723">
+        <v>0</v>
+      </c>
+      <c r="K1723" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1724" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1724" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1724">
+        <v>3239</v>
+      </c>
+      <c r="D1724" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1724" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1724" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1724" s="2">
+        <v>7.0254629629629634E-3</v>
+      </c>
+      <c r="I1724" s="1">
+        <v>46146.62939814815</v>
+      </c>
+      <c r="J1724">
+        <v>0</v>
+      </c>
+      <c r="K1724" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1725" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1725" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1725">
+        <v>2088</v>
+      </c>
+      <c r="D1725" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1725" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1725" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1725" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1725" s="1">
+        <v>46146.63009259259</v>
+      </c>
+      <c r="J1725">
+        <v>0</v>
+      </c>
+      <c r="K1725" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1726" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1726" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1726">
+        <v>2903</v>
+      </c>
+      <c r="D1726" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1726" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1726" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1726" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1726" s="1">
+        <v>46146.630787037036</v>
+      </c>
+      <c r="J1726">
+        <v>0</v>
+      </c>
+      <c r="K1726" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1727" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1727" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1727">
+        <v>2508</v>
+      </c>
+      <c r="D1727" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1727" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1727" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1727" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1727" s="1">
+        <v>46146.631481481483</v>
+      </c>
+      <c r="J1727">
+        <v>0</v>
+      </c>
+      <c r="K1727" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1728" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1728" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1728">
+        <v>2648</v>
+      </c>
+      <c r="D1728" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1728" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1728" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1728" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1728" s="1">
+        <v>46146.631481481483</v>
+      </c>
+      <c r="J1728">
+        <v>0</v>
+      </c>
+      <c r="K1728" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1729" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1729" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1729">
+        <v>2459</v>
+      </c>
+      <c r="D1729" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1729" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1729" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1729" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1729" s="1">
+        <v>46146.632175925923</v>
+      </c>
+      <c r="J1729">
+        <v>0</v>
+      </c>
+      <c r="K1729" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1730" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1730" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1730">
+        <v>2483</v>
+      </c>
+      <c r="D1730" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1730" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1730" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1730" s="2">
+        <v>8.6689814814814806E-3</v>
+      </c>
+      <c r="I1730" s="1">
+        <v>46146.632870370369</v>
+      </c>
+      <c r="J1730">
+        <v>0</v>
+      </c>
+      <c r="K1730" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1731" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1731" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1731">
+        <v>2113</v>
+      </c>
+      <c r="D1731" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1731" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1731" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1731" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1731" s="1">
+        <v>46146.632870370369</v>
+      </c>
+      <c r="J1731">
+        <v>0</v>
+      </c>
+      <c r="K1731" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1732" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1732" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1732">
+        <v>2490</v>
+      </c>
+      <c r="D1732" t="s">
+        <v>122</v>
+      </c>
+      <c r="F1732" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1732" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1732" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1732" s="1">
+        <v>46146.633564814816</v>
+      </c>
+      <c r="J1732">
+        <v>0</v>
+      </c>
+      <c r="K1732" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1733" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1733" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1733">
+        <v>2638</v>
+      </c>
+      <c r="D1733" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1733" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1733" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1733" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1733" s="1">
+        <v>46146.634259259263</v>
+      </c>
+      <c r="J1733">
+        <v>0</v>
+      </c>
+      <c r="K1733" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1734" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1734" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1734">
+        <v>4919</v>
+      </c>
+      <c r="D1734" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1734" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1734" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1734" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1734" s="1">
+        <v>46146.634259259263</v>
+      </c>
+      <c r="J1734">
+        <v>0</v>
+      </c>
+      <c r="K1734" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1735" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1735" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1735">
+        <v>2509</v>
+      </c>
+      <c r="D1735" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1735" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1735" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1735" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1735" s="1">
+        <v>46146.634953703702</v>
+      </c>
+      <c r="J1735">
+        <v>0</v>
+      </c>
+      <c r="K1735" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1736" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1736" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1736">
+        <v>2901</v>
+      </c>
+      <c r="D1736" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1736" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1736" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1736" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1736" s="1">
+        <v>46146.635648148149</v>
+      </c>
+      <c r="J1736">
+        <v>0</v>
+      </c>
+      <c r="K1736" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1737" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1737" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1737">
+        <v>3130</v>
+      </c>
+      <c r="D1737" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1737" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1737" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1737" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1737" s="1">
+        <v>46146.635648148149</v>
+      </c>
+      <c r="J1737">
+        <v>0</v>
+      </c>
+      <c r="K1737" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1738" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1738" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1738">
+        <v>2653</v>
+      </c>
+      <c r="D1738" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1738" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1738" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1738" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1738" s="1">
+        <v>46146.636342592596</v>
+      </c>
+      <c r="J1738">
+        <v>0</v>
+      </c>
+      <c r="K1738" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1739" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1739" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1739">
+        <v>2485</v>
+      </c>
+      <c r="D1739" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1739" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1739" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1739" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1739" s="1">
+        <v>46146.637037037035</v>
+      </c>
+      <c r="J1739">
+        <v>0</v>
+      </c>
+      <c r="K1739" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1740" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1740" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1740">
+        <v>2074</v>
+      </c>
+      <c r="D1740" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1740" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1740" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1740" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1740" s="1">
+        <v>46146.637037037035</v>
+      </c>
+      <c r="J1740">
+        <v>0</v>
+      </c>
+      <c r="K1740" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1741" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1741" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1741">
+        <v>2486</v>
+      </c>
+      <c r="D1741" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1741" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1741" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1741" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1741" s="1">
+        <v>46146.637731481482</v>
+      </c>
+      <c r="J1741">
+        <v>0</v>
+      </c>
+      <c r="K1741" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1742" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1742" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1742">
+        <v>2065</v>
+      </c>
+      <c r="D1742" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1742" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1742" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1742" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1742" s="1">
+        <v>46146.638425925928</v>
+      </c>
+      <c r="J1742">
+        <v>0</v>
+      </c>
+      <c r="K1742" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1743" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1743" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1743">
+        <v>2649</v>
+      </c>
+      <c r="D1743" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1743" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1743" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1743" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1743" s="1">
+        <v>46146.638425925928</v>
+      </c>
+      <c r="J1743">
+        <v>0</v>
+      </c>
+      <c r="K1743" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1744" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1744" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1744">
+        <v>2611</v>
+      </c>
+      <c r="D1744" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1744" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1744" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1744" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1744" s="1">
+        <v>46146.639120370368</v>
+      </c>
+      <c r="J1744">
+        <v>0</v>
+      </c>
+      <c r="K1744" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1745" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1745" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1745">
+        <v>2498</v>
+      </c>
+      <c r="D1745" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1745" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1745" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1745" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1745" s="1">
+        <v>46146.639814814815</v>
+      </c>
+      <c r="J1745">
+        <v>0</v>
+      </c>
+      <c r="K1745" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1746" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1746" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1746">
+        <v>5532</v>
+      </c>
+      <c r="D1746" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1746" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1746" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1746" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1746" s="1">
+        <v>46146.639814814815</v>
+      </c>
+      <c r="J1746">
+        <v>0</v>
+      </c>
+      <c r="K1746" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1747" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1747" s="2"/>
       <c r="I1747" s="1"/>
     </row>
-    <row r="1748" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1748" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1748" s="2"/>
       <c r="I1748" s="1"/>
     </row>
-    <row r="1749" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1749" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
     </row>
-    <row r="1750" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1750" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1750" s="2"/>
       <c r="I1750" s="1"/>
     </row>
-    <row r="1751" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1751" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1751" s="2"/>
       <c r="I1751" s="1"/>
     </row>
-    <row r="1752" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1752" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1752" s="2"/>
       <c r="I1752" s="1"/>
     </row>
-    <row r="1753" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1753" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1753" s="2"/>
       <c r="I1753" s="1"/>
     </row>
-    <row r="1754" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1754" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1754" s="2"/>
       <c r="I1754" s="1"/>
     </row>
-    <row r="1755" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1755" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1755" s="2"/>
       <c r="I1755" s="1"/>
     </row>
-    <row r="1756" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1756" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1756" s="2"/>
       <c r="I1756" s="1"/>
     </row>
-    <row r="1757" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1757" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1757" s="2"/>
       <c r="I1757" s="1"/>
     </row>
-    <row r="1758" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1758" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1758" s="2"/>
       <c r="I1758" s="1"/>
     </row>
-    <row r="1759" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1759" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1759" s="2"/>
       <c r="I1759" s="1"/>
     </row>
-    <row r="1760" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="1760" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1760" s="2"/>
       <c r="I1760" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Apple Towing - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C72150C-73BC-4900-9962-5E4D46CE886E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794972C2-8627-4B0E-B3A5-B23784E02BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8167" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8166" uniqueCount="169">
   <si>
     <t>Company Name</t>
   </si>
@@ -44297,7 +44297,7 @@
         <v>46118.717939814815</v>
       </c>
       <c r="J1592">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1592" t="s">
         <v>11</v>
@@ -44355,7 +44355,7 @@
         <v>46118.719328703701</v>
       </c>
       <c r="J1594">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1594" t="s">
         <v>11</v>
@@ -44413,7 +44413,7 @@
         <v>46118.720023148147</v>
       </c>
       <c r="J1596">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1596" t="s">
         <v>11</v>
@@ -44536,7 +44536,7 @@
         <v>46118.72210648148</v>
       </c>
       <c r="J1601">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1601" t="s">
         <v>11</v>
@@ -44731,7 +44731,7 @@
         <v>46118.72488425926</v>
       </c>
       <c r="J1610">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1610" t="s">
         <v>11</v>
@@ -44854,7 +44854,7 @@
         <v>46118.726273148146</v>
       </c>
       <c r="J1615">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1615" t="s">
         <v>11</v>
@@ -44918,7 +44918,7 @@
         <v>46118.726967592593</v>
       </c>
       <c r="J1618">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1618" t="s">
         <v>11</v>
@@ -44983,7 +44983,7 @@
         <v>46118.728356481479</v>
       </c>
       <c r="J1621">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1621" t="s">
         <v>11</v>
@@ -45041,7 +45041,7 @@
         <v>46118.729050925926</v>
       </c>
       <c r="J1623">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1623" t="s">
         <v>11</v>
@@ -45070,7 +45070,7 @@
         <v>46118.729745370372</v>
       </c>
       <c r="J1624">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1624" t="s">
         <v>11</v>
@@ -45099,7 +45099,7 @@
         <v>46118.729745370372</v>
       </c>
       <c r="J1625">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1625" t="s">
         <v>11</v>
@@ -45309,7 +45309,7 @@
         <v>46118.732523148145</v>
       </c>
       <c r="J1633">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1633" t="s">
         <v>11</v>
@@ -45432,7 +45432,7 @@
         <v>46118.754861111112</v>
       </c>
       <c r="J1638">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1638" t="s">
         <v>11</v>
@@ -45461,7 +45461,7 @@
         <v>46118.755555555559</v>
       </c>
       <c r="J1639">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1639" t="s">
         <v>11</v>
@@ -45519,7 +45519,7 @@
         <v>46118.756249999999</v>
       </c>
       <c r="J1641">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1641" t="s">
         <v>11</v>
@@ -45577,7 +45577,7 @@
         <v>46118.757638888892</v>
       </c>
       <c r="J1643">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1643" t="s">
         <v>11</v>
@@ -45635,7 +45635,7 @@
         <v>46118.758333333331</v>
       </c>
       <c r="J1645">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1645" t="s">
         <v>11</v>
@@ -45693,7 +45693,7 @@
         <v>46118.759027777778</v>
       </c>
       <c r="J1647">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1647" t="s">
         <v>11</v>
@@ -45787,7 +45787,7 @@
         <v>46118.760416666664</v>
       </c>
       <c r="J1651">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1651" t="s">
         <v>11</v>
@@ -45816,7 +45816,7 @@
         <v>46118.761111111111</v>
       </c>
       <c r="J1652">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1652" t="s">
         <v>11</v>
@@ -45903,7 +45903,7 @@
         <v>46118.762499999997</v>
       </c>
       <c r="J1655">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1655" t="s">
         <v>11</v>
@@ -45968,7 +45968,7 @@
         <v>46118.763194444444</v>
       </c>
       <c r="J1658">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1658" t="s">
         <v>11</v>
@@ -46026,7 +46026,7 @@
         <v>46118.763888888891</v>
       </c>
       <c r="J1660">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1660" t="s">
         <v>11</v>
@@ -46149,7 +46149,7 @@
         <v>46118.765972222223</v>
       </c>
       <c r="J1665">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1665" t="s">
         <v>11</v>
@@ -46178,7 +46178,7 @@
         <v>46118.765972222223</v>
       </c>
       <c r="J1666">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1666" t="s">
         <v>11</v>
@@ -46265,7 +46265,7 @@
         <v>46118.767361111109</v>
       </c>
       <c r="J1669">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1669" t="s">
         <v>11</v>
@@ -46352,7 +46352,7 @@
         <v>46118.768750000003</v>
       </c>
       <c r="J1672">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1672" t="s">
         <v>11</v>
@@ -46381,7 +46381,7 @@
         <v>46118.769444444442</v>
       </c>
       <c r="J1673">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1673" t="s">
         <v>11</v>
@@ -46488,10 +46488,10 @@
         <v>21</v>
       </c>
       <c r="G1677" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1677" s="2">
-        <v>0</v>
+        <v>5.6597222222222222E-3</v>
       </c>
       <c r="I1677" s="1">
         <v>46146.632754629631</v>
@@ -47053,10 +47053,10 @@
         <v>21</v>
       </c>
       <c r="G1698" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1698" s="2">
-        <v>0</v>
+        <v>8.3217592592592596E-3</v>
       </c>
       <c r="I1698" s="1">
         <v>46146.641087962962</v>
@@ -47169,10 +47169,10 @@
         <v>21</v>
       </c>
       <c r="G1702" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1702" s="2">
-        <v>0</v>
+        <v>8.3912037037037045E-3</v>
       </c>
       <c r="I1702" s="1">
         <v>46146.643171296295</v>
@@ -47198,10 +47198,10 @@
         <v>21</v>
       </c>
       <c r="G1703" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1703" s="2">
-        <v>3.0671296296296297E-3</v>
+        <v>5.5555555555555558E-3</v>
       </c>
       <c r="I1703" s="1">
         <v>46146.643865740742</v>
@@ -47214,10 +47214,32 @@
       </c>
     </row>
     <row r="1704" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H1704" s="2"/>
-      <c r="I1704" s="1"/>
+      <c r="B1704" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1704">
+        <v>2651</v>
+      </c>
+      <c r="D1704" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1704" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1704" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1704" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1704" s="1">
+        <v>46146.644560185188</v>
+      </c>
+      <c r="J1704">
+        <v>0</v>
+      </c>
       <c r="K1704" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1705" spans="2:11" x14ac:dyDescent="0.25">
@@ -47225,19 +47247,19 @@
         <v>29</v>
       </c>
       <c r="C1705">
-        <v>2651</v>
+        <v>2116</v>
       </c>
       <c r="D1705" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="F1705" t="s">
         <v>21</v>
       </c>
       <c r="G1705" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1705" s="2">
-        <v>0</v>
+        <v>4.3981481481481484E-3</v>
       </c>
       <c r="I1705" s="1">
         <v>46146.644560185188</v>
@@ -47254,10 +47276,10 @@
         <v>29</v>
       </c>
       <c r="C1706">
-        <v>2116</v>
+        <v>2053</v>
       </c>
       <c r="D1706" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1706" t="s">
         <v>21</v>
@@ -47269,7 +47291,7 @@
         <v>0</v>
       </c>
       <c r="I1706" s="1">
-        <v>46146.644560185188</v>
+        <v>46146.645254629628</v>
       </c>
       <c r="J1706">
         <v>0</v>
@@ -47283,10 +47305,10 @@
         <v>29</v>
       </c>
       <c r="C1707">
-        <v>2053</v>
+        <v>2503</v>
       </c>
       <c r="D1707" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1707" t="s">
         <v>21</v>
@@ -47298,7 +47320,7 @@
         <v>0</v>
       </c>
       <c r="I1707" s="1">
-        <v>46146.645254629628</v>
+        <v>46146.645949074074</v>
       </c>
       <c r="J1707">
         <v>0</v>
@@ -47312,10 +47334,10 @@
         <v>29</v>
       </c>
       <c r="C1708">
-        <v>2503</v>
+        <v>2493</v>
       </c>
       <c r="D1708" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1708" t="s">
         <v>21</v>
@@ -47341,22 +47363,22 @@
         <v>29</v>
       </c>
       <c r="C1709">
-        <v>2493</v>
+        <v>5388</v>
       </c>
       <c r="D1709" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="F1709" t="s">
         <v>21</v>
       </c>
       <c r="G1709" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1709" s="2">
-        <v>0</v>
+        <v>1.0486111111111111E-2</v>
       </c>
       <c r="I1709" s="1">
-        <v>46146.645949074074</v>
+        <v>46146.646643518521</v>
       </c>
       <c r="J1709">
         <v>0</v>
@@ -47370,10 +47392,10 @@
         <v>29</v>
       </c>
       <c r="C1710">
-        <v>5388</v>
+        <v>5038</v>
       </c>
       <c r="D1710" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F1710" t="s">
         <v>21</v>
@@ -47385,7 +47407,7 @@
         <v>0</v>
       </c>
       <c r="I1710" s="1">
-        <v>46146.646643518521</v>
+        <v>46146.647337962961</v>
       </c>
       <c r="J1710">
         <v>0</v>
@@ -47399,10 +47421,10 @@
         <v>29</v>
       </c>
       <c r="C1711">
-        <v>5038</v>
+        <v>4961</v>
       </c>
       <c r="D1711" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F1711" t="s">
         <v>21</v>
@@ -47428,10 +47450,10 @@
         <v>29</v>
       </c>
       <c r="C1712">
-        <v>4961</v>
+        <v>2497</v>
       </c>
       <c r="D1712" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="F1712" t="s">
         <v>21</v>
@@ -47443,7 +47465,7 @@
         <v>0</v>
       </c>
       <c r="I1712" s="1">
-        <v>46146.647337962961</v>
+        <v>46146.648032407407</v>
       </c>
       <c r="J1712">
         <v>0</v>
@@ -47457,10 +47479,10 @@
         <v>29</v>
       </c>
       <c r="C1713">
-        <v>2497</v>
+        <v>4946</v>
       </c>
       <c r="D1713" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="F1713" t="s">
         <v>21</v>
@@ -47472,7 +47494,7 @@
         <v>0</v>
       </c>
       <c r="I1713" s="1">
-        <v>46146.648032407407</v>
+        <v>46146.648726851854</v>
       </c>
       <c r="J1713">
         <v>0</v>
@@ -47486,10 +47508,10 @@
         <v>29</v>
       </c>
       <c r="C1714">
-        <v>4946</v>
+        <v>5531</v>
       </c>
       <c r="D1714" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="F1714" t="s">
         <v>21</v>
@@ -47515,10 +47537,10 @@
         <v>29</v>
       </c>
       <c r="C1715">
-        <v>5531</v>
+        <v>2118</v>
       </c>
       <c r="D1715" t="s">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="F1715" t="s">
         <v>21</v>
@@ -47530,7 +47552,7 @@
         <v>0</v>
       </c>
       <c r="I1715" s="1">
-        <v>46146.648726851854</v>
+        <v>46146.649421296293</v>
       </c>
       <c r="J1715">
         <v>0</v>
@@ -47544,10 +47566,10 @@
         <v>29</v>
       </c>
       <c r="C1716">
-        <v>2118</v>
+        <v>2089</v>
       </c>
       <c r="D1716" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F1716" t="s">
         <v>21</v>
@@ -47559,7 +47581,7 @@
         <v>0</v>
       </c>
       <c r="I1716" s="1">
-        <v>46146.649421296293</v>
+        <v>46146.65011574074</v>
       </c>
       <c r="J1716">
         <v>0</v>
@@ -47573,10 +47595,10 @@
         <v>29</v>
       </c>
       <c r="C1717">
-        <v>2089</v>
+        <v>3206</v>
       </c>
       <c r="D1717" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="F1717" t="s">
         <v>21</v>
@@ -47588,7 +47610,7 @@
         <v>0</v>
       </c>
       <c r="I1717" s="1">
-        <v>46146.65011574074</v>
+        <v>46146.626620370371</v>
       </c>
       <c r="J1717">
         <v>0</v>
@@ -47602,10 +47624,10 @@
         <v>29</v>
       </c>
       <c r="C1718">
-        <v>3206</v>
+        <v>2905</v>
       </c>
       <c r="D1718" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="F1718" t="s">
         <v>21</v>
@@ -47617,7 +47639,7 @@
         <v>0</v>
       </c>
       <c r="I1718" s="1">
-        <v>46146.626620370371</v>
+        <v>46146.627314814818</v>
       </c>
       <c r="J1718">
         <v>0</v>
@@ -47631,10 +47653,10 @@
         <v>29</v>
       </c>
       <c r="C1719">
-        <v>2905</v>
+        <v>2652</v>
       </c>
       <c r="D1719" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="F1719" t="s">
         <v>21</v>
@@ -47646,7 +47668,7 @@
         <v>0</v>
       </c>
       <c r="I1719" s="1">
-        <v>46146.627314814818</v>
+        <v>46146.628009259257</v>
       </c>
       <c r="J1719">
         <v>0</v>
@@ -47660,10 +47682,10 @@
         <v>29</v>
       </c>
       <c r="C1720">
-        <v>2652</v>
+        <v>2511</v>
       </c>
       <c r="D1720" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="F1720" t="s">
         <v>21</v>
@@ -47689,10 +47711,10 @@
         <v>29</v>
       </c>
       <c r="C1721">
-        <v>2511</v>
+        <v>2499</v>
       </c>
       <c r="D1721" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="F1721" t="s">
         <v>21</v>
@@ -47704,7 +47726,7 @@
         <v>0</v>
       </c>
       <c r="I1721" s="1">
-        <v>46146.628009259257</v>
+        <v>46146.628703703704</v>
       </c>
       <c r="J1721">
         <v>0</v>
@@ -47718,22 +47740,22 @@
         <v>29</v>
       </c>
       <c r="C1722">
-        <v>2499</v>
+        <v>2510</v>
       </c>
       <c r="D1722" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="F1722" t="s">
         <v>21</v>
       </c>
       <c r="G1722" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1722" s="2">
-        <v>0</v>
+        <v>6.3194444444444444E-3</v>
       </c>
       <c r="I1722" s="1">
-        <v>46146.628703703704</v>
+        <v>46146.62939814815</v>
       </c>
       <c r="J1722">
         <v>0</v>
@@ -47747,19 +47769,19 @@
         <v>29</v>
       </c>
       <c r="C1723">
-        <v>2510</v>
+        <v>3239</v>
       </c>
       <c r="D1723" t="s">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="F1723" t="s">
         <v>21</v>
       </c>
       <c r="G1723" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1723" s="2">
-        <v>0</v>
+        <v>7.0254629629629634E-3</v>
       </c>
       <c r="I1723" s="1">
         <v>46146.62939814815</v>
@@ -47776,22 +47798,22 @@
         <v>29</v>
       </c>
       <c r="C1724">
-        <v>3239</v>
+        <v>2088</v>
       </c>
       <c r="D1724" t="s">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="F1724" t="s">
         <v>21</v>
       </c>
       <c r="G1724" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1724" s="2">
-        <v>7.0254629629629634E-3</v>
+        <v>0</v>
       </c>
       <c r="I1724" s="1">
-        <v>46146.62939814815</v>
+        <v>46146.63009259259</v>
       </c>
       <c r="J1724">
         <v>0</v>
@@ -47805,10 +47827,10 @@
         <v>29</v>
       </c>
       <c r="C1725">
-        <v>2088</v>
+        <v>2903</v>
       </c>
       <c r="D1725" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F1725" t="s">
         <v>21</v>
@@ -47820,7 +47842,7 @@
         <v>0</v>
       </c>
       <c r="I1725" s="1">
-        <v>46146.63009259259</v>
+        <v>46146.630787037036</v>
       </c>
       <c r="J1725">
         <v>0</v>
@@ -47834,10 +47856,10 @@
         <v>29</v>
       </c>
       <c r="C1726">
-        <v>2903</v>
+        <v>2508</v>
       </c>
       <c r="D1726" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F1726" t="s">
         <v>21</v>
@@ -47849,7 +47871,7 @@
         <v>0</v>
       </c>
       <c r="I1726" s="1">
-        <v>46146.630787037036</v>
+        <v>46146.631481481483</v>
       </c>
       <c r="J1726">
         <v>0</v>
@@ -47863,10 +47885,10 @@
         <v>29</v>
       </c>
       <c r="C1727">
-        <v>2508</v>
+        <v>2648</v>
       </c>
       <c r="D1727" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F1727" t="s">
         <v>21</v>
@@ -47892,10 +47914,10 @@
         <v>29</v>
       </c>
       <c r="C1728">
-        <v>2648</v>
+        <v>2459</v>
       </c>
       <c r="D1728" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F1728" t="s">
         <v>21</v>
@@ -47907,7 +47929,7 @@
         <v>0</v>
       </c>
       <c r="I1728" s="1">
-        <v>46146.631481481483</v>
+        <v>46146.632175925923</v>
       </c>
       <c r="J1728">
         <v>0</v>
@@ -47921,22 +47943,22 @@
         <v>29</v>
       </c>
       <c r="C1729">
-        <v>2459</v>
+        <v>2483</v>
       </c>
       <c r="D1729" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="F1729" t="s">
         <v>21</v>
       </c>
       <c r="G1729" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1729" s="2">
-        <v>0</v>
+        <v>8.6689814814814806E-3</v>
       </c>
       <c r="I1729" s="1">
-        <v>46146.632175925923</v>
+        <v>46146.632870370369</v>
       </c>
       <c r="J1729">
         <v>0</v>
@@ -47950,19 +47972,19 @@
         <v>29</v>
       </c>
       <c r="C1730">
-        <v>2483</v>
+        <v>2113</v>
       </c>
       <c r="D1730" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F1730" t="s">
         <v>21</v>
       </c>
       <c r="G1730" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H1730" s="2">
-        <v>8.6689814814814806E-3</v>
+        <v>0</v>
       </c>
       <c r="I1730" s="1">
         <v>46146.632870370369</v>
@@ -47979,10 +48001,10 @@
         <v>29</v>
       </c>
       <c r="C1731">
-        <v>2113</v>
+        <v>2490</v>
       </c>
       <c r="D1731" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="F1731" t="s">
         <v>21</v>
@@ -47994,7 +48016,7 @@
         <v>0</v>
       </c>
       <c r="I1731" s="1">
-        <v>46146.632870370369</v>
+        <v>46146.633564814816</v>
       </c>
       <c r="J1731">
         <v>0</v>
@@ -48008,10 +48030,10 @@
         <v>29</v>
       </c>
       <c r="C1732">
-        <v>2490</v>
+        <v>2638</v>
       </c>
       <c r="D1732" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="F1732" t="s">
         <v>21</v>
@@ -48023,7 +48045,7 @@
         <v>0</v>
       </c>
       <c r="I1732" s="1">
-        <v>46146.633564814816</v>
+        <v>46146.634259259263</v>
       </c>
       <c r="J1732">
         <v>0</v>
@@ -48037,10 +48059,10 @@
         <v>29</v>
       </c>
       <c r="C1733">
-        <v>2638</v>
+        <v>4919</v>
       </c>
       <c r="D1733" t="s">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="F1733" t="s">
         <v>21</v>
@@ -48066,22 +48088,22 @@
         <v>29</v>
       </c>
       <c r="C1734">
-        <v>4919</v>
+        <v>2509</v>
       </c>
       <c r="D1734" t="s">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="F1734" t="s">
         <v>21</v>
       </c>
       <c r="G1734" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1734" s="2">
-        <v>0</v>
+        <v>6.099537037037037E-3</v>
       </c>
       <c r="I1734" s="1">
-        <v>46146.634259259263</v>
+        <v>46146.634953703702</v>
       </c>
       <c r="J1734">
         <v>0</v>
@@ -48095,10 +48117,10 @@
         <v>29</v>
       </c>
       <c r="C1735">
-        <v>2509</v>
+        <v>2901</v>
       </c>
       <c r="D1735" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F1735" t="s">
         <v>21</v>
@@ -48110,7 +48132,7 @@
         <v>0</v>
       </c>
       <c r="I1735" s="1">
-        <v>46146.634953703702</v>
+        <v>46146.635648148149</v>
       </c>
       <c r="J1735">
         <v>0</v>
@@ -48124,10 +48146,10 @@
         <v>29</v>
       </c>
       <c r="C1736">
-        <v>2901</v>
+        <v>3130</v>
       </c>
       <c r="D1736" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="F1736" t="s">
         <v>21</v>
@@ -48153,10 +48175,10 @@
         <v>29</v>
       </c>
       <c r="C1737">
-        <v>3130</v>
+        <v>2653</v>
       </c>
       <c r="D1737" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="F1737" t="s">
         <v>21</v>
@@ -48168,7 +48190,7 @@
         <v>0</v>
       </c>
       <c r="I1737" s="1">
-        <v>46146.635648148149</v>
+        <v>46146.636342592596</v>
       </c>
       <c r="J1737">
         <v>0</v>
@@ -48182,10 +48204,10 @@
         <v>29</v>
       </c>
       <c r="C1738">
-        <v>2653</v>
+        <v>2485</v>
       </c>
       <c r="D1738" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="F1738" t="s">
         <v>21</v>
@@ -48197,7 +48219,7 @@
         <v>0</v>
       </c>
       <c r="I1738" s="1">
-        <v>46146.636342592596</v>
+        <v>46146.637037037035</v>
       </c>
       <c r="J1738">
         <v>0</v>
@@ -48211,19 +48233,19 @@
         <v>29</v>
       </c>
       <c r="C1739">
-        <v>2485</v>
+        <v>2074</v>
       </c>
       <c r="D1739" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="F1739" t="s">
         <v>21</v>
       </c>
       <c r="G1739" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1739" s="2">
-        <v>0</v>
+        <v>4.2245370370370371E-3</v>
       </c>
       <c r="I1739" s="1">
         <v>46146.637037037035</v>
@@ -48240,10 +48262,10 @@
         <v>29</v>
       </c>
       <c r="C1740">
-        <v>2074</v>
+        <v>2486</v>
       </c>
       <c r="D1740" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F1740" t="s">
         <v>21</v>
@@ -48255,7 +48277,7 @@
         <v>0</v>
       </c>
       <c r="I1740" s="1">
-        <v>46146.637037037035</v>
+        <v>46146.637731481482</v>
       </c>
       <c r="J1740">
         <v>0</v>
@@ -48269,10 +48291,10 @@
         <v>29</v>
       </c>
       <c r="C1741">
-        <v>2486</v>
+        <v>2065</v>
       </c>
       <c r="D1741" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F1741" t="s">
         <v>21</v>
@@ -48284,7 +48306,7 @@
         <v>0</v>
       </c>
       <c r="I1741" s="1">
-        <v>46146.637731481482</v>
+        <v>46146.638425925928</v>
       </c>
       <c r="J1741">
         <v>0</v>
@@ -48298,10 +48320,10 @@
         <v>29</v>
       </c>
       <c r="C1742">
-        <v>2065</v>
+        <v>2649</v>
       </c>
       <c r="D1742" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F1742" t="s">
         <v>21</v>
@@ -48327,10 +48349,10 @@
         <v>29</v>
       </c>
       <c r="C1743">
-        <v>2649</v>
+        <v>2611</v>
       </c>
       <c r="D1743" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F1743" t="s">
         <v>21</v>
@@ -48342,7 +48364,7 @@
         <v>0</v>
       </c>
       <c r="I1743" s="1">
-        <v>46146.638425925928</v>
+        <v>46146.639120370368</v>
       </c>
       <c r="J1743">
         <v>0</v>
@@ -48356,10 +48378,10 @@
         <v>29</v>
       </c>
       <c r="C1744">
-        <v>2611</v>
+        <v>2498</v>
       </c>
       <c r="D1744" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F1744" t="s">
         <v>21</v>
@@ -48371,7 +48393,7 @@
         <v>0</v>
       </c>
       <c r="I1744" s="1">
-        <v>46146.639120370368</v>
+        <v>46146.639814814815</v>
       </c>
       <c r="J1744">
         <v>0</v>
@@ -48385,19 +48407,19 @@
         <v>29</v>
       </c>
       <c r="C1745">
-        <v>2498</v>
+        <v>5532</v>
       </c>
       <c r="D1745" t="s">
-        <v>95</v>
+        <v>168</v>
       </c>
       <c r="F1745" t="s">
         <v>21</v>
       </c>
       <c r="G1745" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H1745" s="2">
-        <v>0</v>
+        <v>1.1863425925925927E-2</v>
       </c>
       <c r="I1745" s="1">
         <v>46146.639814814815</v>
@@ -48410,33 +48432,8 @@
       </c>
     </row>
     <row r="1746" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1746" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1746">
-        <v>5532</v>
-      </c>
-      <c r="D1746" t="s">
-        <v>168</v>
-      </c>
-      <c r="F1746" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1746" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1746" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1746" s="1">
-        <v>46146.639814814815</v>
-      </c>
-      <c r="J1746">
-        <v>0</v>
-      </c>
-      <c r="K1746" t="s">
-        <v>11</v>
-      </c>
+      <c r="H1746" s="2"/>
+      <c r="I1746" s="1"/>
     </row>
     <row r="1747" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H1747" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Apple Towing - Samsara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3A5857-7A6E-4AB6-86A1-E777E88B1CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDE34D8-3ECA-43C1-AEA3-FB2477634DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8516" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8508" uniqueCount="170">
   <si>
     <t>Company Name</t>
   </si>
@@ -48658,7 +48658,7 @@
         <v>16</v>
       </c>
       <c r="I1757" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J1757" s="2">
         <v>3.4722222222222222E-5</v>
@@ -48674,10 +48674,32 @@
       </c>
     </row>
     <row r="1758" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H1758" s="2"/>
-      <c r="I1758" s="1"/>
+      <c r="D1758" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1758">
+        <v>2633</v>
+      </c>
+      <c r="F1758" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1758" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1758" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1758" s="2">
+        <v>9.3981481481481485E-3</v>
+      </c>
+      <c r="K1758" s="1">
+        <v>46174.510763888888</v>
+      </c>
+      <c r="L1758">
+        <v>0</v>
+      </c>
       <c r="M1758" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1759" spans="4:13" x14ac:dyDescent="0.3">
@@ -48685,10 +48707,10 @@
         <v>35</v>
       </c>
       <c r="E1759">
-        <v>2633</v>
+        <v>2247</v>
       </c>
       <c r="F1759" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="H1759" s="2" t="s">
         <v>16</v>
@@ -48697,10 +48719,10 @@
         <v>10</v>
       </c>
       <c r="J1759" s="2">
-        <v>9.3981481481481485E-3</v>
+        <v>0.77934027777777781</v>
       </c>
       <c r="K1759" s="1">
-        <v>46174.510763888888</v>
+        <v>46174.512152777781</v>
       </c>
       <c r="L1759">
         <v>0</v>
@@ -48714,10 +48736,10 @@
         <v>35</v>
       </c>
       <c r="E1760">
-        <v>2247</v>
+        <v>2116</v>
       </c>
       <c r="F1760" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="H1760" s="2" t="s">
         <v>16</v>
@@ -48726,10 +48748,10 @@
         <v>10</v>
       </c>
       <c r="J1760" s="2">
-        <v>0.77934027777777781</v>
+        <v>7.789351851851852E-3</v>
       </c>
       <c r="K1760" s="1">
-        <v>46174.512152777781</v>
+        <v>46174.51284722222</v>
       </c>
       <c r="L1760">
         <v>0</v>
@@ -48743,10 +48765,10 @@
         <v>35</v>
       </c>
       <c r="E1761">
-        <v>2116</v>
+        <v>2053</v>
       </c>
       <c r="F1761" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H1761" s="2" t="s">
         <v>16</v>
@@ -48755,7 +48777,7 @@
         <v>10</v>
       </c>
       <c r="J1761" s="2">
-        <v>7.789351851851852E-3</v>
+        <v>3.3564814814814812E-4</v>
       </c>
       <c r="K1761" s="1">
         <v>46174.51284722222</v>
@@ -48772,10 +48794,10 @@
         <v>35</v>
       </c>
       <c r="E1762">
-        <v>2053</v>
+        <v>4946</v>
       </c>
       <c r="F1762" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="H1762" s="2" t="s">
         <v>16</v>
@@ -48784,10 +48806,10 @@
         <v>10</v>
       </c>
       <c r="J1762" s="2">
-        <v>3.3564814814814812E-4</v>
+        <v>3.0092592592592595E-4</v>
       </c>
       <c r="K1762" s="1">
-        <v>46174.51284722222</v>
+        <v>46174.514930555553</v>
       </c>
       <c r="L1762">
         <v>0</v>
@@ -48801,10 +48823,10 @@
         <v>35</v>
       </c>
       <c r="E1763">
-        <v>4946</v>
+        <v>5531</v>
       </c>
       <c r="F1763" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H1763" s="2" t="s">
         <v>16</v>
@@ -48813,7 +48835,7 @@
         <v>10</v>
       </c>
       <c r="J1763" s="2">
-        <v>3.0092592592592595E-4</v>
+        <v>7.9976851851851858E-3</v>
       </c>
       <c r="K1763" s="1">
         <v>46174.514930555553</v>
@@ -48830,10 +48852,10 @@
         <v>35</v>
       </c>
       <c r="E1764">
-        <v>5531</v>
+        <v>3239</v>
       </c>
       <c r="F1764" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="H1764" s="2" t="s">
         <v>16</v>
@@ -48842,10 +48864,10 @@
         <v>10</v>
       </c>
       <c r="J1764" s="2">
-        <v>7.9976851851851858E-3</v>
+        <v>1.337962962962963E-2</v>
       </c>
       <c r="K1764" s="1">
-        <v>46174.514930555553</v>
+        <v>46174.51840277778</v>
       </c>
       <c r="L1764">
         <v>0</v>
@@ -48859,10 +48881,10 @@
         <v>35</v>
       </c>
       <c r="E1765">
-        <v>3239</v>
+        <v>2483</v>
       </c>
       <c r="F1765" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="H1765" s="2" t="s">
         <v>16</v>
@@ -48871,10 +48893,10 @@
         <v>10</v>
       </c>
       <c r="J1765" s="2">
-        <v>1.337962962962963E-2</v>
+        <v>8.1018518518518514E-3</v>
       </c>
       <c r="K1765" s="1">
-        <v>46174.51840277778</v>
+        <v>46174.503935185188</v>
       </c>
       <c r="L1765">
         <v>0</v>
@@ -48888,10 +48910,10 @@
         <v>35</v>
       </c>
       <c r="E1766">
-        <v>2483</v>
+        <v>2901</v>
       </c>
       <c r="F1766" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H1766" s="2" t="s">
         <v>16</v>
@@ -48900,10 +48922,10 @@
         <v>10</v>
       </c>
       <c r="J1766" s="2">
-        <v>8.1018518518518514E-3</v>
+        <v>8.0324074074074082E-3</v>
       </c>
       <c r="K1766" s="1">
-        <v>46174.503935185188</v>
+        <v>46174.506018518521</v>
       </c>
       <c r="L1766">
         <v>0</v>
@@ -48917,10 +48939,10 @@
         <v>35</v>
       </c>
       <c r="E1767">
-        <v>2901</v>
+        <v>2074</v>
       </c>
       <c r="F1767" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H1767" s="2" t="s">
         <v>16</v>
@@ -48929,10 +48951,10 @@
         <v>10</v>
       </c>
       <c r="J1767" s="2">
-        <v>8.0324074074074082E-3</v>
+        <v>7.8935185185185185E-3</v>
       </c>
       <c r="K1767" s="1">
-        <v>46174.506018518521</v>
+        <v>46174.507407407407</v>
       </c>
       <c r="L1767">
         <v>0</v>
@@ -48946,10 +48968,10 @@
         <v>35</v>
       </c>
       <c r="E1768">
-        <v>2074</v>
+        <v>2486</v>
       </c>
       <c r="F1768" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H1768" s="2" t="s">
         <v>16</v>
@@ -48958,10 +48980,10 @@
         <v>10</v>
       </c>
       <c r="J1768" s="2">
-        <v>7.8935185185185185E-3</v>
+        <v>4.9942129629629628E-2</v>
       </c>
       <c r="K1768" s="1">
-        <v>46174.507407407407</v>
+        <v>46174.508101851854</v>
       </c>
       <c r="L1768">
         <v>0</v>
@@ -48975,25 +48997,25 @@
         <v>35</v>
       </c>
       <c r="E1769">
-        <v>2486</v>
+        <v>2111</v>
       </c>
       <c r="F1769" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="H1769" s="2" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
       <c r="I1769" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1769" s="2">
-        <v>4.9942129629629628E-2</v>
+        <v>0</v>
       </c>
       <c r="K1769" s="1">
-        <v>46174.508101851854</v>
+        <v>46176.463773148149</v>
       </c>
       <c r="L1769">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1769" t="s">
         <v>11</v>
@@ -49004,19 +49026,19 @@
         <v>35</v>
       </c>
       <c r="E1770">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="F1770" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H1770" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1770" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1770">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="J1770" s="2">
+        <v>8.5416666666666662E-3</v>
       </c>
       <c r="K1770" s="1">
         <v>46176.463773148149</v>
@@ -49033,25 +49055,25 @@
         <v>35</v>
       </c>
       <c r="E1771">
-        <v>2114</v>
+        <v>2613</v>
       </c>
       <c r="F1771" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H1771" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1771" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1771" s="2">
-        <v>8.5416666666666662E-3</v>
+        <v>0</v>
       </c>
       <c r="K1771" s="1">
         <v>46176.463773148149</v>
       </c>
       <c r="L1771">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1771" t="s">
         <v>11</v>
@@ -49062,22 +49084,22 @@
         <v>35</v>
       </c>
       <c r="E1772">
-        <v>2613</v>
+        <v>2506</v>
       </c>
       <c r="F1772" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1772" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1772" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J1772">
         <v>0</v>
       </c>
       <c r="K1772" s="1">
-        <v>46176.463773148149</v>
+        <v>46176.464467592596</v>
       </c>
       <c r="L1772">
         <v>0</v>
@@ -49087,39 +49109,40 @@
       </c>
     </row>
     <row r="1773" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D1773" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1773">
-        <v>2506</v>
-      </c>
-      <c r="F1773" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1773" s="2" t="s">
+      <c r="H1773" s="2"/>
+      <c r="I1773" s="1"/>
+      <c r="K1773" s="1"/>
+      <c r="M1773" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="1774" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D1774" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1774">
+        <v>2507</v>
+      </c>
+      <c r="F1774" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1774" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="I1773" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1773">
-        <v>0</v>
-      </c>
-      <c r="K1773" s="1">
+      <c r="I1774" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1774">
+        <v>0</v>
+      </c>
+      <c r="K1774" s="1">
         <v>46176.464467592596</v>
       </c>
-      <c r="L1773">
-        <v>0</v>
-      </c>
-      <c r="M1773" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1774" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H1774" s="2"/>
-      <c r="I1774" s="1"/>
+      <c r="L1774">
+        <v>1</v>
+      </c>
       <c r="M1774" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1775" spans="4:13" x14ac:dyDescent="0.3">
@@ -49127,25 +49150,25 @@
         <v>35</v>
       </c>
       <c r="E1775">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="F1775" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1775" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1775" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1775">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="J1775" s="2">
+        <v>8.8541666666666664E-3</v>
       </c>
       <c r="K1775" s="1">
-        <v>46176.464467592596</v>
+        <v>46176.465162037035</v>
       </c>
       <c r="L1775">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1775" t="s">
         <v>11</v>
@@ -49156,19 +49179,19 @@
         <v>35</v>
       </c>
       <c r="E1776">
-        <v>2505</v>
+        <v>2489</v>
       </c>
       <c r="F1776" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H1776" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1776" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1776">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="J1776" s="2">
+        <v>2.5706018518518517E-2</v>
       </c>
       <c r="K1776" s="1">
         <v>46176.465162037035</v>
@@ -49185,25 +49208,25 @@
         <v>35</v>
       </c>
       <c r="E1777">
-        <v>2489</v>
+        <v>2615</v>
       </c>
       <c r="F1777" t="s">
-        <v>43</v>
+        <v>114</v>
       </c>
       <c r="H1777" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1777" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1777" s="2">
-        <v>2.5706018518518517E-2</v>
+        <v>0</v>
       </c>
       <c r="K1777" s="1">
-        <v>46176.465162037035</v>
+        <v>46176.465856481482</v>
       </c>
       <c r="L1777">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1777" t="s">
         <v>11</v>
@@ -49214,35 +49237,57 @@
         <v>35</v>
       </c>
       <c r="E1778">
-        <v>2082</v>
+        <v>2612</v>
       </c>
       <c r="F1778" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H1778" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1778" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1778">
         <v>0</v>
       </c>
       <c r="K1778" s="1">
-        <v>46176.465162037035</v>
+        <v>46176.465856481482</v>
       </c>
       <c r="L1778">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1778" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1779" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H1779" s="2"/>
-      <c r="I1779" s="1"/>
+      <c r="D1779" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1779">
+        <v>2634</v>
+      </c>
+      <c r="F1779" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1779" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1779" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1779" s="2">
+        <v>2.1296296296296296E-2</v>
+      </c>
+      <c r="K1779" s="1">
+        <v>46176.466550925928</v>
+      </c>
+      <c r="L1779">
+        <v>0</v>
+      </c>
       <c r="M1779" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1780" spans="4:13" x14ac:dyDescent="0.3">
@@ -49250,10 +49295,10 @@
         <v>35</v>
       </c>
       <c r="E1780">
-        <v>2615</v>
+        <v>2636</v>
       </c>
       <c r="F1780" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H1780" s="2" t="s">
         <v>169</v>
@@ -49265,10 +49310,10 @@
         <v>0</v>
       </c>
       <c r="K1780" s="1">
-        <v>46176.465856481482</v>
+        <v>46176.466550925928</v>
       </c>
       <c r="L1780">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1780" t="s">
         <v>11</v>
@@ -49279,10 +49324,10 @@
         <v>35</v>
       </c>
       <c r="E1781">
-        <v>2612</v>
+        <v>2492</v>
       </c>
       <c r="F1781" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H1781" s="2" t="s">
         <v>169</v>
@@ -49294,10 +49339,10 @@
         <v>0</v>
       </c>
       <c r="K1781" s="1">
-        <v>46176.465856481482</v>
+        <v>46176.466550925928</v>
       </c>
       <c r="L1781">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1781" t="s">
         <v>11</v>
@@ -49308,25 +49353,25 @@
         <v>35</v>
       </c>
       <c r="E1782">
-        <v>2634</v>
+        <v>5065</v>
       </c>
       <c r="F1782" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="H1782" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1782" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1782" s="2">
-        <v>2.1296296296296296E-2</v>
+        <v>0</v>
       </c>
       <c r="K1782" s="1">
-        <v>46176.466550925928</v>
+        <v>46176.467245370368</v>
       </c>
       <c r="L1782">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1782" t="s">
         <v>11</v>
@@ -49337,10 +49382,10 @@
         <v>35</v>
       </c>
       <c r="E1783">
-        <v>2636</v>
+        <v>2632</v>
       </c>
       <c r="F1783" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="H1783" s="2" t="s">
         <v>169</v>
@@ -49352,10 +49397,10 @@
         <v>0</v>
       </c>
       <c r="K1783" s="1">
-        <v>46176.466550925928</v>
+        <v>46176.467245370368</v>
       </c>
       <c r="L1783">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1783" t="s">
         <v>11</v>
@@ -49366,10 +49411,10 @@
         <v>35</v>
       </c>
       <c r="E1784">
-        <v>2492</v>
+        <v>2902</v>
       </c>
       <c r="F1784" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="H1784" s="2" t="s">
         <v>169</v>
@@ -49381,10 +49426,10 @@
         <v>0</v>
       </c>
       <c r="K1784" s="1">
-        <v>46176.466550925928</v>
+        <v>46176.467939814815</v>
       </c>
       <c r="L1784">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1784" t="s">
         <v>11</v>
@@ -49395,10 +49440,10 @@
         <v>35</v>
       </c>
       <c r="E1785">
-        <v>5065</v>
+        <v>2115</v>
       </c>
       <c r="F1785" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="H1785" s="2" t="s">
         <v>169</v>
@@ -49410,10 +49455,10 @@
         <v>0</v>
       </c>
       <c r="K1785" s="1">
-        <v>46176.467245370368</v>
+        <v>46176.467939814815</v>
       </c>
       <c r="L1785">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1785" t="s">
         <v>11</v>
@@ -49424,10 +49469,10 @@
         <v>35</v>
       </c>
       <c r="E1786">
-        <v>2632</v>
+        <v>2635</v>
       </c>
       <c r="F1786" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H1786" s="2" t="s">
         <v>169</v>
@@ -49439,10 +49484,10 @@
         <v>0</v>
       </c>
       <c r="K1786" s="1">
-        <v>46176.467245370368</v>
+        <v>46176.467939814815</v>
       </c>
       <c r="L1786">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1786" t="s">
         <v>11</v>
@@ -49453,10 +49498,10 @@
         <v>35</v>
       </c>
       <c r="E1787">
-        <v>2902</v>
+        <v>2651</v>
       </c>
       <c r="F1787" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H1787" s="2" t="s">
         <v>169</v>
@@ -49468,10 +49513,10 @@
         <v>0</v>
       </c>
       <c r="K1787" s="1">
-        <v>46176.467939814815</v>
+        <v>46176.468634259261</v>
       </c>
       <c r="L1787">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1787" t="s">
         <v>11</v>
@@ -49482,10 +49527,10 @@
         <v>35</v>
       </c>
       <c r="E1788">
-        <v>2115</v>
+        <v>2503</v>
       </c>
       <c r="F1788" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H1788" s="2" t="s">
         <v>169</v>
@@ -49497,10 +49542,10 @@
         <v>0</v>
       </c>
       <c r="K1788" s="1">
-        <v>46176.467939814815</v>
+        <v>46176.468634259261</v>
       </c>
       <c r="L1788">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1788" t="s">
         <v>11</v>
@@ -49511,10 +49556,10 @@
         <v>35</v>
       </c>
       <c r="E1789">
-        <v>2635</v>
+        <v>2493</v>
       </c>
       <c r="F1789" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H1789" s="2" t="s">
         <v>169</v>
@@ -49526,10 +49571,10 @@
         <v>0</v>
       </c>
       <c r="K1789" s="1">
-        <v>46176.467939814815</v>
+        <v>46176.468634259261</v>
       </c>
       <c r="L1789">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1789" t="s">
         <v>11</v>
@@ -49540,22 +49585,22 @@
         <v>35</v>
       </c>
       <c r="E1790">
-        <v>2651</v>
+        <v>5388</v>
       </c>
       <c r="F1790" t="s">
-        <v>109</v>
+        <v>166</v>
       </c>
       <c r="H1790" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1790" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1790">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="J1790" s="2">
+        <v>3.3564814814814812E-4</v>
       </c>
       <c r="K1790" s="1">
-        <v>46176.468634259261</v>
+        <v>46176.469328703701</v>
       </c>
       <c r="L1790">
         <v>0</v>
@@ -49565,32 +49610,11 @@
       </c>
     </row>
     <row r="1791" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D1791" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1791">
-        <v>2503</v>
-      </c>
-      <c r="F1791" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1791" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I1791" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1791">
-        <v>0</v>
-      </c>
-      <c r="K1791" s="1">
-        <v>46176.468634259261</v>
-      </c>
-      <c r="L1791">
-        <v>0</v>
-      </c>
+      <c r="H1791" s="2"/>
+      <c r="I1791" s="1"/>
+      <c r="K1791" s="1"/>
       <c r="M1791" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1792" spans="4:13" x14ac:dyDescent="0.3">
@@ -49598,22 +49622,22 @@
         <v>35</v>
       </c>
       <c r="E1792">
-        <v>2493</v>
+        <v>5038</v>
       </c>
       <c r="F1792" t="s">
-        <v>66</v>
+        <v>161</v>
       </c>
       <c r="H1792" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1792" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1792">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="J1792" s="2">
+        <v>8.5416666666666662E-3</v>
       </c>
       <c r="K1792" s="1">
-        <v>46176.468634259261</v>
+        <v>46176.469328703701</v>
       </c>
       <c r="L1792">
         <v>0</v>
@@ -49627,35 +49651,57 @@
         <v>35</v>
       </c>
       <c r="E1793">
-        <v>5388</v>
+        <v>4961</v>
       </c>
       <c r="F1793" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H1793" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1793" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1793" s="2">
-        <v>3.3564814814814812E-4</v>
+        <v>0</v>
       </c>
       <c r="K1793" s="1">
-        <v>46176.469328703701</v>
+        <v>46176.470023148147</v>
       </c>
       <c r="L1793">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1793" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1794" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H1794" s="2"/>
-      <c r="I1794" s="1"/>
+      <c r="D1794" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1794">
+        <v>2497</v>
+      </c>
+      <c r="F1794" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1794" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1794" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1794" s="2">
+        <v>7.2222222222222219E-3</v>
+      </c>
+      <c r="K1794" s="1">
+        <v>46176.470023148147</v>
+      </c>
+      <c r="L1794">
+        <v>0</v>
+      </c>
       <c r="M1794" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1795" spans="4:13" x14ac:dyDescent="0.3">
@@ -49663,25 +49709,25 @@
         <v>35</v>
       </c>
       <c r="E1795">
-        <v>5038</v>
+        <v>2118</v>
       </c>
       <c r="F1795" t="s">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="H1795" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1795" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1795" s="2">
-        <v>8.5416666666666662E-3</v>
+        <v>0</v>
       </c>
       <c r="K1795" s="1">
-        <v>46176.469328703701</v>
+        <v>46176.470023148147</v>
       </c>
       <c r="L1795">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1795" t="s">
         <v>11</v>
@@ -49692,10 +49738,10 @@
         <v>35</v>
       </c>
       <c r="E1796">
-        <v>4961</v>
+        <v>2089</v>
       </c>
       <c r="F1796" t="s">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="H1796" s="2" t="s">
         <v>169</v>
@@ -49707,10 +49753,10 @@
         <v>0</v>
       </c>
       <c r="K1796" s="1">
-        <v>46176.470023148147</v>
+        <v>46176.470717592594</v>
       </c>
       <c r="L1796">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1796" t="s">
         <v>11</v>
@@ -49721,25 +49767,25 @@
         <v>35</v>
       </c>
       <c r="E1797">
-        <v>2497</v>
+        <v>3206</v>
       </c>
       <c r="F1797" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="H1797" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1797" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1797" s="2">
-        <v>7.2222222222222219E-3</v>
+        <v>0</v>
       </c>
       <c r="K1797" s="1">
-        <v>46176.470023148147</v>
+        <v>46176.470717592594</v>
       </c>
       <c r="L1797">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1797" t="s">
         <v>11</v>
@@ -49750,22 +49796,22 @@
         <v>35</v>
       </c>
       <c r="E1798">
-        <v>2118</v>
+        <v>2905</v>
       </c>
       <c r="F1798" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H1798" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1798" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1798">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="J1798" s="2">
+        <v>9.5486111111111119E-3</v>
       </c>
       <c r="K1798" s="1">
-        <v>46176.470023148147</v>
+        <v>46176.470717592594</v>
       </c>
       <c r="L1798">
         <v>0</v>
@@ -49779,10 +49825,10 @@
         <v>35</v>
       </c>
       <c r="E1799">
-        <v>2089</v>
+        <v>2652</v>
       </c>
       <c r="F1799" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="H1799" s="2" t="s">
         <v>169</v>
@@ -49794,10 +49840,10 @@
         <v>0</v>
       </c>
       <c r="K1799" s="1">
-        <v>46176.470717592594</v>
+        <v>46176.471412037034</v>
       </c>
       <c r="L1799">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1799" t="s">
         <v>11</v>
@@ -49808,10 +49854,10 @@
         <v>35</v>
       </c>
       <c r="E1800">
-        <v>3206</v>
+        <v>2511</v>
       </c>
       <c r="F1800" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="H1800" s="2" t="s">
         <v>169</v>
@@ -49823,10 +49869,10 @@
         <v>0</v>
       </c>
       <c r="K1800" s="1">
-        <v>46176.470717592594</v>
+        <v>46176.471412037034</v>
       </c>
       <c r="L1800">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1800" t="s">
         <v>11</v>
@@ -49837,25 +49883,25 @@
         <v>35</v>
       </c>
       <c r="E1801">
-        <v>2905</v>
+        <v>2499</v>
       </c>
       <c r="F1801" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="H1801" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1801" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1801" s="2">
-        <v>9.5486111111111119E-3</v>
+        <v>0</v>
       </c>
       <c r="K1801" s="1">
-        <v>46176.470717592594</v>
+        <v>46176.47210648148</v>
       </c>
       <c r="L1801">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1801" t="s">
         <v>11</v>
@@ -49866,22 +49912,22 @@
         <v>35</v>
       </c>
       <c r="E1802">
-        <v>2652</v>
+        <v>2510</v>
       </c>
       <c r="F1802" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="H1802" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1802" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1802">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="J1802" s="2">
+        <v>2.1273148148148149E-2</v>
       </c>
       <c r="K1802" s="1">
-        <v>46176.471412037034</v>
+        <v>46176.47210648148</v>
       </c>
       <c r="L1802">
         <v>0</v>
@@ -49895,10 +49941,10 @@
         <v>35</v>
       </c>
       <c r="E1803">
-        <v>2511</v>
+        <v>2088</v>
       </c>
       <c r="F1803" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H1803" s="2" t="s">
         <v>169</v>
@@ -49910,10 +49956,10 @@
         <v>0</v>
       </c>
       <c r="K1803" s="1">
-        <v>46176.471412037034</v>
+        <v>46176.47210648148</v>
       </c>
       <c r="L1803">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1803" t="s">
         <v>11</v>
@@ -49924,10 +49970,10 @@
         <v>35</v>
       </c>
       <c r="E1804">
-        <v>2499</v>
+        <v>2903</v>
       </c>
       <c r="F1804" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="H1804" s="2" t="s">
         <v>169</v>
@@ -49939,10 +49985,10 @@
         <v>0</v>
       </c>
       <c r="K1804" s="1">
-        <v>46176.47210648148</v>
+        <v>46176.472800925927</v>
       </c>
       <c r="L1804">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1804" t="s">
         <v>11</v>
@@ -49953,22 +49999,22 @@
         <v>35</v>
       </c>
       <c r="E1805">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="F1805" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H1805" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1805" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1805">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="J1805" s="2">
+        <v>1.1122685185185185E-2</v>
       </c>
       <c r="K1805" s="1">
-        <v>46176.47210648148</v>
+        <v>46176.472800925927</v>
       </c>
       <c r="L1805">
         <v>0</v>
@@ -49978,10 +50024,32 @@
       </c>
     </row>
     <row r="1806" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H1806" s="2"/>
-      <c r="I1806" s="1"/>
+      <c r="D1806" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1806">
+        <v>2648</v>
+      </c>
+      <c r="F1806" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1806" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1806" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1806">
+        <v>0</v>
+      </c>
+      <c r="K1806" s="1">
+        <v>46176.472800925927</v>
+      </c>
+      <c r="L1806">
+        <v>1</v>
+      </c>
       <c r="M1806" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1807" spans="4:13" x14ac:dyDescent="0.3">
@@ -49989,10 +50057,10 @@
         <v>35</v>
       </c>
       <c r="E1807">
-        <v>2088</v>
+        <v>2459</v>
       </c>
       <c r="F1807" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="H1807" s="2" t="s">
         <v>169</v>
@@ -50004,10 +50072,10 @@
         <v>0</v>
       </c>
       <c r="K1807" s="1">
-        <v>46176.47210648148</v>
+        <v>46176.473495370374</v>
       </c>
       <c r="L1807">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1807" t="s">
         <v>11</v>
@@ -50018,10 +50086,10 @@
         <v>35</v>
       </c>
       <c r="E1808">
-        <v>2903</v>
+        <v>2113</v>
       </c>
       <c r="F1808" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H1808" s="2" t="s">
         <v>169</v>
@@ -50033,10 +50101,10 @@
         <v>0</v>
       </c>
       <c r="K1808" s="1">
-        <v>46176.472800925927</v>
+        <v>46176.473495370374</v>
       </c>
       <c r="L1808">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1808" t="s">
         <v>11</v>
@@ -50047,10 +50115,10 @@
         <v>35</v>
       </c>
       <c r="E1809">
-        <v>2508</v>
+        <v>2490</v>
       </c>
       <c r="F1809" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="H1809" s="2" t="s">
         <v>169</v>
@@ -50059,10 +50127,10 @@
         <v>10</v>
       </c>
       <c r="J1809" s="2">
-        <v>1.1122685185185185E-2</v>
+        <v>7.5115740740740742E-3</v>
       </c>
       <c r="K1809" s="1">
-        <v>46176.472800925927</v>
+        <v>46176.474189814813</v>
       </c>
       <c r="L1809">
         <v>0</v>
@@ -50076,10 +50144,10 @@
         <v>35</v>
       </c>
       <c r="E1810">
-        <v>2648</v>
+        <v>2638</v>
       </c>
       <c r="F1810" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="H1810" t="s">
         <v>169</v>
@@ -50091,10 +50159,10 @@
         <v>0</v>
       </c>
       <c r="K1810" s="1">
-        <v>46176.472800925927</v>
+        <v>46176.474189814813</v>
       </c>
       <c r="L1810">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1810" t="s">
         <v>11</v>
@@ -50105,10 +50173,10 @@
         <v>35</v>
       </c>
       <c r="E1811">
-        <v>2459</v>
+        <v>4919</v>
       </c>
       <c r="F1811" t="s">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="H1811" t="s">
         <v>169</v>
@@ -50120,10 +50188,10 @@
         <v>0</v>
       </c>
       <c r="K1811" s="1">
-        <v>46176.473495370374</v>
+        <v>46176.474189814813</v>
       </c>
       <c r="L1811">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1811" t="s">
         <v>11</v>
@@ -50134,22 +50202,22 @@
         <v>35</v>
       </c>
       <c r="E1812">
-        <v>2113</v>
+        <v>2509</v>
       </c>
       <c r="F1812" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H1812" s="2" t="s">
         <v>169</v>
       </c>
       <c r="I1812" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1812">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="J1812" s="2">
+        <v>6.6782407407407407E-3</v>
       </c>
       <c r="K1812" s="1">
-        <v>46176.473495370374</v>
+        <v>46176.502083333333</v>
       </c>
       <c r="L1812">
         <v>0</v>
@@ -50163,25 +50231,25 @@
         <v>35</v>
       </c>
       <c r="E1813">
-        <v>2490</v>
+        <v>3130</v>
       </c>
       <c r="F1813" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="H1813" t="s">
         <v>169</v>
       </c>
       <c r="I1813" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J1813" s="2">
-        <v>7.5115740740740742E-3</v>
+        <v>0</v>
       </c>
       <c r="K1813" s="1">
-        <v>46176.474189814813</v>
+        <v>46176.50277777778</v>
       </c>
       <c r="L1813">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1813" t="s">
         <v>11</v>
@@ -50192,10 +50260,10 @@
         <v>35</v>
       </c>
       <c r="E1814">
-        <v>2638</v>
+        <v>2653</v>
       </c>
       <c r="F1814" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="H1814" t="s">
         <v>169</v>
@@ -50207,10 +50275,10 @@
         <v>0</v>
       </c>
       <c r="K1814" s="1">
-        <v>46176.474189814813</v>
+        <v>46176.503472222219</v>
       </c>
       <c r="L1814">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1814" t="s">
         <v>11</v>
@@ -50221,25 +50289,25 @@
         <v>35</v>
       </c>
       <c r="E1815">
-        <v>4919</v>
+        <v>2485</v>
       </c>
       <c r="F1815" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="H1815" t="s">
         <v>169</v>
       </c>
       <c r="I1815" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1815">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="J1815" s="2">
+        <v>7.1759259259259259E-3</v>
       </c>
       <c r="K1815" s="1">
-        <v>46176.474189814813</v>
+        <v>46176.503472222219</v>
       </c>
       <c r="L1815">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1815" t="s">
         <v>11</v>
@@ -50250,10 +50318,10 @@
         <v>35</v>
       </c>
       <c r="E1816">
-        <v>2509</v>
+        <v>2065</v>
       </c>
       <c r="F1816" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H1816" s="2" t="s">
         <v>169</v>
@@ -50262,10 +50330,10 @@
         <v>10</v>
       </c>
       <c r="J1816" s="2">
-        <v>6.6782407407407407E-3</v>
+        <v>8.819444444444444E-3</v>
       </c>
       <c r="K1816" s="1">
-        <v>46176.502083333333</v>
+        <v>46176.504166666666</v>
       </c>
       <c r="L1816">
         <v>0</v>
@@ -50279,10 +50347,10 @@
         <v>35</v>
       </c>
       <c r="E1817">
-        <v>3130</v>
+        <v>2649</v>
       </c>
       <c r="F1817" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="H1817" s="2" t="s">
         <v>169</v>
@@ -50294,10 +50362,10 @@
         <v>0</v>
       </c>
       <c r="K1817" s="1">
-        <v>46176.50277777778</v>
+        <v>46176.504166666666</v>
       </c>
       <c r="L1817">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1817" t="s">
         <v>11</v>
@@ -50308,10 +50376,10 @@
         <v>35</v>
       </c>
       <c r="E1818">
-        <v>2653</v>
+        <v>2611</v>
       </c>
       <c r="F1818" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H1818" t="s">
         <v>169</v>
@@ -50323,10 +50391,10 @@
         <v>0</v>
       </c>
       <c r="K1818" s="1">
-        <v>46176.503472222219</v>
+        <v>46176.504861111112</v>
       </c>
       <c r="L1818">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1818" t="s">
         <v>11</v>
@@ -50337,10 +50405,10 @@
         <v>35</v>
       </c>
       <c r="E1819">
-        <v>2485</v>
+        <v>2498</v>
       </c>
       <c r="F1819" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="H1819" t="s">
         <v>169</v>
@@ -50352,130 +50420,34 @@
         <v>0</v>
       </c>
       <c r="K1819" s="1">
-        <v>46176.503472222219</v>
+        <v>46176.505555555559</v>
       </c>
       <c r="L1819">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1819" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1820" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D1820" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1820">
-        <v>2065</v>
-      </c>
-      <c r="F1820" t="s">
-        <v>97</v>
-      </c>
-      <c r="H1820" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I1820" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1820" s="2">
-        <v>8.819444444444444E-3</v>
-      </c>
-      <c r="K1820" s="1">
-        <v>46176.504166666666</v>
-      </c>
-      <c r="L1820">
-        <v>0</v>
-      </c>
-      <c r="M1820" t="s">
-        <v>11</v>
-      </c>
+      <c r="H1820" s="2"/>
+      <c r="I1820" s="1"/>
+      <c r="J1820" s="2"/>
+      <c r="K1820" s="1"/>
     </row>
     <row r="1821" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D1821" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1821">
-        <v>2649</v>
-      </c>
-      <c r="F1821" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1821" t="s">
-        <v>169</v>
-      </c>
-      <c r="I1821" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1821">
-        <v>0</v>
-      </c>
-      <c r="K1821" s="1">
-        <v>46176.504166666666</v>
-      </c>
-      <c r="L1821">
-        <v>0</v>
-      </c>
-      <c r="M1821" t="s">
-        <v>11</v>
-      </c>
+      <c r="I1821" s="1"/>
+      <c r="K1821" s="1"/>
     </row>
     <row r="1822" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D1822" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1822">
-        <v>2611</v>
-      </c>
-      <c r="F1822" t="s">
-        <v>100</v>
-      </c>
-      <c r="H1822" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I1822" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1822">
-        <v>0</v>
-      </c>
-      <c r="K1822" s="1">
-        <v>46176.504861111112</v>
-      </c>
-      <c r="L1822">
-        <v>0</v>
-      </c>
-      <c r="M1822" t="s">
-        <v>11</v>
-      </c>
+      <c r="H1822" s="2"/>
+      <c r="I1822" s="1"/>
+      <c r="K1822" s="1"/>
     </row>
     <row r="1823" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D1823" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1823">
-        <v>2498</v>
-      </c>
-      <c r="F1823" t="s">
-        <v>101</v>
-      </c>
-      <c r="H1823" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I1823" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1823">
-        <v>0</v>
-      </c>
-      <c r="K1823" s="1">
-        <v>46176.505555555559</v>
-      </c>
-      <c r="L1823">
-        <v>0</v>
-      </c>
-      <c r="M1823" t="s">
-        <v>11</v>
-      </c>
+      <c r="H1823" s="2"/>
+      <c r="I1823" s="1"/>
+      <c r="K1823" s="1"/>
     </row>
     <row r="1824" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H1824" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Apple Towing - Samsara\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\apple-towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C3B234-CA06-42A4-88DE-5F5C16CCFF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8749041-A48C-423A-A491-2C90D492D643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49235,7 +49235,7 @@
         <v>46176.463773148149</v>
       </c>
       <c r="J1769">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1769" t="s">
         <v>11</v>
@@ -49293,7 +49293,7 @@
         <v>46176.463773148149</v>
       </c>
       <c r="J1771">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1771" t="s">
         <v>11</v>
@@ -49360,7 +49360,7 @@
         <v>46176.464467592596</v>
       </c>
       <c r="J1774">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1774" t="s">
         <v>11</v>
@@ -49447,7 +49447,7 @@
         <v>46176.465856481482</v>
       </c>
       <c r="J1777">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1777" t="s">
         <v>11</v>
@@ -49476,7 +49476,7 @@
         <v>46176.465856481482</v>
       </c>
       <c r="J1778">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1778" t="s">
         <v>11</v>
@@ -49534,7 +49534,7 @@
         <v>46176.466550925928</v>
       </c>
       <c r="J1780">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1780" t="s">
         <v>11</v>
@@ -49554,7 +49554,7 @@
         <v>169</v>
       </c>
       <c r="G1781" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1781">
         <v>0</v>
@@ -49563,39 +49563,19 @@
         <v>46176.466550925928</v>
       </c>
       <c r="J1781">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1781" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="1782" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1782" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1782">
-        <v>5065</v>
-      </c>
-      <c r="D1782" t="s">
-        <v>165</v>
-      </c>
-      <c r="F1782" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G1782" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1782" s="2">
-        <v>0</v>
-      </c>
-      <c r="I1782" s="1">
-        <v>46176.467245370368</v>
-      </c>
-      <c r="J1782">
-        <v>1</v>
-      </c>
+      <c r="F1782" s="2"/>
+      <c r="G1782" s="1"/>
+      <c r="H1782" s="2"/>
+      <c r="I1782" s="1"/>
       <c r="K1782" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1783" spans="2:11" x14ac:dyDescent="0.25">
@@ -49603,10 +49583,10 @@
         <v>35</v>
       </c>
       <c r="C1783">
-        <v>2632</v>
+        <v>5065</v>
       </c>
       <c r="D1783" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="F1783" s="2" t="s">
         <v>169</v>
@@ -49621,7 +49601,7 @@
         <v>46176.467245370368</v>
       </c>
       <c r="J1783">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1783" t="s">
         <v>11</v>
@@ -49632,25 +49612,25 @@
         <v>35</v>
       </c>
       <c r="C1784">
-        <v>2902</v>
+        <v>2632</v>
       </c>
       <c r="D1784" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="F1784" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1784" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1784" s="2">
-        <v>0</v>
+        <v>8.0787037037037043E-3</v>
       </c>
       <c r="I1784" s="1">
-        <v>46176.467939814815</v>
+        <v>46176.467245370368</v>
       </c>
       <c r="J1784">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1784" t="s">
         <v>11</v>
@@ -49661,10 +49641,10 @@
         <v>35</v>
       </c>
       <c r="C1785">
-        <v>2115</v>
+        <v>2902</v>
       </c>
       <c r="D1785" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="F1785" s="2" t="s">
         <v>169</v>
@@ -49679,7 +49659,7 @@
         <v>46176.467939814815</v>
       </c>
       <c r="J1785">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1785" t="s">
         <v>11</v>
@@ -49690,10 +49670,10 @@
         <v>35</v>
       </c>
       <c r="C1786">
-        <v>2635</v>
+        <v>2115</v>
       </c>
       <c r="D1786" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F1786" s="2" t="s">
         <v>169</v>
@@ -49708,7 +49688,7 @@
         <v>46176.467939814815</v>
       </c>
       <c r="J1786">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1786" t="s">
         <v>11</v>
@@ -49719,10 +49699,10 @@
         <v>35</v>
       </c>
       <c r="C1787">
-        <v>2651</v>
+        <v>2635</v>
       </c>
       <c r="D1787" t="s">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="F1787" s="2" t="s">
         <v>169</v>
@@ -49734,10 +49714,10 @@
         <v>0</v>
       </c>
       <c r="I1787" s="1">
-        <v>46176.468634259261</v>
+        <v>46176.467939814815</v>
       </c>
       <c r="J1787">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1787" t="s">
         <v>11</v>
@@ -49748,10 +49728,10 @@
         <v>35</v>
       </c>
       <c r="C1788">
-        <v>2503</v>
+        <v>2651</v>
       </c>
       <c r="D1788" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="F1788" s="2" t="s">
         <v>169</v>
@@ -49766,7 +49746,7 @@
         <v>46176.468634259261</v>
       </c>
       <c r="J1788">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1788" t="s">
         <v>11</v>
@@ -49777,10 +49757,10 @@
         <v>35</v>
       </c>
       <c r="C1789">
-        <v>2493</v>
+        <v>2503</v>
       </c>
       <c r="D1789" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F1789" s="2" t="s">
         <v>169</v>
@@ -49795,7 +49775,7 @@
         <v>46176.468634259261</v>
       </c>
       <c r="J1789">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1789" t="s">
         <v>11</v>
@@ -49806,66 +49786,66 @@
         <v>35</v>
       </c>
       <c r="C1790">
-        <v>5388</v>
+        <v>2493</v>
       </c>
       <c r="D1790" t="s">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="F1790" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1790" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1790" s="2">
+        <v>0</v>
+      </c>
+      <c r="I1790" s="1">
+        <v>46176.468634259261</v>
+      </c>
+      <c r="J1790">
+        <v>2</v>
+      </c>
+      <c r="K1790" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1791" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1791" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1791">
+        <v>5388</v>
+      </c>
+      <c r="D1791" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1791" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1791" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1790" s="2">
+      <c r="H1791" s="2">
         <v>3.3564814814814812E-4</v>
       </c>
-      <c r="I1790" s="1">
+      <c r="I1791" s="1">
         <v>46176.469328703701</v>
       </c>
-      <c r="J1790">
-        <v>0</v>
-      </c>
-      <c r="K1790" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1791" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F1791" s="2"/>
-      <c r="G1791" s="1"/>
-      <c r="H1791" s="2"/>
-      <c r="I1791" s="1"/>
+      <c r="J1791">
+        <v>0</v>
+      </c>
       <c r="K1791" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1792" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F1792" s="2"/>
+      <c r="G1792" s="1"/>
+      <c r="H1792" s="2"/>
+      <c r="I1792" s="1"/>
+      <c r="K1792" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="1792" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1792" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1792">
-        <v>5038</v>
-      </c>
-      <c r="D1792" t="s">
-        <v>161</v>
-      </c>
-      <c r="F1792" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G1792" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1792" s="2">
-        <v>8.5416666666666662E-3</v>
-      </c>
-      <c r="I1792" s="1">
-        <v>46176.469328703701</v>
-      </c>
-      <c r="J1792">
-        <v>0</v>
-      </c>
-      <c r="K1792" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="1793" spans="2:11" x14ac:dyDescent="0.25">
@@ -49873,25 +49853,25 @@
         <v>35</v>
       </c>
       <c r="C1793">
-        <v>4961</v>
+        <v>5038</v>
       </c>
       <c r="D1793" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F1793" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1793" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1793" s="2">
-        <v>0</v>
+        <v>8.5416666666666662E-3</v>
       </c>
       <c r="I1793" s="1">
-        <v>46176.470023148147</v>
+        <v>46176.469328703701</v>
       </c>
       <c r="J1793">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1793" t="s">
         <v>11</v>
@@ -49902,25 +49882,25 @@
         <v>35</v>
       </c>
       <c r="C1794">
-        <v>2497</v>
+        <v>4961</v>
       </c>
       <c r="D1794" t="s">
-        <v>70</v>
+        <v>162</v>
       </c>
       <c r="F1794" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1794" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1794" s="2">
-        <v>7.2222222222222219E-3</v>
+        <v>0</v>
       </c>
       <c r="I1794" s="1">
         <v>46176.470023148147</v>
       </c>
       <c r="J1794">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1794" t="s">
         <v>11</v>
@@ -49931,25 +49911,25 @@
         <v>35</v>
       </c>
       <c r="C1795">
-        <v>2118</v>
+        <v>2497</v>
       </c>
       <c r="D1795" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F1795" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1795" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1795" s="2">
-        <v>0</v>
+        <v>7.2222222222222219E-3</v>
       </c>
       <c r="I1795" s="1">
         <v>46176.470023148147</v>
       </c>
       <c r="J1795">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1795" t="s">
         <v>11</v>
@@ -49960,25 +49940,25 @@
         <v>35</v>
       </c>
       <c r="C1796">
-        <v>2089</v>
+        <v>2118</v>
       </c>
       <c r="D1796" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F1796" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1796" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1796" s="2">
-        <v>7.9282407407407409E-3</v>
+        <v>0</v>
       </c>
       <c r="I1796" s="1">
-        <v>46176.470717592594</v>
+        <v>46176.470023148147</v>
       </c>
       <c r="J1796">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1796" t="s">
         <v>11</v>
@@ -49989,19 +49969,19 @@
         <v>35</v>
       </c>
       <c r="C1797">
-        <v>3206</v>
+        <v>2089</v>
       </c>
       <c r="D1797" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="F1797" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1797" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1797" s="2">
-        <v>0</v>
+        <v>7.9282407407407409E-3</v>
       </c>
       <c r="I1797" s="1">
         <v>46176.470717592594</v>
@@ -50018,25 +49998,25 @@
         <v>35</v>
       </c>
       <c r="C1798">
-        <v>2905</v>
+        <v>3206</v>
       </c>
       <c r="D1798" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="F1798" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1798" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1798" s="2">
-        <v>9.5486111111111119E-3</v>
+        <v>0</v>
       </c>
       <c r="I1798" s="1">
         <v>46176.470717592594</v>
       </c>
       <c r="J1798">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1798" t="s">
         <v>11</v>
@@ -50047,25 +50027,25 @@
         <v>35</v>
       </c>
       <c r="C1799">
-        <v>2652</v>
+        <v>2905</v>
       </c>
       <c r="D1799" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="F1799" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1799" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1799" s="2">
-        <v>0</v>
+        <v>9.5486111111111119E-3</v>
       </c>
       <c r="I1799" s="1">
-        <v>46176.471412037034</v>
+        <v>46176.470717592594</v>
       </c>
       <c r="J1799">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1799" t="s">
         <v>11</v>
@@ -50076,25 +50056,25 @@
         <v>35</v>
       </c>
       <c r="C1800">
-        <v>2511</v>
+        <v>2652</v>
       </c>
       <c r="D1800" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F1800" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1800" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1800" s="2">
-        <v>8.2291666666666659E-3</v>
+        <v>0</v>
       </c>
       <c r="I1800" s="1">
         <v>46176.471412037034</v>
       </c>
       <c r="J1800">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1800" t="s">
         <v>11</v>
@@ -50105,22 +50085,22 @@
         <v>35</v>
       </c>
       <c r="C1801">
-        <v>2499</v>
+        <v>2511</v>
       </c>
       <c r="D1801" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="F1801" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1801" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1801" s="2">
-        <v>0</v>
+        <v>8.2291666666666659E-3</v>
       </c>
       <c r="I1801" s="1">
-        <v>46176.47210648148</v>
+        <v>46176.471412037034</v>
       </c>
       <c r="J1801">
         <v>1</v>
@@ -50134,25 +50114,25 @@
         <v>35</v>
       </c>
       <c r="C1802">
-        <v>2510</v>
+        <v>2499</v>
       </c>
       <c r="D1802" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="F1802" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1802" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1802" s="2">
-        <v>2.1273148148148149E-2</v>
+        <v>0</v>
       </c>
       <c r="I1802" s="1">
         <v>46176.47210648148</v>
       </c>
       <c r="J1802">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1802" t="s">
         <v>11</v>
@@ -50163,25 +50143,25 @@
         <v>35</v>
       </c>
       <c r="C1803">
-        <v>2088</v>
+        <v>2510</v>
       </c>
       <c r="D1803" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F1803" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1803" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1803" s="2">
-        <v>0</v>
+        <v>2.1273148148148149E-2</v>
       </c>
       <c r="I1803" s="1">
         <v>46176.47210648148</v>
       </c>
       <c r="J1803">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1803" t="s">
         <v>11</v>
@@ -50192,10 +50172,10 @@
         <v>35</v>
       </c>
       <c r="C1804">
-        <v>2903</v>
+        <v>2088</v>
       </c>
       <c r="D1804" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F1804" s="2" t="s">
         <v>169</v>
@@ -50207,7 +50187,7 @@
         <v>0</v>
       </c>
       <c r="I1804" s="1">
-        <v>46176.472800925927</v>
+        <v>46176.47210648148</v>
       </c>
       <c r="J1804">
         <v>1</v>
@@ -50221,25 +50201,25 @@
         <v>35</v>
       </c>
       <c r="C1805">
-        <v>2508</v>
+        <v>2903</v>
       </c>
       <c r="D1805" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F1805" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1805" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1805" s="2">
-        <v>1.1122685185185185E-2</v>
+        <v>0</v>
       </c>
       <c r="I1805" s="1">
         <v>46176.472800925927</v>
       </c>
       <c r="J1805">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1805" t="s">
         <v>11</v>
@@ -50250,25 +50230,25 @@
         <v>35</v>
       </c>
       <c r="C1806">
-        <v>2648</v>
+        <v>2508</v>
       </c>
       <c r="D1806" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="F1806" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1806" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1806" s="2">
-        <v>0</v>
+        <v>1.1122685185185185E-2</v>
       </c>
       <c r="I1806" s="1">
         <v>46176.472800925927</v>
       </c>
       <c r="J1806">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1806" t="s">
         <v>11</v>
@@ -50279,10 +50259,10 @@
         <v>35</v>
       </c>
       <c r="C1807">
-        <v>2459</v>
+        <v>2648</v>
       </c>
       <c r="D1807" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F1807" s="2" t="s">
         <v>169</v>
@@ -50294,10 +50274,10 @@
         <v>0</v>
       </c>
       <c r="I1807" s="1">
-        <v>46176.473495370374</v>
+        <v>46176.472800925927</v>
       </c>
       <c r="J1807">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1807" t="s">
         <v>11</v>
@@ -50308,10 +50288,10 @@
         <v>35</v>
       </c>
       <c r="C1808">
-        <v>2113</v>
+        <v>2459</v>
       </c>
       <c r="D1808" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="F1808" s="2" t="s">
         <v>169</v>
@@ -50337,25 +50317,25 @@
         <v>35</v>
       </c>
       <c r="C1809">
-        <v>2490</v>
+        <v>2113</v>
       </c>
       <c r="D1809" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
       <c r="F1809" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1809" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1809" s="2">
-        <v>7.5115740740740742E-3</v>
+        <v>0</v>
       </c>
       <c r="I1809" s="1">
-        <v>46176.474189814813</v>
+        <v>46176.473495370374</v>
       </c>
       <c r="J1809">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1809" t="s">
         <v>11</v>
@@ -50366,25 +50346,25 @@
         <v>35</v>
       </c>
       <c r="C1810">
-        <v>2638</v>
+        <v>2490</v>
       </c>
       <c r="D1810" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="F1810" t="s">
         <v>169</v>
       </c>
       <c r="G1810" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1810" s="2">
-        <v>0</v>
+        <v>7.5115740740740742E-3</v>
       </c>
       <c r="I1810" s="1">
         <v>46176.474189814813</v>
       </c>
       <c r="J1810">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1810" t="s">
         <v>11</v>
@@ -50395,10 +50375,10 @@
         <v>35</v>
       </c>
       <c r="C1811">
-        <v>4919</v>
+        <v>2638</v>
       </c>
       <c r="D1811" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="F1811" t="s">
         <v>169</v>
@@ -50413,7 +50393,7 @@
         <v>46176.474189814813</v>
       </c>
       <c r="J1811">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1811" t="s">
         <v>11</v>
@@ -50424,25 +50404,25 @@
         <v>35</v>
       </c>
       <c r="C1812">
-        <v>2509</v>
+        <v>4919</v>
       </c>
       <c r="D1812" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="F1812" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1812" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1812" s="2">
-        <v>6.6782407407407407E-3</v>
+        <v>0</v>
       </c>
       <c r="I1812" s="1">
-        <v>46176.502083333333</v>
+        <v>46176.474189814813</v>
       </c>
       <c r="J1812">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1812" t="s">
         <v>11</v>
@@ -50453,25 +50433,25 @@
         <v>35</v>
       </c>
       <c r="C1813">
-        <v>3130</v>
+        <v>2509</v>
       </c>
       <c r="D1813" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="F1813" t="s">
         <v>169</v>
       </c>
       <c r="G1813" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H1813" s="2">
-        <v>0</v>
+        <v>6.6782407407407407E-3</v>
       </c>
       <c r="I1813" s="1">
-        <v>46176.50277777778</v>
+        <v>46176.502083333333</v>
       </c>
       <c r="J1813">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1813" t="s">
         <v>11</v>
@@ -50482,10 +50462,10 @@
         <v>35</v>
       </c>
       <c r="C1814">
-        <v>2653</v>
+        <v>3130</v>
       </c>
       <c r="D1814" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="F1814" t="s">
         <v>169</v>
@@ -50497,10 +50477,10 @@
         <v>0</v>
       </c>
       <c r="I1814" s="1">
-        <v>46176.503472222219</v>
+        <v>46176.50277777778</v>
       </c>
       <c r="J1814">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1814" t="s">
         <v>11</v>
@@ -50511,25 +50491,25 @@
         <v>35</v>
       </c>
       <c r="C1815">
-        <v>2485</v>
+        <v>2653</v>
       </c>
       <c r="D1815" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F1815" t="s">
         <v>169</v>
       </c>
       <c r="G1815" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H1815" s="2">
-        <v>7.1759259259259259E-3</v>
+        <v>0</v>
       </c>
       <c r="I1815" s="1">
         <v>46176.503472222219</v>
       </c>
       <c r="J1815">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1815" t="s">
         <v>11</v>
@@ -50540,10 +50520,10 @@
         <v>35</v>
       </c>
       <c r="C1816">
-        <v>2065</v>
+        <v>2485</v>
       </c>
       <c r="D1816" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="F1816" s="2" t="s">
         <v>169</v>
@@ -50552,13 +50532,13 @@
         <v>10</v>
       </c>
       <c r="H1816" s="2">
-        <v>8.819444444444444E-3</v>
+        <v>7.1759259259259259E-3</v>
       </c>
       <c r="I1816" s="1">
-        <v>46176.504166666666</v>
+        <v>46176.503472222219</v>
       </c>
       <c r="J1816">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1816" t="s">
         <v>11</v>
@@ -50569,36 +50549,57 @@
         <v>35</v>
       </c>
       <c r="C1817">
-        <v>2649</v>
+        <v>2065</v>
       </c>
       <c r="D1817" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="F1817" s="2" t="s">
         <v>169</v>
       </c>
       <c r="G1817" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H1817" s="2">
-        <v>5.6261574074074075E-2</v>
+        <v>8.819444444444444E-3</v>
       </c>
       <c r="I1817" s="1">
         <v>46176.504166666666</v>
       </c>
       <c r="J1817">
+        <v>0</v>
+      </c>
+      <c r="K1817" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1818" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1818" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1818">
+        <v>2649</v>
+      </c>
+      <c r="D1818" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1818" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1818" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1818" s="2">
+        <v>6.1921296296296294E-2</v>
+      </c>
+      <c r="I1818" s="1">
+        <v>46176.504166666666</v>
+      </c>
+      <c r="J1818">
         <v>1</v>
       </c>
-      <c r="K1817" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1818" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="G1818" s="1"/>
-      <c r="H1818" s="2"/>
-      <c r="I1818" s="1"/>
       <c r="K1818" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1819" spans="2:11" x14ac:dyDescent="0.25">
@@ -50624,7 +50625,7 @@
         <v>46176.504861111112</v>
       </c>
       <c r="J1819">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1819" t="s">
         <v>11</v>
@@ -50653,7 +50654,7 @@
         <v>46176.505555555559</v>
       </c>
       <c r="J1820">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1820" t="s">
         <v>11</v>
